--- a/calendario_iglesia_datos.xlsx
+++ b/calendario_iglesia_datos.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Servidores" sheetId="1" r:id="R5ff2fdb293224362"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Servicios" sheetId="2" r:id="Re094bd2fa2cf4a33"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Estados" sheetId="3" r:id="Rfe2add4206d24fb6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Meses" sheetId="4" r:id="R890f81a78e0d4277"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Registro Servicios" sheetId="5" r:id="R8338c78a544d4a80"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Configuracion" sheetId="6" r:id="R9ab7a2e12cb54f21"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Servidores" sheetId="1" r:id="R6da3d35450894aef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Servicios" sheetId="2" r:id="R3dc9e9a7945641c3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Estados" sheetId="3" r:id="R63f7243222a44a1a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Meses" sheetId="4" r:id="Ra7c9c05c45e24971"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Registro Servicios" sheetId="5" r:id="R54f1f5f3c8714bc4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Configuracion" sheetId="6" r:id="R32e458b9f1ac4d93"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,8 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="1">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
+    <x:numFmt numFmtId="201" formatCode="0"/>
+    <x:numFmt numFmtId="202" formatCode="dd/mm/yyyy"/>
+    <x:numFmt numFmtId="203" formatCode="@"/>
   </x:numFmts>
   <x:fonts count="2">
     <x:font>
@@ -33,12 +36,17 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="3">
+  <x:fills count="4">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="gray125"/>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="0F766E"/>
+      </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
@@ -53,7 +61,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="16">
+  <x:cellXfs count="26">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -86,6 +94,26 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="200" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="201" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="201" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -463,7 +491,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4a2ff3a5e72f46e1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R84fc0369fa62446d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -557,7 +585,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5cb5b4bc94504033"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reff9a4effed94302"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -597,7 +625,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R700574e647b34c14"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R11680feeff1744d4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -717,7 +745,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc2a4b0e1fccd4359"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf434ef7dd4df4bfa"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1474,7 +1502,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb5ceb3515b0d4d50"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf161b2d1d2d04c51"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1488,49 +1516,137 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="8" t="str">
+      <x:c r="A1" s="22" t="str">
         <x:v>Parametro</x:v>
       </x:c>
-      <x:c r="B1" s="8" t="str">
+      <x:c r="B1" s="22" t="str">
         <x:v>Valor</x:v>
+      </x:c>
+      <x:c r="C1" s="25" t="str">
+        <x:v>Descripción</x:v>
+      </x:c>
+      <x:c r="D1" s="25" t="str">
+        <x:v>Editable</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="9" t="str">
         <x:v>CantidadGrupos</x:v>
       </x:c>
-      <x:c r="B2" s="9" t="n">
+      <x:c r="B2" s="17" t="n">
         <x:v>5</x:v>
+      </x:c>
+      <x:c r="C2" t="str">
+        <x:v>Total de grupos de servicio.</x:v>
+      </x:c>
+      <x:c r="D2" t="str">
+        <x:v>Sí</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="9" t="str">
-        <x:v>FechaReferenciaSemana</x:v>
-      </x:c>
-      <x:c r="B3" s="12" t="n">
+        <x:v>FechaBaseRotacion</x:v>
+      </x:c>
+      <x:c r="B3" s="18" t="n">
         <x:v>46173</x:v>
+      </x:c>
+      <x:c r="C3" t="str">
+        <x:v>Domingo de la semana conocida. Base fija para calcular la rotación.</x:v>
+      </x:c>
+      <x:c r="D3" t="str">
+        <x:v>Sí</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="9" t="str">
-        <x:v>GrupoReferencia</x:v>
-      </x:c>
-      <x:c r="B4" s="9" t="n">
+        <x:v>GrupoBaseRotacion</x:v>
+      </x:c>
+      <x:c r="B4" s="17" t="n">
         <x:v>5</x:v>
+      </x:c>
+      <x:c r="C4" t="str">
+        <x:v>Grupo que sirvió en la semana base.</x:v>
+      </x:c>
+      <x:c r="D4" t="str">
+        <x:v>Sí</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="9" t="str">
         <x:v>InicioSemana</x:v>
       </x:c>
-      <x:c r="B5" s="9" t="str">
+      <x:c r="B5" s="19" t="str">
         <x:v>Domingo</x:v>
+      </x:c>
+      <x:c r="C5" t="str">
+        <x:v>La app trabaja de domingo a sábado.</x:v>
+      </x:c>
+      <x:c r="D5" t="str">
+        <x:v>No</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="str">
+        <x:v>FechaSemanaActual</x:v>
+      </x:c>
+      <x:c r="B6" s="20" t="e">
+        <x:f>HOY()-DIASEM(HOY(),1)+1</x:f>
+      </x:c>
+      <x:c r="C6" t="str">
+        <x:v>Domingo de la semana actual. En Excel se actualiza al abrir/recalcular.</x:v>
+      </x:c>
+      <x:c r="D6" t="str">
+        <x:v>No</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="str">
+        <x:v>GrupoActivoActual</x:v>
+      </x:c>
+      <x:c r="B7" s="21" t="e">
+        <x:f>RESIDUO(B3-1+ENTERO((B6-B2)/7),B1)+1</x:f>
+      </x:c>
+      <x:c r="C7" t="str">
+        <x:v>Grupo que sirve esta semana según la rotación.</x:v>
+      </x:c>
+      <x:c r="D7" t="str">
+        <x:v>No</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" t="str">
+        <x:v>FechaReferenciaSemana</x:v>
+      </x:c>
+      <x:c r="B8" s="20" t="n">
+        <x:f>B2</x:f>
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C8" t="str">
+        <x:v>Compatibilidad: igual a FechaBaseRotacion.</x:v>
+      </x:c>
+      <x:c r="D8" t="str">
+        <x:v>No</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" t="str">
+        <x:v>GrupoReferencia</x:v>
+      </x:c>
+      <x:c r="B9" s="21" t="n">
+        <x:f>B3</x:f>
+        <x:v>46173</x:v>
+      </x:c>
+      <x:c r="C9" t="str">
+        <x:v>Compatibilidad: igual a GrupoBaseRotacion.</x:v>
+      </x:c>
+      <x:c r="D9" t="str">
+        <x:v>No</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc8d21a9a144b40bb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf2b4ff0304024aa4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/calendario_iglesia_datos.xlsx
+++ b/calendario_iglesia_datos.xlsx
@@ -2,12 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Servidores" sheetId="1" r:id="R6da3d35450894aef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Servicios" sheetId="2" r:id="R3dc9e9a7945641c3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Estados" sheetId="3" r:id="R63f7243222a44a1a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Meses" sheetId="4" r:id="Ra7c9c05c45e24971"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Registro Servicios" sheetId="5" r:id="R54f1f5f3c8714bc4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Configuracion" sheetId="6" r:id="R32e458b9f1ac4d93"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Servidores" sheetId="1" r:id="R76a94c6c68594ee6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Servicios" sheetId="2" r:id="Rbd2c3011ec1d4b2e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Estados" sheetId="3" r:id="R31b588c23e374acb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Meses" sheetId="4" r:id="Rd857367da101421c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Registro Servicios" sheetId="5" r:id="Rd16b2eae66ec4461"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Configuracion" sheetId="6" r:id="R9796f3f01d234e35"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lista Servidores" sheetId="7" r:id="R135a92fbf7004eec"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,11 +19,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="4">
+  <x:numFmts count="3">
     <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
     <x:numFmt numFmtId="201" formatCode="0"/>
-    <x:numFmt numFmtId="202" formatCode="dd/mm/yyyy"/>
-    <x:numFmt numFmtId="203" formatCode="@"/>
+    <x:numFmt numFmtId="202" formatCode="@"/>
   </x:numFmts>
   <x:fonts count="2">
     <x:font>
@@ -95,17 +95,6 @@
     </x:xf>
     <x:xf numFmtId="200" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="201" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="202" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="203" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="202" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="201" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" wrapText="1"/>
     </x:xf>
@@ -114,6 +103,19 @@
     <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -336,25 +338,47 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="10.229999542236328" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="5.110000133514404" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="5.110000133514404" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="4.710000038146973" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="35" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="8" t="str">
+      <x:c r="A1" s="21" t="str">
         <x:v>Servidor</x:v>
       </x:c>
-      <x:c r="B1" s="8" t="str">
+      <x:c r="B1" s="21" t="str">
         <x:v>Grupo</x:v>
       </x:c>
-      <x:c r="C1" s="8" t="str">
+      <x:c r="C1" s="21" t="str">
         <x:v>Activo</x:v>
       </x:c>
-      <x:c r="D1" s="8" t="str">
+      <x:c r="D1" s="21" t="str">
         <x:v>Notas</x:v>
       </x:c>
+      <x:c r="E1" s="22"/>
+      <x:c r="F1" s="22"/>
+      <x:c r="G1" s="22"/>
+      <x:c r="H1" s="22"/>
+      <x:c r="I1" s="22"/>
+      <x:c r="J1" s="22"/>
+      <x:c r="K1" s="22"/>
+      <x:c r="L1" s="22"/>
+      <x:c r="M1" s="22"/>
+      <x:c r="N1" s="22"/>
+      <x:c r="O1" s="22"/>
+      <x:c r="P1" s="22"/>
+      <x:c r="Q1" s="22"/>
+      <x:c r="R1" s="22"/>
+      <x:c r="S1" s="22"/>
+      <x:c r="T1" s="22"/>
+      <x:c r="U1" s="22"/>
+      <x:c r="V1" s="22"/>
+      <x:c r="W1" s="22"/>
+      <x:c r="X1" s="22"/>
+      <x:c r="Y1" s="22"/>
+      <x:c r="Z1" s="22"/>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="9" t="str">
@@ -489,9 +513,21 @@
       <x:c r="D12" s="9" t="str"/>
     </x:row>
   </x:sheetData>
+  <x:dataValidations count="3">
+    <x:dataValidation type="list" sqref="A2:A500">
+      <x:formula1>'Lista Servidores'!$A$2:$A$500</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="whole" operator="between" sqref="B2:B500">
+      <x:formula1>1</x:formula1>
+      <x:formula2>5</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="C2:C500">
+      <x:formula1>"Sí,No"</x:formula1>
+    </x:dataValidation>
+  </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R84fc0369fa62446d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9f495ffbd0314d19"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -500,21 +536,44 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="9.149999618530273" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="7.670000076293945" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="18.030000686645508" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="8" t="str">
+      <x:c r="A1" s="21" t="str">
         <x:v>Servicio</x:v>
       </x:c>
-      <x:c r="B1" s="8" t="str">
+      <x:c r="B1" s="21" t="str">
         <x:v>Categoria</x:v>
       </x:c>
-      <x:c r="C1" s="8" t="str">
+      <x:c r="C1" s="21" t="str">
         <x:v>Mostrar en calendario</x:v>
       </x:c>
+      <x:c r="D1" s="22"/>
+      <x:c r="E1" s="22"/>
+      <x:c r="F1" s="22"/>
+      <x:c r="G1" s="22"/>
+      <x:c r="H1" s="22"/>
+      <x:c r="I1" s="22"/>
+      <x:c r="J1" s="22"/>
+      <x:c r="K1" s="22"/>
+      <x:c r="L1" s="22"/>
+      <x:c r="M1" s="22"/>
+      <x:c r="N1" s="22"/>
+      <x:c r="O1" s="22"/>
+      <x:c r="P1" s="22"/>
+      <x:c r="Q1" s="22"/>
+      <x:c r="R1" s="22"/>
+      <x:c r="S1" s="22"/>
+      <x:c r="T1" s="22"/>
+      <x:c r="U1" s="22"/>
+      <x:c r="V1" s="22"/>
+      <x:c r="W1" s="22"/>
+      <x:c r="X1" s="22"/>
+      <x:c r="Y1" s="22"/>
+      <x:c r="Z1" s="22"/>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="9" t="str">
@@ -583,9 +642,17 @@
       </x:c>
     </x:row>
   </x:sheetData>
+  <x:dataValidations count="2">
+    <x:dataValidation type="list" sqref="B2:B500">
+      <x:formula1>"Servicio,Actividad"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="C2:C500">
+      <x:formula1>"Sí,No"</x:formula1>
+    </x:dataValidation>
+  </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reff9a4effed94302"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R80e3afe1b12644f9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -625,7 +692,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R11680feeff1744d4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9b9bcc10b0a34b67"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -745,7 +812,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf434ef7dd4df4bfa"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra1cc2442468040f1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -754,33 +821,58 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="4.980000019073486" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="10.229999542236328" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="9.149999618530273" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="9.420000076293945" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="20.459999084472656" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="20" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="20" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="20" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="38" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="28" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="28" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="28" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="8" t="str">
+      <x:c r="A1" s="21" t="str">
         <x:v>Fecha</x:v>
       </x:c>
-      <x:c r="B1" s="8" t="str">
+      <x:c r="B1" s="21" t="str">
         <x:v>TipoRegistro</x:v>
       </x:c>
-      <x:c r="C1" s="8" t="str">
+      <x:c r="C1" s="21" t="str">
         <x:v>ServicioActividad</x:v>
       </x:c>
-      <x:c r="D1" s="8" t="str">
+      <x:c r="D1" s="21" t="str">
         <x:v>Servidor</x:v>
       </x:c>
-      <x:c r="E1" s="8" t="str">
+      <x:c r="E1" s="21" t="str">
         <x:v>Estado</x:v>
       </x:c>
-      <x:c r="F1" s="8" t="str">
+      <x:c r="F1" s="21" t="str">
         <x:v>Observaciones</x:v>
       </x:c>
+      <x:c r="G1" s="22"/>
+      <x:c r="H1" s="21" t="str">
+        <x:v>Notas importantes</x:v>
+      </x:c>
+      <x:c r="I1" s="21" t="str"/>
+      <x:c r="J1" s="21" t="str"/>
+      <x:c r="K1" s="22"/>
+      <x:c r="L1" s="22"/>
+      <x:c r="M1" s="22"/>
+      <x:c r="N1" s="22"/>
+      <x:c r="O1" s="22"/>
+      <x:c r="P1" s="22"/>
+      <x:c r="Q1" s="22"/>
+      <x:c r="R1" s="22"/>
+      <x:c r="S1" s="22"/>
+      <x:c r="T1" s="22"/>
+      <x:c r="U1" s="22"/>
+      <x:c r="V1" s="22"/>
+      <x:c r="W1" s="22"/>
+      <x:c r="X1" s="22"/>
+      <x:c r="Y1" s="22"/>
+      <x:c r="Z1" s="22"/>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="12" t="n">
@@ -799,6 +891,13 @@
         <x:v>Confirmado</x:v>
       </x:c>
       <x:c r="F2" s="9" t="str"/>
+      <x:c r="H2" s="9" t="str">
+        <x:v>ServicioActividad</x:v>
+      </x:c>
+      <x:c r="I2" s="9" t="str">
+        <x:v>Se selecciona desde la hoja Servicios.</x:v>
+      </x:c>
+      <x:c r="J2" s="9" t="str"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="12" t="n">
@@ -817,6 +916,13 @@
         <x:v>Confirmado</x:v>
       </x:c>
       <x:c r="F3" s="9" t="str"/>
+      <x:c r="H3" s="9" t="str">
+        <x:v>Servidor</x:v>
+      </x:c>
+      <x:c r="I3" s="9" t="str">
+        <x:v>Se selecciona desde Lista Servidores.</x:v>
+      </x:c>
+      <x:c r="J3" s="9" t="str"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="12" t="n">
@@ -835,6 +941,13 @@
         <x:v>Pendiente</x:v>
       </x:c>
       <x:c r="F4" s="9" t="str"/>
+      <x:c r="H4" s="9" t="str">
+        <x:v>TipoRegistro</x:v>
+      </x:c>
+      <x:c r="I4" s="9" t="str">
+        <x:v>Usa Servicio para privilegios y Actividad para actividades generales.</x:v>
+      </x:c>
+      <x:c r="J4" s="9" t="str"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="12" t="n">
@@ -853,6 +966,13 @@
         <x:v>Pendiente</x:v>
       </x:c>
       <x:c r="F5" s="9" t="str"/>
+      <x:c r="H5" s="9" t="str">
+        <x:v>Duplicados</x:v>
+      </x:c>
+      <x:c r="I5" s="9" t="str">
+        <x:v>La app permite doble privilegio, pero muestra alerta.</x:v>
+      </x:c>
+      <x:c r="J5" s="9" t="str"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="12" t="n">
@@ -871,6 +991,13 @@
       <x:c r="F6" s="9" t="str">
         <x:v>Publicación de santa cena</x:v>
       </x:c>
+      <x:c r="H6" s="9" t="str">
+        <x:v>Configuración</x:v>
+      </x:c>
+      <x:c r="I6" s="9" t="str">
+        <x:v>El grupo activo se calcula automáticamente desde la fecha base.</x:v>
+      </x:c>
+      <x:c r="J6" s="9" t="str"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="12" t="n">
@@ -927,582 +1054,3951 @@
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="13"/>
+      <x:c r="A10" s="12"/>
+      <x:c r="B10" s="9"/>
+      <x:c r="C10" s="9"/>
+      <x:c r="D10" s="9"/>
+      <x:c r="E10" s="9"/>
+      <x:c r="F10" s="9"/>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="13"/>
+      <x:c r="A11" s="12"/>
+      <x:c r="B11" s="9"/>
+      <x:c r="C11" s="9"/>
+      <x:c r="D11" s="9"/>
+      <x:c r="E11" s="9"/>
+      <x:c r="F11" s="9"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="13"/>
+      <x:c r="A12" s="12"/>
+      <x:c r="B12" s="9"/>
+      <x:c r="C12" s="9"/>
+      <x:c r="D12" s="9"/>
+      <x:c r="E12" s="9"/>
+      <x:c r="F12" s="9"/>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="13"/>
+      <x:c r="A13" s="12"/>
+      <x:c r="B13" s="9"/>
+      <x:c r="C13" s="9"/>
+      <x:c r="D13" s="9"/>
+      <x:c r="E13" s="9"/>
+      <x:c r="F13" s="9"/>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="13"/>
+      <x:c r="A14" s="12"/>
+      <x:c r="B14" s="9"/>
+      <x:c r="C14" s="9"/>
+      <x:c r="D14" s="9"/>
+      <x:c r="E14" s="9"/>
+      <x:c r="F14" s="9"/>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="13"/>
+      <x:c r="A15" s="12"/>
+      <x:c r="B15" s="9"/>
+      <x:c r="C15" s="9"/>
+      <x:c r="D15" s="9"/>
+      <x:c r="E15" s="9"/>
+      <x:c r="F15" s="9"/>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="13"/>
+      <x:c r="A16" s="12"/>
+      <x:c r="B16" s="9"/>
+      <x:c r="C16" s="9"/>
+      <x:c r="D16" s="9"/>
+      <x:c r="E16" s="9"/>
+      <x:c r="F16" s="9"/>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" s="13"/>
+      <x:c r="A17" s="12"/>
+      <x:c r="B17" s="9"/>
+      <x:c r="C17" s="9"/>
+      <x:c r="D17" s="9"/>
+      <x:c r="E17" s="9"/>
+      <x:c r="F17" s="9"/>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" s="13"/>
+      <x:c r="A18" s="12"/>
+      <x:c r="B18" s="9"/>
+      <x:c r="C18" s="9"/>
+      <x:c r="D18" s="9"/>
+      <x:c r="E18" s="9"/>
+      <x:c r="F18" s="9"/>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" s="13"/>
+      <x:c r="A19" s="12"/>
+      <x:c r="B19" s="9"/>
+      <x:c r="C19" s="9"/>
+      <x:c r="D19" s="9"/>
+      <x:c r="E19" s="9"/>
+      <x:c r="F19" s="9"/>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" s="13"/>
+      <x:c r="A20" s="12"/>
+      <x:c r="B20" s="9"/>
+      <x:c r="C20" s="9"/>
+      <x:c r="D20" s="9"/>
+      <x:c r="E20" s="9"/>
+      <x:c r="F20" s="9"/>
     </x:row>
     <x:row r="21">
-      <x:c r="A21" s="13"/>
+      <x:c r="A21" s="12"/>
+      <x:c r="B21" s="9"/>
+      <x:c r="C21" s="9"/>
+      <x:c r="D21" s="9"/>
+      <x:c r="E21" s="9"/>
+      <x:c r="F21" s="9"/>
     </x:row>
     <x:row r="22">
-      <x:c r="A22" s="13"/>
+      <x:c r="A22" s="12"/>
+      <x:c r="B22" s="9"/>
+      <x:c r="C22" s="9"/>
+      <x:c r="D22" s="9"/>
+      <x:c r="E22" s="9"/>
+      <x:c r="F22" s="9"/>
     </x:row>
     <x:row r="23">
-      <x:c r="A23" s="13"/>
+      <x:c r="A23" s="12"/>
+      <x:c r="B23" s="9"/>
+      <x:c r="C23" s="9"/>
+      <x:c r="D23" s="9"/>
+      <x:c r="E23" s="9"/>
+      <x:c r="F23" s="9"/>
     </x:row>
     <x:row r="24">
-      <x:c r="A24" s="13"/>
+      <x:c r="A24" s="12"/>
+      <x:c r="B24" s="9"/>
+      <x:c r="C24" s="9"/>
+      <x:c r="D24" s="9"/>
+      <x:c r="E24" s="9"/>
+      <x:c r="F24" s="9"/>
     </x:row>
     <x:row r="25">
-      <x:c r="A25" s="13"/>
+      <x:c r="A25" s="12"/>
+      <x:c r="B25" s="9"/>
+      <x:c r="C25" s="9"/>
+      <x:c r="D25" s="9"/>
+      <x:c r="E25" s="9"/>
+      <x:c r="F25" s="9"/>
     </x:row>
     <x:row r="26">
-      <x:c r="A26" s="13"/>
+      <x:c r="A26" s="12"/>
+      <x:c r="B26" s="9"/>
+      <x:c r="C26" s="9"/>
+      <x:c r="D26" s="9"/>
+      <x:c r="E26" s="9"/>
+      <x:c r="F26" s="9"/>
     </x:row>
     <x:row r="27">
-      <x:c r="A27" s="13"/>
+      <x:c r="A27" s="12"/>
+      <x:c r="B27" s="9"/>
+      <x:c r="C27" s="9"/>
+      <x:c r="D27" s="9"/>
+      <x:c r="E27" s="9"/>
+      <x:c r="F27" s="9"/>
     </x:row>
     <x:row r="28">
-      <x:c r="A28" s="13"/>
+      <x:c r="A28" s="12"/>
+      <x:c r="B28" s="9"/>
+      <x:c r="C28" s="9"/>
+      <x:c r="D28" s="9"/>
+      <x:c r="E28" s="9"/>
+      <x:c r="F28" s="9"/>
     </x:row>
     <x:row r="29">
-      <x:c r="A29" s="13"/>
+      <x:c r="A29" s="12"/>
+      <x:c r="B29" s="9"/>
+      <x:c r="C29" s="9"/>
+      <x:c r="D29" s="9"/>
+      <x:c r="E29" s="9"/>
+      <x:c r="F29" s="9"/>
     </x:row>
     <x:row r="30">
-      <x:c r="A30" s="13"/>
+      <x:c r="A30" s="12"/>
+      <x:c r="B30" s="9"/>
+      <x:c r="C30" s="9"/>
+      <x:c r="D30" s="9"/>
+      <x:c r="E30" s="9"/>
+      <x:c r="F30" s="9"/>
     </x:row>
     <x:row r="31">
-      <x:c r="A31" s="13"/>
+      <x:c r="A31" s="12"/>
+      <x:c r="B31" s="9"/>
+      <x:c r="C31" s="9"/>
+      <x:c r="D31" s="9"/>
+      <x:c r="E31" s="9"/>
+      <x:c r="F31" s="9"/>
     </x:row>
     <x:row r="32">
-      <x:c r="A32" s="13"/>
+      <x:c r="A32" s="12"/>
+      <x:c r="B32" s="9"/>
+      <x:c r="C32" s="9"/>
+      <x:c r="D32" s="9"/>
+      <x:c r="E32" s="9"/>
+      <x:c r="F32" s="9"/>
     </x:row>
     <x:row r="33">
-      <x:c r="A33" s="13"/>
+      <x:c r="A33" s="12"/>
+      <x:c r="B33" s="9"/>
+      <x:c r="C33" s="9"/>
+      <x:c r="D33" s="9"/>
+      <x:c r="E33" s="9"/>
+      <x:c r="F33" s="9"/>
     </x:row>
     <x:row r="34">
-      <x:c r="A34" s="13"/>
+      <x:c r="A34" s="12"/>
+      <x:c r="B34" s="9"/>
+      <x:c r="C34" s="9"/>
+      <x:c r="D34" s="9"/>
+      <x:c r="E34" s="9"/>
+      <x:c r="F34" s="9"/>
     </x:row>
     <x:row r="35">
-      <x:c r="A35" s="13"/>
+      <x:c r="A35" s="12"/>
+      <x:c r="B35" s="9"/>
+      <x:c r="C35" s="9"/>
+      <x:c r="D35" s="9"/>
+      <x:c r="E35" s="9"/>
+      <x:c r="F35" s="9"/>
     </x:row>
     <x:row r="36">
-      <x:c r="A36" s="13"/>
+      <x:c r="A36" s="12"/>
+      <x:c r="B36" s="9"/>
+      <x:c r="C36" s="9"/>
+      <x:c r="D36" s="9"/>
+      <x:c r="E36" s="9"/>
+      <x:c r="F36" s="9"/>
     </x:row>
     <x:row r="37">
-      <x:c r="A37" s="13"/>
+      <x:c r="A37" s="12"/>
+      <x:c r="B37" s="9"/>
+      <x:c r="C37" s="9"/>
+      <x:c r="D37" s="9"/>
+      <x:c r="E37" s="9"/>
+      <x:c r="F37" s="9"/>
     </x:row>
     <x:row r="38">
-      <x:c r="A38" s="13"/>
+      <x:c r="A38" s="12"/>
+      <x:c r="B38" s="9"/>
+      <x:c r="C38" s="9"/>
+      <x:c r="D38" s="9"/>
+      <x:c r="E38" s="9"/>
+      <x:c r="F38" s="9"/>
     </x:row>
     <x:row r="39">
-      <x:c r="A39" s="13"/>
+      <x:c r="A39" s="12"/>
+      <x:c r="B39" s="9"/>
+      <x:c r="C39" s="9"/>
+      <x:c r="D39" s="9"/>
+      <x:c r="E39" s="9"/>
+      <x:c r="F39" s="9"/>
     </x:row>
     <x:row r="40">
-      <x:c r="A40" s="13"/>
+      <x:c r="A40" s="12"/>
+      <x:c r="B40" s="9"/>
+      <x:c r="C40" s="9"/>
+      <x:c r="D40" s="9"/>
+      <x:c r="E40" s="9"/>
+      <x:c r="F40" s="9"/>
     </x:row>
     <x:row r="41">
-      <x:c r="A41" s="13"/>
+      <x:c r="A41" s="12"/>
+      <x:c r="B41" s="9"/>
+      <x:c r="C41" s="9"/>
+      <x:c r="D41" s="9"/>
+      <x:c r="E41" s="9"/>
+      <x:c r="F41" s="9"/>
     </x:row>
     <x:row r="42">
-      <x:c r="A42" s="13"/>
+      <x:c r="A42" s="12"/>
+      <x:c r="B42" s="9"/>
+      <x:c r="C42" s="9"/>
+      <x:c r="D42" s="9"/>
+      <x:c r="E42" s="9"/>
+      <x:c r="F42" s="9"/>
     </x:row>
     <x:row r="43">
-      <x:c r="A43" s="13"/>
+      <x:c r="A43" s="12"/>
+      <x:c r="B43" s="9"/>
+      <x:c r="C43" s="9"/>
+      <x:c r="D43" s="9"/>
+      <x:c r="E43" s="9"/>
+      <x:c r="F43" s="9"/>
     </x:row>
     <x:row r="44">
-      <x:c r="A44" s="13"/>
+      <x:c r="A44" s="12"/>
+      <x:c r="B44" s="9"/>
+      <x:c r="C44" s="9"/>
+      <x:c r="D44" s="9"/>
+      <x:c r="E44" s="9"/>
+      <x:c r="F44" s="9"/>
     </x:row>
     <x:row r="45">
-      <x:c r="A45" s="13"/>
+      <x:c r="A45" s="12"/>
+      <x:c r="B45" s="9"/>
+      <x:c r="C45" s="9"/>
+      <x:c r="D45" s="9"/>
+      <x:c r="E45" s="9"/>
+      <x:c r="F45" s="9"/>
     </x:row>
     <x:row r="46">
-      <x:c r="A46" s="13"/>
+      <x:c r="A46" s="12"/>
+      <x:c r="B46" s="9"/>
+      <x:c r="C46" s="9"/>
+      <x:c r="D46" s="9"/>
+      <x:c r="E46" s="9"/>
+      <x:c r="F46" s="9"/>
     </x:row>
     <x:row r="47">
-      <x:c r="A47" s="13"/>
+      <x:c r="A47" s="12"/>
+      <x:c r="B47" s="9"/>
+      <x:c r="C47" s="9"/>
+      <x:c r="D47" s="9"/>
+      <x:c r="E47" s="9"/>
+      <x:c r="F47" s="9"/>
     </x:row>
     <x:row r="48">
-      <x:c r="A48" s="13"/>
+      <x:c r="A48" s="12"/>
+      <x:c r="B48" s="9"/>
+      <x:c r="C48" s="9"/>
+      <x:c r="D48" s="9"/>
+      <x:c r="E48" s="9"/>
+      <x:c r="F48" s="9"/>
     </x:row>
     <x:row r="49">
-      <x:c r="A49" s="13"/>
+      <x:c r="A49" s="12"/>
+      <x:c r="B49" s="9"/>
+      <x:c r="C49" s="9"/>
+      <x:c r="D49" s="9"/>
+      <x:c r="E49" s="9"/>
+      <x:c r="F49" s="9"/>
     </x:row>
     <x:row r="50">
-      <x:c r="A50" s="13"/>
+      <x:c r="A50" s="12"/>
+      <x:c r="B50" s="9"/>
+      <x:c r="C50" s="9"/>
+      <x:c r="D50" s="9"/>
+      <x:c r="E50" s="9"/>
+      <x:c r="F50" s="9"/>
     </x:row>
     <x:row r="51">
-      <x:c r="A51" s="13"/>
+      <x:c r="A51" s="12"/>
+      <x:c r="B51" s="9"/>
+      <x:c r="C51" s="9"/>
+      <x:c r="D51" s="9"/>
+      <x:c r="E51" s="9"/>
+      <x:c r="F51" s="9"/>
     </x:row>
     <x:row r="52">
-      <x:c r="A52" s="13"/>
+      <x:c r="A52" s="12"/>
+      <x:c r="B52" s="9"/>
+      <x:c r="C52" s="9"/>
+      <x:c r="D52" s="9"/>
+      <x:c r="E52" s="9"/>
+      <x:c r="F52" s="9"/>
     </x:row>
     <x:row r="53">
-      <x:c r="A53" s="13"/>
+      <x:c r="A53" s="12"/>
+      <x:c r="B53" s="9"/>
+      <x:c r="C53" s="9"/>
+      <x:c r="D53" s="9"/>
+      <x:c r="E53" s="9"/>
+      <x:c r="F53" s="9"/>
     </x:row>
     <x:row r="54">
-      <x:c r="A54" s="13"/>
+      <x:c r="A54" s="12"/>
+      <x:c r="B54" s="9"/>
+      <x:c r="C54" s="9"/>
+      <x:c r="D54" s="9"/>
+      <x:c r="E54" s="9"/>
+      <x:c r="F54" s="9"/>
     </x:row>
     <x:row r="55">
-      <x:c r="A55" s="13"/>
+      <x:c r="A55" s="12"/>
+      <x:c r="B55" s="9"/>
+      <x:c r="C55" s="9"/>
+      <x:c r="D55" s="9"/>
+      <x:c r="E55" s="9"/>
+      <x:c r="F55" s="9"/>
     </x:row>
     <x:row r="56">
-      <x:c r="A56" s="13"/>
+      <x:c r="A56" s="12"/>
+      <x:c r="B56" s="9"/>
+      <x:c r="C56" s="9"/>
+      <x:c r="D56" s="9"/>
+      <x:c r="E56" s="9"/>
+      <x:c r="F56" s="9"/>
     </x:row>
     <x:row r="57">
-      <x:c r="A57" s="13"/>
+      <x:c r="A57" s="12"/>
+      <x:c r="B57" s="9"/>
+      <x:c r="C57" s="9"/>
+      <x:c r="D57" s="9"/>
+      <x:c r="E57" s="9"/>
+      <x:c r="F57" s="9"/>
     </x:row>
     <x:row r="58">
-      <x:c r="A58" s="13"/>
+      <x:c r="A58" s="12"/>
+      <x:c r="B58" s="9"/>
+      <x:c r="C58" s="9"/>
+      <x:c r="D58" s="9"/>
+      <x:c r="E58" s="9"/>
+      <x:c r="F58" s="9"/>
     </x:row>
     <x:row r="59">
-      <x:c r="A59" s="13"/>
+      <x:c r="A59" s="12"/>
+      <x:c r="B59" s="9"/>
+      <x:c r="C59" s="9"/>
+      <x:c r="D59" s="9"/>
+      <x:c r="E59" s="9"/>
+      <x:c r="F59" s="9"/>
     </x:row>
     <x:row r="60">
-      <x:c r="A60" s="13"/>
+      <x:c r="A60" s="12"/>
+      <x:c r="B60" s="9"/>
+      <x:c r="C60" s="9"/>
+      <x:c r="D60" s="9"/>
+      <x:c r="E60" s="9"/>
+      <x:c r="F60" s="9"/>
     </x:row>
     <x:row r="61">
-      <x:c r="A61" s="13"/>
+      <x:c r="A61" s="12"/>
+      <x:c r="B61" s="9"/>
+      <x:c r="C61" s="9"/>
+      <x:c r="D61" s="9"/>
+      <x:c r="E61" s="9"/>
+      <x:c r="F61" s="9"/>
     </x:row>
     <x:row r="62">
-      <x:c r="A62" s="13"/>
+      <x:c r="A62" s="12"/>
+      <x:c r="B62" s="9"/>
+      <x:c r="C62" s="9"/>
+      <x:c r="D62" s="9"/>
+      <x:c r="E62" s="9"/>
+      <x:c r="F62" s="9"/>
     </x:row>
     <x:row r="63">
-      <x:c r="A63" s="13"/>
+      <x:c r="A63" s="12"/>
+      <x:c r="B63" s="9"/>
+      <x:c r="C63" s="9"/>
+      <x:c r="D63" s="9"/>
+      <x:c r="E63" s="9"/>
+      <x:c r="F63" s="9"/>
     </x:row>
     <x:row r="64">
-      <x:c r="A64" s="13"/>
+      <x:c r="A64" s="12"/>
+      <x:c r="B64" s="9"/>
+      <x:c r="C64" s="9"/>
+      <x:c r="D64" s="9"/>
+      <x:c r="E64" s="9"/>
+      <x:c r="F64" s="9"/>
     </x:row>
     <x:row r="65">
-      <x:c r="A65" s="13"/>
+      <x:c r="A65" s="12"/>
+      <x:c r="B65" s="9"/>
+      <x:c r="C65" s="9"/>
+      <x:c r="D65" s="9"/>
+      <x:c r="E65" s="9"/>
+      <x:c r="F65" s="9"/>
     </x:row>
     <x:row r="66">
-      <x:c r="A66" s="13"/>
+      <x:c r="A66" s="12"/>
+      <x:c r="B66" s="9"/>
+      <x:c r="C66" s="9"/>
+      <x:c r="D66" s="9"/>
+      <x:c r="E66" s="9"/>
+      <x:c r="F66" s="9"/>
     </x:row>
     <x:row r="67">
-      <x:c r="A67" s="13"/>
+      <x:c r="A67" s="12"/>
+      <x:c r="B67" s="9"/>
+      <x:c r="C67" s="9"/>
+      <x:c r="D67" s="9"/>
+      <x:c r="E67" s="9"/>
+      <x:c r="F67" s="9"/>
     </x:row>
     <x:row r="68">
-      <x:c r="A68" s="13"/>
+      <x:c r="A68" s="12"/>
+      <x:c r="B68" s="9"/>
+      <x:c r="C68" s="9"/>
+      <x:c r="D68" s="9"/>
+      <x:c r="E68" s="9"/>
+      <x:c r="F68" s="9"/>
     </x:row>
     <x:row r="69">
-      <x:c r="A69" s="13"/>
+      <x:c r="A69" s="12"/>
+      <x:c r="B69" s="9"/>
+      <x:c r="C69" s="9"/>
+      <x:c r="D69" s="9"/>
+      <x:c r="E69" s="9"/>
+      <x:c r="F69" s="9"/>
     </x:row>
     <x:row r="70">
-      <x:c r="A70" s="13"/>
+      <x:c r="A70" s="12"/>
+      <x:c r="B70" s="9"/>
+      <x:c r="C70" s="9"/>
+      <x:c r="D70" s="9"/>
+      <x:c r="E70" s="9"/>
+      <x:c r="F70" s="9"/>
     </x:row>
     <x:row r="71">
-      <x:c r="A71" s="13"/>
+      <x:c r="A71" s="12"/>
+      <x:c r="B71" s="9"/>
+      <x:c r="C71" s="9"/>
+      <x:c r="D71" s="9"/>
+      <x:c r="E71" s="9"/>
+      <x:c r="F71" s="9"/>
     </x:row>
     <x:row r="72">
-      <x:c r="A72" s="13"/>
+      <x:c r="A72" s="12"/>
+      <x:c r="B72" s="9"/>
+      <x:c r="C72" s="9"/>
+      <x:c r="D72" s="9"/>
+      <x:c r="E72" s="9"/>
+      <x:c r="F72" s="9"/>
     </x:row>
     <x:row r="73">
-      <x:c r="A73" s="13"/>
+      <x:c r="A73" s="12"/>
+      <x:c r="B73" s="9"/>
+      <x:c r="C73" s="9"/>
+      <x:c r="D73" s="9"/>
+      <x:c r="E73" s="9"/>
+      <x:c r="F73" s="9"/>
     </x:row>
     <x:row r="74">
-      <x:c r="A74" s="13"/>
+      <x:c r="A74" s="12"/>
+      <x:c r="B74" s="9"/>
+      <x:c r="C74" s="9"/>
+      <x:c r="D74" s="9"/>
+      <x:c r="E74" s="9"/>
+      <x:c r="F74" s="9"/>
     </x:row>
     <x:row r="75">
-      <x:c r="A75" s="13"/>
+      <x:c r="A75" s="12"/>
+      <x:c r="B75" s="9"/>
+      <x:c r="C75" s="9"/>
+      <x:c r="D75" s="9"/>
+      <x:c r="E75" s="9"/>
+      <x:c r="F75" s="9"/>
     </x:row>
     <x:row r="76">
-      <x:c r="A76" s="13"/>
+      <x:c r="A76" s="12"/>
+      <x:c r="B76" s="9"/>
+      <x:c r="C76" s="9"/>
+      <x:c r="D76" s="9"/>
+      <x:c r="E76" s="9"/>
+      <x:c r="F76" s="9"/>
     </x:row>
     <x:row r="77">
-      <x:c r="A77" s="13"/>
+      <x:c r="A77" s="12"/>
+      <x:c r="B77" s="9"/>
+      <x:c r="C77" s="9"/>
+      <x:c r="D77" s="9"/>
+      <x:c r="E77" s="9"/>
+      <x:c r="F77" s="9"/>
     </x:row>
     <x:row r="78">
-      <x:c r="A78" s="13"/>
+      <x:c r="A78" s="12"/>
+      <x:c r="B78" s="9"/>
+      <x:c r="C78" s="9"/>
+      <x:c r="D78" s="9"/>
+      <x:c r="E78" s="9"/>
+      <x:c r="F78" s="9"/>
     </x:row>
     <x:row r="79">
-      <x:c r="A79" s="13"/>
+      <x:c r="A79" s="12"/>
+      <x:c r="B79" s="9"/>
+      <x:c r="C79" s="9"/>
+      <x:c r="D79" s="9"/>
+      <x:c r="E79" s="9"/>
+      <x:c r="F79" s="9"/>
     </x:row>
     <x:row r="80">
-      <x:c r="A80" s="13"/>
+      <x:c r="A80" s="12"/>
+      <x:c r="B80" s="9"/>
+      <x:c r="C80" s="9"/>
+      <x:c r="D80" s="9"/>
+      <x:c r="E80" s="9"/>
+      <x:c r="F80" s="9"/>
     </x:row>
     <x:row r="81">
-      <x:c r="A81" s="13"/>
+      <x:c r="A81" s="12"/>
+      <x:c r="B81" s="9"/>
+      <x:c r="C81" s="9"/>
+      <x:c r="D81" s="9"/>
+      <x:c r="E81" s="9"/>
+      <x:c r="F81" s="9"/>
     </x:row>
     <x:row r="82">
-      <x:c r="A82" s="13"/>
+      <x:c r="A82" s="12"/>
+      <x:c r="B82" s="9"/>
+      <x:c r="C82" s="9"/>
+      <x:c r="D82" s="9"/>
+      <x:c r="E82" s="9"/>
+      <x:c r="F82" s="9"/>
     </x:row>
     <x:row r="83">
-      <x:c r="A83" s="13"/>
+      <x:c r="A83" s="12"/>
+      <x:c r="B83" s="9"/>
+      <x:c r="C83" s="9"/>
+      <x:c r="D83" s="9"/>
+      <x:c r="E83" s="9"/>
+      <x:c r="F83" s="9"/>
     </x:row>
     <x:row r="84">
-      <x:c r="A84" s="13"/>
+      <x:c r="A84" s="12"/>
+      <x:c r="B84" s="9"/>
+      <x:c r="C84" s="9"/>
+      <x:c r="D84" s="9"/>
+      <x:c r="E84" s="9"/>
+      <x:c r="F84" s="9"/>
     </x:row>
     <x:row r="85">
-      <x:c r="A85" s="13"/>
+      <x:c r="A85" s="12"/>
+      <x:c r="B85" s="9"/>
+      <x:c r="C85" s="9"/>
+      <x:c r="D85" s="9"/>
+      <x:c r="E85" s="9"/>
+      <x:c r="F85" s="9"/>
     </x:row>
     <x:row r="86">
-      <x:c r="A86" s="13"/>
+      <x:c r="A86" s="12"/>
+      <x:c r="B86" s="9"/>
+      <x:c r="C86" s="9"/>
+      <x:c r="D86" s="9"/>
+      <x:c r="E86" s="9"/>
+      <x:c r="F86" s="9"/>
     </x:row>
     <x:row r="87">
-      <x:c r="A87" s="13"/>
+      <x:c r="A87" s="12"/>
+      <x:c r="B87" s="9"/>
+      <x:c r="C87" s="9"/>
+      <x:c r="D87" s="9"/>
+      <x:c r="E87" s="9"/>
+      <x:c r="F87" s="9"/>
     </x:row>
     <x:row r="88">
-      <x:c r="A88" s="13"/>
+      <x:c r="A88" s="12"/>
+      <x:c r="B88" s="9"/>
+      <x:c r="C88" s="9"/>
+      <x:c r="D88" s="9"/>
+      <x:c r="E88" s="9"/>
+      <x:c r="F88" s="9"/>
     </x:row>
     <x:row r="89">
-      <x:c r="A89" s="13"/>
+      <x:c r="A89" s="12"/>
+      <x:c r="B89" s="9"/>
+      <x:c r="C89" s="9"/>
+      <x:c r="D89" s="9"/>
+      <x:c r="E89" s="9"/>
+      <x:c r="F89" s="9"/>
     </x:row>
     <x:row r="90">
-      <x:c r="A90" s="13"/>
+      <x:c r="A90" s="12"/>
+      <x:c r="B90" s="9"/>
+      <x:c r="C90" s="9"/>
+      <x:c r="D90" s="9"/>
+      <x:c r="E90" s="9"/>
+      <x:c r="F90" s="9"/>
     </x:row>
     <x:row r="91">
-      <x:c r="A91" s="13"/>
+      <x:c r="A91" s="12"/>
+      <x:c r="B91" s="9"/>
+      <x:c r="C91" s="9"/>
+      <x:c r="D91" s="9"/>
+      <x:c r="E91" s="9"/>
+      <x:c r="F91" s="9"/>
     </x:row>
     <x:row r="92">
-      <x:c r="A92" s="13"/>
+      <x:c r="A92" s="12"/>
+      <x:c r="B92" s="9"/>
+      <x:c r="C92" s="9"/>
+      <x:c r="D92" s="9"/>
+      <x:c r="E92" s="9"/>
+      <x:c r="F92" s="9"/>
     </x:row>
     <x:row r="93">
-      <x:c r="A93" s="13"/>
+      <x:c r="A93" s="12"/>
+      <x:c r="B93" s="9"/>
+      <x:c r="C93" s="9"/>
+      <x:c r="D93" s="9"/>
+      <x:c r="E93" s="9"/>
+      <x:c r="F93" s="9"/>
     </x:row>
     <x:row r="94">
-      <x:c r="A94" s="13"/>
+      <x:c r="A94" s="12"/>
+      <x:c r="B94" s="9"/>
+      <x:c r="C94" s="9"/>
+      <x:c r="D94" s="9"/>
+      <x:c r="E94" s="9"/>
+      <x:c r="F94" s="9"/>
     </x:row>
     <x:row r="95">
-      <x:c r="A95" s="13"/>
+      <x:c r="A95" s="12"/>
+      <x:c r="B95" s="9"/>
+      <x:c r="C95" s="9"/>
+      <x:c r="D95" s="9"/>
+      <x:c r="E95" s="9"/>
+      <x:c r="F95" s="9"/>
     </x:row>
     <x:row r="96">
-      <x:c r="A96" s="13"/>
+      <x:c r="A96" s="12"/>
+      <x:c r="B96" s="9"/>
+      <x:c r="C96" s="9"/>
+      <x:c r="D96" s="9"/>
+      <x:c r="E96" s="9"/>
+      <x:c r="F96" s="9"/>
     </x:row>
     <x:row r="97">
-      <x:c r="A97" s="13"/>
+      <x:c r="A97" s="12"/>
+      <x:c r="B97" s="9"/>
+      <x:c r="C97" s="9"/>
+      <x:c r="D97" s="9"/>
+      <x:c r="E97" s="9"/>
+      <x:c r="F97" s="9"/>
     </x:row>
     <x:row r="98">
-      <x:c r="A98" s="13"/>
+      <x:c r="A98" s="12"/>
+      <x:c r="B98" s="9"/>
+      <x:c r="C98" s="9"/>
+      <x:c r="D98" s="9"/>
+      <x:c r="E98" s="9"/>
+      <x:c r="F98" s="9"/>
     </x:row>
     <x:row r="99">
-      <x:c r="A99" s="13"/>
+      <x:c r="A99" s="12"/>
+      <x:c r="B99" s="9"/>
+      <x:c r="C99" s="9"/>
+      <x:c r="D99" s="9"/>
+      <x:c r="E99" s="9"/>
+      <x:c r="F99" s="9"/>
     </x:row>
     <x:row r="100">
-      <x:c r="A100" s="13"/>
+      <x:c r="A100" s="12"/>
+      <x:c r="B100" s="9"/>
+      <x:c r="C100" s="9"/>
+      <x:c r="D100" s="9"/>
+      <x:c r="E100" s="9"/>
+      <x:c r="F100" s="9"/>
     </x:row>
     <x:row r="101">
-      <x:c r="A101" s="13"/>
+      <x:c r="A101" s="12"/>
+      <x:c r="B101" s="9"/>
+      <x:c r="C101" s="9"/>
+      <x:c r="D101" s="9"/>
+      <x:c r="E101" s="9"/>
+      <x:c r="F101" s="9"/>
     </x:row>
     <x:row r="102">
-      <x:c r="A102" s="13"/>
+      <x:c r="A102" s="12"/>
+      <x:c r="B102" s="9"/>
+      <x:c r="C102" s="9"/>
+      <x:c r="D102" s="9"/>
+      <x:c r="E102" s="9"/>
+      <x:c r="F102" s="9"/>
     </x:row>
     <x:row r="103">
-      <x:c r="A103" s="13"/>
+      <x:c r="A103" s="12"/>
+      <x:c r="B103" s="9"/>
+      <x:c r="C103" s="9"/>
+      <x:c r="D103" s="9"/>
+      <x:c r="E103" s="9"/>
+      <x:c r="F103" s="9"/>
     </x:row>
     <x:row r="104">
-      <x:c r="A104" s="13"/>
+      <x:c r="A104" s="12"/>
+      <x:c r="B104" s="9"/>
+      <x:c r="C104" s="9"/>
+      <x:c r="D104" s="9"/>
+      <x:c r="E104" s="9"/>
+      <x:c r="F104" s="9"/>
     </x:row>
     <x:row r="105">
-      <x:c r="A105" s="13"/>
+      <x:c r="A105" s="12"/>
+      <x:c r="B105" s="9"/>
+      <x:c r="C105" s="9"/>
+      <x:c r="D105" s="9"/>
+      <x:c r="E105" s="9"/>
+      <x:c r="F105" s="9"/>
     </x:row>
     <x:row r="106">
-      <x:c r="A106" s="13"/>
+      <x:c r="A106" s="12"/>
+      <x:c r="B106" s="9"/>
+      <x:c r="C106" s="9"/>
+      <x:c r="D106" s="9"/>
+      <x:c r="E106" s="9"/>
+      <x:c r="F106" s="9"/>
     </x:row>
     <x:row r="107">
-      <x:c r="A107" s="13"/>
+      <x:c r="A107" s="12"/>
+      <x:c r="B107" s="9"/>
+      <x:c r="C107" s="9"/>
+      <x:c r="D107" s="9"/>
+      <x:c r="E107" s="9"/>
+      <x:c r="F107" s="9"/>
     </x:row>
     <x:row r="108">
-      <x:c r="A108" s="13"/>
+      <x:c r="A108" s="12"/>
+      <x:c r="B108" s="9"/>
+      <x:c r="C108" s="9"/>
+      <x:c r="D108" s="9"/>
+      <x:c r="E108" s="9"/>
+      <x:c r="F108" s="9"/>
     </x:row>
     <x:row r="109">
-      <x:c r="A109" s="13"/>
+      <x:c r="A109" s="12"/>
+      <x:c r="B109" s="9"/>
+      <x:c r="C109" s="9"/>
+      <x:c r="D109" s="9"/>
+      <x:c r="E109" s="9"/>
+      <x:c r="F109" s="9"/>
     </x:row>
     <x:row r="110">
-      <x:c r="A110" s="13"/>
+      <x:c r="A110" s="12"/>
+      <x:c r="B110" s="9"/>
+      <x:c r="C110" s="9"/>
+      <x:c r="D110" s="9"/>
+      <x:c r="E110" s="9"/>
+      <x:c r="F110" s="9"/>
     </x:row>
     <x:row r="111">
-      <x:c r="A111" s="13"/>
+      <x:c r="A111" s="12"/>
+      <x:c r="B111" s="9"/>
+      <x:c r="C111" s="9"/>
+      <x:c r="D111" s="9"/>
+      <x:c r="E111" s="9"/>
+      <x:c r="F111" s="9"/>
     </x:row>
     <x:row r="112">
-      <x:c r="A112" s="13"/>
+      <x:c r="A112" s="12"/>
+      <x:c r="B112" s="9"/>
+      <x:c r="C112" s="9"/>
+      <x:c r="D112" s="9"/>
+      <x:c r="E112" s="9"/>
+      <x:c r="F112" s="9"/>
     </x:row>
     <x:row r="113">
-      <x:c r="A113" s="13"/>
+      <x:c r="A113" s="12"/>
+      <x:c r="B113" s="9"/>
+      <x:c r="C113" s="9"/>
+      <x:c r="D113" s="9"/>
+      <x:c r="E113" s="9"/>
+      <x:c r="F113" s="9"/>
     </x:row>
     <x:row r="114">
-      <x:c r="A114" s="13"/>
+      <x:c r="A114" s="12"/>
+      <x:c r="B114" s="9"/>
+      <x:c r="C114" s="9"/>
+      <x:c r="D114" s="9"/>
+      <x:c r="E114" s="9"/>
+      <x:c r="F114" s="9"/>
     </x:row>
     <x:row r="115">
-      <x:c r="A115" s="13"/>
+      <x:c r="A115" s="12"/>
+      <x:c r="B115" s="9"/>
+      <x:c r="C115" s="9"/>
+      <x:c r="D115" s="9"/>
+      <x:c r="E115" s="9"/>
+      <x:c r="F115" s="9"/>
     </x:row>
     <x:row r="116">
-      <x:c r="A116" s="13"/>
+      <x:c r="A116" s="12"/>
+      <x:c r="B116" s="9"/>
+      <x:c r="C116" s="9"/>
+      <x:c r="D116" s="9"/>
+      <x:c r="E116" s="9"/>
+      <x:c r="F116" s="9"/>
     </x:row>
     <x:row r="117">
-      <x:c r="A117" s="13"/>
+      <x:c r="A117" s="12"/>
+      <x:c r="B117" s="9"/>
+      <x:c r="C117" s="9"/>
+      <x:c r="D117" s="9"/>
+      <x:c r="E117" s="9"/>
+      <x:c r="F117" s="9"/>
     </x:row>
     <x:row r="118">
-      <x:c r="A118" s="13"/>
+      <x:c r="A118" s="12"/>
+      <x:c r="B118" s="9"/>
+      <x:c r="C118" s="9"/>
+      <x:c r="D118" s="9"/>
+      <x:c r="E118" s="9"/>
+      <x:c r="F118" s="9"/>
     </x:row>
     <x:row r="119">
-      <x:c r="A119" s="13"/>
+      <x:c r="A119" s="12"/>
+      <x:c r="B119" s="9"/>
+      <x:c r="C119" s="9"/>
+      <x:c r="D119" s="9"/>
+      <x:c r="E119" s="9"/>
+      <x:c r="F119" s="9"/>
     </x:row>
     <x:row r="120">
-      <x:c r="A120" s="13"/>
+      <x:c r="A120" s="12"/>
+      <x:c r="B120" s="9"/>
+      <x:c r="C120" s="9"/>
+      <x:c r="D120" s="9"/>
+      <x:c r="E120" s="9"/>
+      <x:c r="F120" s="9"/>
     </x:row>
     <x:row r="121">
-      <x:c r="A121" s="13"/>
+      <x:c r="A121" s="12"/>
+      <x:c r="B121" s="9"/>
+      <x:c r="C121" s="9"/>
+      <x:c r="D121" s="9"/>
+      <x:c r="E121" s="9"/>
+      <x:c r="F121" s="9"/>
     </x:row>
     <x:row r="122">
-      <x:c r="A122" s="13"/>
+      <x:c r="A122" s="12"/>
+      <x:c r="B122" s="9"/>
+      <x:c r="C122" s="9"/>
+      <x:c r="D122" s="9"/>
+      <x:c r="E122" s="9"/>
+      <x:c r="F122" s="9"/>
     </x:row>
     <x:row r="123">
-      <x:c r="A123" s="13"/>
+      <x:c r="A123" s="12"/>
+      <x:c r="B123" s="9"/>
+      <x:c r="C123" s="9"/>
+      <x:c r="D123" s="9"/>
+      <x:c r="E123" s="9"/>
+      <x:c r="F123" s="9"/>
     </x:row>
     <x:row r="124">
-      <x:c r="A124" s="13"/>
+      <x:c r="A124" s="12"/>
+      <x:c r="B124" s="9"/>
+      <x:c r="C124" s="9"/>
+      <x:c r="D124" s="9"/>
+      <x:c r="E124" s="9"/>
+      <x:c r="F124" s="9"/>
     </x:row>
     <x:row r="125">
-      <x:c r="A125" s="13"/>
+      <x:c r="A125" s="12"/>
+      <x:c r="B125" s="9"/>
+      <x:c r="C125" s="9"/>
+      <x:c r="D125" s="9"/>
+      <x:c r="E125" s="9"/>
+      <x:c r="F125" s="9"/>
     </x:row>
     <x:row r="126">
-      <x:c r="A126" s="13"/>
+      <x:c r="A126" s="12"/>
+      <x:c r="B126" s="9"/>
+      <x:c r="C126" s="9"/>
+      <x:c r="D126" s="9"/>
+      <x:c r="E126" s="9"/>
+      <x:c r="F126" s="9"/>
     </x:row>
     <x:row r="127">
-      <x:c r="A127" s="13"/>
+      <x:c r="A127" s="12"/>
+      <x:c r="B127" s="9"/>
+      <x:c r="C127" s="9"/>
+      <x:c r="D127" s="9"/>
+      <x:c r="E127" s="9"/>
+      <x:c r="F127" s="9"/>
     </x:row>
     <x:row r="128">
-      <x:c r="A128" s="13"/>
+      <x:c r="A128" s="12"/>
+      <x:c r="B128" s="9"/>
+      <x:c r="C128" s="9"/>
+      <x:c r="D128" s="9"/>
+      <x:c r="E128" s="9"/>
+      <x:c r="F128" s="9"/>
     </x:row>
     <x:row r="129">
-      <x:c r="A129" s="13"/>
+      <x:c r="A129" s="12"/>
+      <x:c r="B129" s="9"/>
+      <x:c r="C129" s="9"/>
+      <x:c r="D129" s="9"/>
+      <x:c r="E129" s="9"/>
+      <x:c r="F129" s="9"/>
     </x:row>
     <x:row r="130">
-      <x:c r="A130" s="13"/>
+      <x:c r="A130" s="12"/>
+      <x:c r="B130" s="9"/>
+      <x:c r="C130" s="9"/>
+      <x:c r="D130" s="9"/>
+      <x:c r="E130" s="9"/>
+      <x:c r="F130" s="9"/>
     </x:row>
     <x:row r="131">
-      <x:c r="A131" s="13"/>
+      <x:c r="A131" s="12"/>
+      <x:c r="B131" s="9"/>
+      <x:c r="C131" s="9"/>
+      <x:c r="D131" s="9"/>
+      <x:c r="E131" s="9"/>
+      <x:c r="F131" s="9"/>
     </x:row>
     <x:row r="132">
-      <x:c r="A132" s="13"/>
+      <x:c r="A132" s="12"/>
+      <x:c r="B132" s="9"/>
+      <x:c r="C132" s="9"/>
+      <x:c r="D132" s="9"/>
+      <x:c r="E132" s="9"/>
+      <x:c r="F132" s="9"/>
     </x:row>
     <x:row r="133">
-      <x:c r="A133" s="13"/>
+      <x:c r="A133" s="12"/>
+      <x:c r="B133" s="9"/>
+      <x:c r="C133" s="9"/>
+      <x:c r="D133" s="9"/>
+      <x:c r="E133" s="9"/>
+      <x:c r="F133" s="9"/>
     </x:row>
     <x:row r="134">
-      <x:c r="A134" s="13"/>
+      <x:c r="A134" s="12"/>
+      <x:c r="B134" s="9"/>
+      <x:c r="C134" s="9"/>
+      <x:c r="D134" s="9"/>
+      <x:c r="E134" s="9"/>
+      <x:c r="F134" s="9"/>
     </x:row>
     <x:row r="135">
-      <x:c r="A135" s="13"/>
+      <x:c r="A135" s="12"/>
+      <x:c r="B135" s="9"/>
+      <x:c r="C135" s="9"/>
+      <x:c r="D135" s="9"/>
+      <x:c r="E135" s="9"/>
+      <x:c r="F135" s="9"/>
     </x:row>
     <x:row r="136">
-      <x:c r="A136" s="13"/>
+      <x:c r="A136" s="12"/>
+      <x:c r="B136" s="9"/>
+      <x:c r="C136" s="9"/>
+      <x:c r="D136" s="9"/>
+      <x:c r="E136" s="9"/>
+      <x:c r="F136" s="9"/>
     </x:row>
     <x:row r="137">
-      <x:c r="A137" s="13"/>
+      <x:c r="A137" s="12"/>
+      <x:c r="B137" s="9"/>
+      <x:c r="C137" s="9"/>
+      <x:c r="D137" s="9"/>
+      <x:c r="E137" s="9"/>
+      <x:c r="F137" s="9"/>
     </x:row>
     <x:row r="138">
-      <x:c r="A138" s="13"/>
+      <x:c r="A138" s="12"/>
+      <x:c r="B138" s="9"/>
+      <x:c r="C138" s="9"/>
+      <x:c r="D138" s="9"/>
+      <x:c r="E138" s="9"/>
+      <x:c r="F138" s="9"/>
     </x:row>
     <x:row r="139">
-      <x:c r="A139" s="13"/>
+      <x:c r="A139" s="12"/>
+      <x:c r="B139" s="9"/>
+      <x:c r="C139" s="9"/>
+      <x:c r="D139" s="9"/>
+      <x:c r="E139" s="9"/>
+      <x:c r="F139" s="9"/>
     </x:row>
     <x:row r="140">
-      <x:c r="A140" s="13"/>
+      <x:c r="A140" s="12"/>
+      <x:c r="B140" s="9"/>
+      <x:c r="C140" s="9"/>
+      <x:c r="D140" s="9"/>
+      <x:c r="E140" s="9"/>
+      <x:c r="F140" s="9"/>
     </x:row>
     <x:row r="141">
-      <x:c r="A141" s="13"/>
+      <x:c r="A141" s="12"/>
+      <x:c r="B141" s="9"/>
+      <x:c r="C141" s="9"/>
+      <x:c r="D141" s="9"/>
+      <x:c r="E141" s="9"/>
+      <x:c r="F141" s="9"/>
     </x:row>
     <x:row r="142">
-      <x:c r="A142" s="13"/>
+      <x:c r="A142" s="12"/>
+      <x:c r="B142" s="9"/>
+      <x:c r="C142" s="9"/>
+      <x:c r="D142" s="9"/>
+      <x:c r="E142" s="9"/>
+      <x:c r="F142" s="9"/>
     </x:row>
     <x:row r="143">
-      <x:c r="A143" s="13"/>
+      <x:c r="A143" s="12"/>
+      <x:c r="B143" s="9"/>
+      <x:c r="C143" s="9"/>
+      <x:c r="D143" s="9"/>
+      <x:c r="E143" s="9"/>
+      <x:c r="F143" s="9"/>
     </x:row>
     <x:row r="144">
-      <x:c r="A144" s="13"/>
+      <x:c r="A144" s="12"/>
+      <x:c r="B144" s="9"/>
+      <x:c r="C144" s="9"/>
+      <x:c r="D144" s="9"/>
+      <x:c r="E144" s="9"/>
+      <x:c r="F144" s="9"/>
     </x:row>
     <x:row r="145">
-      <x:c r="A145" s="13"/>
+      <x:c r="A145" s="12"/>
+      <x:c r="B145" s="9"/>
+      <x:c r="C145" s="9"/>
+      <x:c r="D145" s="9"/>
+      <x:c r="E145" s="9"/>
+      <x:c r="F145" s="9"/>
     </x:row>
     <x:row r="146">
-      <x:c r="A146" s="13"/>
+      <x:c r="A146" s="12"/>
+      <x:c r="B146" s="9"/>
+      <x:c r="C146" s="9"/>
+      <x:c r="D146" s="9"/>
+      <x:c r="E146" s="9"/>
+      <x:c r="F146" s="9"/>
     </x:row>
     <x:row r="147">
-      <x:c r="A147" s="13"/>
+      <x:c r="A147" s="12"/>
+      <x:c r="B147" s="9"/>
+      <x:c r="C147" s="9"/>
+      <x:c r="D147" s="9"/>
+      <x:c r="E147" s="9"/>
+      <x:c r="F147" s="9"/>
     </x:row>
     <x:row r="148">
-      <x:c r="A148" s="13"/>
+      <x:c r="A148" s="12"/>
+      <x:c r="B148" s="9"/>
+      <x:c r="C148" s="9"/>
+      <x:c r="D148" s="9"/>
+      <x:c r="E148" s="9"/>
+      <x:c r="F148" s="9"/>
     </x:row>
     <x:row r="149">
-      <x:c r="A149" s="13"/>
+      <x:c r="A149" s="12"/>
+      <x:c r="B149" s="9"/>
+      <x:c r="C149" s="9"/>
+      <x:c r="D149" s="9"/>
+      <x:c r="E149" s="9"/>
+      <x:c r="F149" s="9"/>
     </x:row>
     <x:row r="150">
-      <x:c r="A150" s="13"/>
+      <x:c r="A150" s="12"/>
+      <x:c r="B150" s="9"/>
+      <x:c r="C150" s="9"/>
+      <x:c r="D150" s="9"/>
+      <x:c r="E150" s="9"/>
+      <x:c r="F150" s="9"/>
     </x:row>
     <x:row r="151">
-      <x:c r="A151" s="13"/>
+      <x:c r="A151" s="12"/>
+      <x:c r="B151" s="9"/>
+      <x:c r="C151" s="9"/>
+      <x:c r="D151" s="9"/>
+      <x:c r="E151" s="9"/>
+      <x:c r="F151" s="9"/>
     </x:row>
     <x:row r="152">
-      <x:c r="A152" s="13"/>
+      <x:c r="A152" s="12"/>
+      <x:c r="B152" s="9"/>
+      <x:c r="C152" s="9"/>
+      <x:c r="D152" s="9"/>
+      <x:c r="E152" s="9"/>
+      <x:c r="F152" s="9"/>
     </x:row>
     <x:row r="153">
-      <x:c r="A153" s="13"/>
+      <x:c r="A153" s="12"/>
+      <x:c r="B153" s="9"/>
+      <x:c r="C153" s="9"/>
+      <x:c r="D153" s="9"/>
+      <x:c r="E153" s="9"/>
+      <x:c r="F153" s="9"/>
     </x:row>
     <x:row r="154">
-      <x:c r="A154" s="13"/>
+      <x:c r="A154" s="12"/>
+      <x:c r="B154" s="9"/>
+      <x:c r="C154" s="9"/>
+      <x:c r="D154" s="9"/>
+      <x:c r="E154" s="9"/>
+      <x:c r="F154" s="9"/>
     </x:row>
     <x:row r="155">
-      <x:c r="A155" s="13"/>
+      <x:c r="A155" s="12"/>
+      <x:c r="B155" s="9"/>
+      <x:c r="C155" s="9"/>
+      <x:c r="D155" s="9"/>
+      <x:c r="E155" s="9"/>
+      <x:c r="F155" s="9"/>
     </x:row>
     <x:row r="156">
-      <x:c r="A156" s="13"/>
+      <x:c r="A156" s="12"/>
+      <x:c r="B156" s="9"/>
+      <x:c r="C156" s="9"/>
+      <x:c r="D156" s="9"/>
+      <x:c r="E156" s="9"/>
+      <x:c r="F156" s="9"/>
     </x:row>
     <x:row r="157">
-      <x:c r="A157" s="13"/>
+      <x:c r="A157" s="12"/>
+      <x:c r="B157" s="9"/>
+      <x:c r="C157" s="9"/>
+      <x:c r="D157" s="9"/>
+      <x:c r="E157" s="9"/>
+      <x:c r="F157" s="9"/>
     </x:row>
     <x:row r="158">
-      <x:c r="A158" s="13"/>
+      <x:c r="A158" s="12"/>
+      <x:c r="B158" s="9"/>
+      <x:c r="C158" s="9"/>
+      <x:c r="D158" s="9"/>
+      <x:c r="E158" s="9"/>
+      <x:c r="F158" s="9"/>
     </x:row>
     <x:row r="159">
-      <x:c r="A159" s="13"/>
+      <x:c r="A159" s="12"/>
+      <x:c r="B159" s="9"/>
+      <x:c r="C159" s="9"/>
+      <x:c r="D159" s="9"/>
+      <x:c r="E159" s="9"/>
+      <x:c r="F159" s="9"/>
     </x:row>
     <x:row r="160">
-      <x:c r="A160" s="13"/>
+      <x:c r="A160" s="12"/>
+      <x:c r="B160" s="9"/>
+      <x:c r="C160" s="9"/>
+      <x:c r="D160" s="9"/>
+      <x:c r="E160" s="9"/>
+      <x:c r="F160" s="9"/>
     </x:row>
     <x:row r="161">
-      <x:c r="A161" s="13"/>
+      <x:c r="A161" s="12"/>
+      <x:c r="B161" s="9"/>
+      <x:c r="C161" s="9"/>
+      <x:c r="D161" s="9"/>
+      <x:c r="E161" s="9"/>
+      <x:c r="F161" s="9"/>
     </x:row>
     <x:row r="162">
-      <x:c r="A162" s="13"/>
+      <x:c r="A162" s="12"/>
+      <x:c r="B162" s="9"/>
+      <x:c r="C162" s="9"/>
+      <x:c r="D162" s="9"/>
+      <x:c r="E162" s="9"/>
+      <x:c r="F162" s="9"/>
     </x:row>
     <x:row r="163">
-      <x:c r="A163" s="13"/>
+      <x:c r="A163" s="12"/>
+      <x:c r="B163" s="9"/>
+      <x:c r="C163" s="9"/>
+      <x:c r="D163" s="9"/>
+      <x:c r="E163" s="9"/>
+      <x:c r="F163" s="9"/>
     </x:row>
     <x:row r="164">
-      <x:c r="A164" s="13"/>
+      <x:c r="A164" s="12"/>
+      <x:c r="B164" s="9"/>
+      <x:c r="C164" s="9"/>
+      <x:c r="D164" s="9"/>
+      <x:c r="E164" s="9"/>
+      <x:c r="F164" s="9"/>
     </x:row>
     <x:row r="165">
-      <x:c r="A165" s="13"/>
+      <x:c r="A165" s="12"/>
+      <x:c r="B165" s="9"/>
+      <x:c r="C165" s="9"/>
+      <x:c r="D165" s="9"/>
+      <x:c r="E165" s="9"/>
+      <x:c r="F165" s="9"/>
     </x:row>
     <x:row r="166">
-      <x:c r="A166" s="13"/>
+      <x:c r="A166" s="12"/>
+      <x:c r="B166" s="9"/>
+      <x:c r="C166" s="9"/>
+      <x:c r="D166" s="9"/>
+      <x:c r="E166" s="9"/>
+      <x:c r="F166" s="9"/>
     </x:row>
     <x:row r="167">
-      <x:c r="A167" s="13"/>
+      <x:c r="A167" s="12"/>
+      <x:c r="B167" s="9"/>
+      <x:c r="C167" s="9"/>
+      <x:c r="D167" s="9"/>
+      <x:c r="E167" s="9"/>
+      <x:c r="F167" s="9"/>
     </x:row>
     <x:row r="168">
-      <x:c r="A168" s="13"/>
+      <x:c r="A168" s="12"/>
+      <x:c r="B168" s="9"/>
+      <x:c r="C168" s="9"/>
+      <x:c r="D168" s="9"/>
+      <x:c r="E168" s="9"/>
+      <x:c r="F168" s="9"/>
     </x:row>
     <x:row r="169">
-      <x:c r="A169" s="13"/>
+      <x:c r="A169" s="12"/>
+      <x:c r="B169" s="9"/>
+      <x:c r="C169" s="9"/>
+      <x:c r="D169" s="9"/>
+      <x:c r="E169" s="9"/>
+      <x:c r="F169" s="9"/>
     </x:row>
     <x:row r="170">
-      <x:c r="A170" s="13"/>
+      <x:c r="A170" s="12"/>
+      <x:c r="B170" s="9"/>
+      <x:c r="C170" s="9"/>
+      <x:c r="D170" s="9"/>
+      <x:c r="E170" s="9"/>
+      <x:c r="F170" s="9"/>
     </x:row>
     <x:row r="171">
-      <x:c r="A171" s="13"/>
+      <x:c r="A171" s="12"/>
+      <x:c r="B171" s="9"/>
+      <x:c r="C171" s="9"/>
+      <x:c r="D171" s="9"/>
+      <x:c r="E171" s="9"/>
+      <x:c r="F171" s="9"/>
     </x:row>
     <x:row r="172">
-      <x:c r="A172" s="13"/>
+      <x:c r="A172" s="12"/>
+      <x:c r="B172" s="9"/>
+      <x:c r="C172" s="9"/>
+      <x:c r="D172" s="9"/>
+      <x:c r="E172" s="9"/>
+      <x:c r="F172" s="9"/>
     </x:row>
     <x:row r="173">
-      <x:c r="A173" s="13"/>
+      <x:c r="A173" s="12"/>
+      <x:c r="B173" s="9"/>
+      <x:c r="C173" s="9"/>
+      <x:c r="D173" s="9"/>
+      <x:c r="E173" s="9"/>
+      <x:c r="F173" s="9"/>
     </x:row>
     <x:row r="174">
-      <x:c r="A174" s="13"/>
+      <x:c r="A174" s="12"/>
+      <x:c r="B174" s="9"/>
+      <x:c r="C174" s="9"/>
+      <x:c r="D174" s="9"/>
+      <x:c r="E174" s="9"/>
+      <x:c r="F174" s="9"/>
     </x:row>
     <x:row r="175">
-      <x:c r="A175" s="13"/>
+      <x:c r="A175" s="12"/>
+      <x:c r="B175" s="9"/>
+      <x:c r="C175" s="9"/>
+      <x:c r="D175" s="9"/>
+      <x:c r="E175" s="9"/>
+      <x:c r="F175" s="9"/>
     </x:row>
     <x:row r="176">
-      <x:c r="A176" s="13"/>
+      <x:c r="A176" s="12"/>
+      <x:c r="B176" s="9"/>
+      <x:c r="C176" s="9"/>
+      <x:c r="D176" s="9"/>
+      <x:c r="E176" s="9"/>
+      <x:c r="F176" s="9"/>
     </x:row>
     <x:row r="177">
-      <x:c r="A177" s="13"/>
+      <x:c r="A177" s="12"/>
+      <x:c r="B177" s="9"/>
+      <x:c r="C177" s="9"/>
+      <x:c r="D177" s="9"/>
+      <x:c r="E177" s="9"/>
+      <x:c r="F177" s="9"/>
     </x:row>
     <x:row r="178">
-      <x:c r="A178" s="13"/>
+      <x:c r="A178" s="12"/>
+      <x:c r="B178" s="9"/>
+      <x:c r="C178" s="9"/>
+      <x:c r="D178" s="9"/>
+      <x:c r="E178" s="9"/>
+      <x:c r="F178" s="9"/>
     </x:row>
     <x:row r="179">
-      <x:c r="A179" s="13"/>
+      <x:c r="A179" s="12"/>
+      <x:c r="B179" s="9"/>
+      <x:c r="C179" s="9"/>
+      <x:c r="D179" s="9"/>
+      <x:c r="E179" s="9"/>
+      <x:c r="F179" s="9"/>
     </x:row>
     <x:row r="180">
-      <x:c r="A180" s="13"/>
+      <x:c r="A180" s="12"/>
+      <x:c r="B180" s="9"/>
+      <x:c r="C180" s="9"/>
+      <x:c r="D180" s="9"/>
+      <x:c r="E180" s="9"/>
+      <x:c r="F180" s="9"/>
     </x:row>
     <x:row r="181">
-      <x:c r="A181" s="13"/>
+      <x:c r="A181" s="12"/>
+      <x:c r="B181" s="9"/>
+      <x:c r="C181" s="9"/>
+      <x:c r="D181" s="9"/>
+      <x:c r="E181" s="9"/>
+      <x:c r="F181" s="9"/>
     </x:row>
     <x:row r="182">
-      <x:c r="A182" s="13"/>
+      <x:c r="A182" s="12"/>
+      <x:c r="B182" s="9"/>
+      <x:c r="C182" s="9"/>
+      <x:c r="D182" s="9"/>
+      <x:c r="E182" s="9"/>
+      <x:c r="F182" s="9"/>
     </x:row>
     <x:row r="183">
-      <x:c r="A183" s="13"/>
+      <x:c r="A183" s="12"/>
+      <x:c r="B183" s="9"/>
+      <x:c r="C183" s="9"/>
+      <x:c r="D183" s="9"/>
+      <x:c r="E183" s="9"/>
+      <x:c r="F183" s="9"/>
     </x:row>
     <x:row r="184">
-      <x:c r="A184" s="13"/>
+      <x:c r="A184" s="12"/>
+      <x:c r="B184" s="9"/>
+      <x:c r="C184" s="9"/>
+      <x:c r="D184" s="9"/>
+      <x:c r="E184" s="9"/>
+      <x:c r="F184" s="9"/>
     </x:row>
     <x:row r="185">
-      <x:c r="A185" s="13"/>
+      <x:c r="A185" s="12"/>
+      <x:c r="B185" s="9"/>
+      <x:c r="C185" s="9"/>
+      <x:c r="D185" s="9"/>
+      <x:c r="E185" s="9"/>
+      <x:c r="F185" s="9"/>
     </x:row>
     <x:row r="186">
-      <x:c r="A186" s="13"/>
+      <x:c r="A186" s="12"/>
+      <x:c r="B186" s="9"/>
+      <x:c r="C186" s="9"/>
+      <x:c r="D186" s="9"/>
+      <x:c r="E186" s="9"/>
+      <x:c r="F186" s="9"/>
     </x:row>
     <x:row r="187">
-      <x:c r="A187" s="13"/>
+      <x:c r="A187" s="12"/>
+      <x:c r="B187" s="9"/>
+      <x:c r="C187" s="9"/>
+      <x:c r="D187" s="9"/>
+      <x:c r="E187" s="9"/>
+      <x:c r="F187" s="9"/>
     </x:row>
     <x:row r="188">
-      <x:c r="A188" s="13"/>
+      <x:c r="A188" s="12"/>
+      <x:c r="B188" s="9"/>
+      <x:c r="C188" s="9"/>
+      <x:c r="D188" s="9"/>
+      <x:c r="E188" s="9"/>
+      <x:c r="F188" s="9"/>
     </x:row>
     <x:row r="189">
-      <x:c r="A189" s="13"/>
+      <x:c r="A189" s="12"/>
+      <x:c r="B189" s="9"/>
+      <x:c r="C189" s="9"/>
+      <x:c r="D189" s="9"/>
+      <x:c r="E189" s="9"/>
+      <x:c r="F189" s="9"/>
     </x:row>
     <x:row r="190">
-      <x:c r="A190" s="13"/>
+      <x:c r="A190" s="12"/>
+      <x:c r="B190" s="9"/>
+      <x:c r="C190" s="9"/>
+      <x:c r="D190" s="9"/>
+      <x:c r="E190" s="9"/>
+      <x:c r="F190" s="9"/>
     </x:row>
     <x:row r="191">
-      <x:c r="A191" s="13"/>
+      <x:c r="A191" s="12"/>
+      <x:c r="B191" s="9"/>
+      <x:c r="C191" s="9"/>
+      <x:c r="D191" s="9"/>
+      <x:c r="E191" s="9"/>
+      <x:c r="F191" s="9"/>
     </x:row>
     <x:row r="192">
-      <x:c r="A192" s="13"/>
+      <x:c r="A192" s="12"/>
+      <x:c r="B192" s="9"/>
+      <x:c r="C192" s="9"/>
+      <x:c r="D192" s="9"/>
+      <x:c r="E192" s="9"/>
+      <x:c r="F192" s="9"/>
     </x:row>
     <x:row r="193">
-      <x:c r="A193" s="13"/>
+      <x:c r="A193" s="12"/>
+      <x:c r="B193" s="9"/>
+      <x:c r="C193" s="9"/>
+      <x:c r="D193" s="9"/>
+      <x:c r="E193" s="9"/>
+      <x:c r="F193" s="9"/>
     </x:row>
     <x:row r="194">
-      <x:c r="A194" s="13"/>
+      <x:c r="A194" s="12"/>
+      <x:c r="B194" s="9"/>
+      <x:c r="C194" s="9"/>
+      <x:c r="D194" s="9"/>
+      <x:c r="E194" s="9"/>
+      <x:c r="F194" s="9"/>
     </x:row>
     <x:row r="195">
-      <x:c r="A195" s="13"/>
+      <x:c r="A195" s="12"/>
+      <x:c r="B195" s="9"/>
+      <x:c r="C195" s="9"/>
+      <x:c r="D195" s="9"/>
+      <x:c r="E195" s="9"/>
+      <x:c r="F195" s="9"/>
     </x:row>
     <x:row r="196">
-      <x:c r="A196" s="13"/>
+      <x:c r="A196" s="12"/>
+      <x:c r="B196" s="9"/>
+      <x:c r="C196" s="9"/>
+      <x:c r="D196" s="9"/>
+      <x:c r="E196" s="9"/>
+      <x:c r="F196" s="9"/>
     </x:row>
     <x:row r="197">
-      <x:c r="A197" s="13"/>
+      <x:c r="A197" s="12"/>
+      <x:c r="B197" s="9"/>
+      <x:c r="C197" s="9"/>
+      <x:c r="D197" s="9"/>
+      <x:c r="E197" s="9"/>
+      <x:c r="F197" s="9"/>
     </x:row>
     <x:row r="198">
-      <x:c r="A198" s="13"/>
+      <x:c r="A198" s="12"/>
+      <x:c r="B198" s="9"/>
+      <x:c r="C198" s="9"/>
+      <x:c r="D198" s="9"/>
+      <x:c r="E198" s="9"/>
+      <x:c r="F198" s="9"/>
     </x:row>
     <x:row r="199">
-      <x:c r="A199" s="13"/>
+      <x:c r="A199" s="12"/>
+      <x:c r="B199" s="9"/>
+      <x:c r="C199" s="9"/>
+      <x:c r="D199" s="9"/>
+      <x:c r="E199" s="9"/>
+      <x:c r="F199" s="9"/>
     </x:row>
     <x:row r="200">
-      <x:c r="A200" s="13"/>
+      <x:c r="A200" s="12"/>
+      <x:c r="B200" s="9"/>
+      <x:c r="C200" s="9"/>
+      <x:c r="D200" s="9"/>
+      <x:c r="E200" s="9"/>
+      <x:c r="F200" s="9"/>
+    </x:row>
+    <x:row r="201">
+      <x:c r="A201" s="12"/>
+      <x:c r="B201" s="9"/>
+      <x:c r="C201" s="9"/>
+      <x:c r="D201" s="9"/>
+      <x:c r="E201" s="9"/>
+      <x:c r="F201" s="9"/>
+    </x:row>
+    <x:row r="202">
+      <x:c r="A202" s="12"/>
+      <x:c r="B202" s="9"/>
+      <x:c r="C202" s="9"/>
+      <x:c r="D202" s="9"/>
+      <x:c r="E202" s="9"/>
+      <x:c r="F202" s="9"/>
+    </x:row>
+    <x:row r="203">
+      <x:c r="A203" s="12"/>
+      <x:c r="B203" s="9"/>
+      <x:c r="C203" s="9"/>
+      <x:c r="D203" s="9"/>
+      <x:c r="E203" s="9"/>
+      <x:c r="F203" s="9"/>
+    </x:row>
+    <x:row r="204">
+      <x:c r="A204" s="12"/>
+      <x:c r="B204" s="9"/>
+      <x:c r="C204" s="9"/>
+      <x:c r="D204" s="9"/>
+      <x:c r="E204" s="9"/>
+      <x:c r="F204" s="9"/>
+    </x:row>
+    <x:row r="205">
+      <x:c r="A205" s="12"/>
+      <x:c r="B205" s="9"/>
+      <x:c r="C205" s="9"/>
+      <x:c r="D205" s="9"/>
+      <x:c r="E205" s="9"/>
+      <x:c r="F205" s="9"/>
+    </x:row>
+    <x:row r="206">
+      <x:c r="A206" s="12"/>
+      <x:c r="B206" s="9"/>
+      <x:c r="C206" s="9"/>
+      <x:c r="D206" s="9"/>
+      <x:c r="E206" s="9"/>
+      <x:c r="F206" s="9"/>
+    </x:row>
+    <x:row r="207">
+      <x:c r="A207" s="12"/>
+      <x:c r="B207" s="9"/>
+      <x:c r="C207" s="9"/>
+      <x:c r="D207" s="9"/>
+      <x:c r="E207" s="9"/>
+      <x:c r="F207" s="9"/>
+    </x:row>
+    <x:row r="208">
+      <x:c r="A208" s="12"/>
+      <x:c r="B208" s="9"/>
+      <x:c r="C208" s="9"/>
+      <x:c r="D208" s="9"/>
+      <x:c r="E208" s="9"/>
+      <x:c r="F208" s="9"/>
+    </x:row>
+    <x:row r="209">
+      <x:c r="A209" s="12"/>
+      <x:c r="B209" s="9"/>
+      <x:c r="C209" s="9"/>
+      <x:c r="D209" s="9"/>
+      <x:c r="E209" s="9"/>
+      <x:c r="F209" s="9"/>
+    </x:row>
+    <x:row r="210">
+      <x:c r="A210" s="12"/>
+      <x:c r="B210" s="9"/>
+      <x:c r="C210" s="9"/>
+      <x:c r="D210" s="9"/>
+      <x:c r="E210" s="9"/>
+      <x:c r="F210" s="9"/>
+    </x:row>
+    <x:row r="211">
+      <x:c r="A211" s="12"/>
+      <x:c r="B211" s="9"/>
+      <x:c r="C211" s="9"/>
+      <x:c r="D211" s="9"/>
+      <x:c r="E211" s="9"/>
+      <x:c r="F211" s="9"/>
+    </x:row>
+    <x:row r="212">
+      <x:c r="A212" s="12"/>
+      <x:c r="B212" s="9"/>
+      <x:c r="C212" s="9"/>
+      <x:c r="D212" s="9"/>
+      <x:c r="E212" s="9"/>
+      <x:c r="F212" s="9"/>
+    </x:row>
+    <x:row r="213">
+      <x:c r="A213" s="12"/>
+      <x:c r="B213" s="9"/>
+      <x:c r="C213" s="9"/>
+      <x:c r="D213" s="9"/>
+      <x:c r="E213" s="9"/>
+      <x:c r="F213" s="9"/>
+    </x:row>
+    <x:row r="214">
+      <x:c r="A214" s="12"/>
+      <x:c r="B214" s="9"/>
+      <x:c r="C214" s="9"/>
+      <x:c r="D214" s="9"/>
+      <x:c r="E214" s="9"/>
+      <x:c r="F214" s="9"/>
+    </x:row>
+    <x:row r="215">
+      <x:c r="A215" s="12"/>
+      <x:c r="B215" s="9"/>
+      <x:c r="C215" s="9"/>
+      <x:c r="D215" s="9"/>
+      <x:c r="E215" s="9"/>
+      <x:c r="F215" s="9"/>
+    </x:row>
+    <x:row r="216">
+      <x:c r="A216" s="12"/>
+      <x:c r="B216" s="9"/>
+      <x:c r="C216" s="9"/>
+      <x:c r="D216" s="9"/>
+      <x:c r="E216" s="9"/>
+      <x:c r="F216" s="9"/>
+    </x:row>
+    <x:row r="217">
+      <x:c r="A217" s="12"/>
+      <x:c r="B217" s="9"/>
+      <x:c r="C217" s="9"/>
+      <x:c r="D217" s="9"/>
+      <x:c r="E217" s="9"/>
+      <x:c r="F217" s="9"/>
+    </x:row>
+    <x:row r="218">
+      <x:c r="A218" s="12"/>
+      <x:c r="B218" s="9"/>
+      <x:c r="C218" s="9"/>
+      <x:c r="D218" s="9"/>
+      <x:c r="E218" s="9"/>
+      <x:c r="F218" s="9"/>
+    </x:row>
+    <x:row r="219">
+      <x:c r="A219" s="12"/>
+      <x:c r="B219" s="9"/>
+      <x:c r="C219" s="9"/>
+      <x:c r="D219" s="9"/>
+      <x:c r="E219" s="9"/>
+      <x:c r="F219" s="9"/>
+    </x:row>
+    <x:row r="220">
+      <x:c r="A220" s="12"/>
+      <x:c r="B220" s="9"/>
+      <x:c r="C220" s="9"/>
+      <x:c r="D220" s="9"/>
+      <x:c r="E220" s="9"/>
+      <x:c r="F220" s="9"/>
+    </x:row>
+    <x:row r="221">
+      <x:c r="A221" s="12"/>
+      <x:c r="B221" s="9"/>
+      <x:c r="C221" s="9"/>
+      <x:c r="D221" s="9"/>
+      <x:c r="E221" s="9"/>
+      <x:c r="F221" s="9"/>
+    </x:row>
+    <x:row r="222">
+      <x:c r="A222" s="12"/>
+      <x:c r="B222" s="9"/>
+      <x:c r="C222" s="9"/>
+      <x:c r="D222" s="9"/>
+      <x:c r="E222" s="9"/>
+      <x:c r="F222" s="9"/>
+    </x:row>
+    <x:row r="223">
+      <x:c r="A223" s="12"/>
+      <x:c r="B223" s="9"/>
+      <x:c r="C223" s="9"/>
+      <x:c r="D223" s="9"/>
+      <x:c r="E223" s="9"/>
+      <x:c r="F223" s="9"/>
+    </x:row>
+    <x:row r="224">
+      <x:c r="A224" s="12"/>
+      <x:c r="B224" s="9"/>
+      <x:c r="C224" s="9"/>
+      <x:c r="D224" s="9"/>
+      <x:c r="E224" s="9"/>
+      <x:c r="F224" s="9"/>
+    </x:row>
+    <x:row r="225">
+      <x:c r="A225" s="12"/>
+      <x:c r="B225" s="9"/>
+      <x:c r="C225" s="9"/>
+      <x:c r="D225" s="9"/>
+      <x:c r="E225" s="9"/>
+      <x:c r="F225" s="9"/>
+    </x:row>
+    <x:row r="226">
+      <x:c r="A226" s="12"/>
+      <x:c r="B226" s="9"/>
+      <x:c r="C226" s="9"/>
+      <x:c r="D226" s="9"/>
+      <x:c r="E226" s="9"/>
+      <x:c r="F226" s="9"/>
+    </x:row>
+    <x:row r="227">
+      <x:c r="A227" s="12"/>
+      <x:c r="B227" s="9"/>
+      <x:c r="C227" s="9"/>
+      <x:c r="D227" s="9"/>
+      <x:c r="E227" s="9"/>
+      <x:c r="F227" s="9"/>
+    </x:row>
+    <x:row r="228">
+      <x:c r="A228" s="12"/>
+      <x:c r="B228" s="9"/>
+      <x:c r="C228" s="9"/>
+      <x:c r="D228" s="9"/>
+      <x:c r="E228" s="9"/>
+      <x:c r="F228" s="9"/>
+    </x:row>
+    <x:row r="229">
+      <x:c r="A229" s="12"/>
+      <x:c r="B229" s="9"/>
+      <x:c r="C229" s="9"/>
+      <x:c r="D229" s="9"/>
+      <x:c r="E229" s="9"/>
+      <x:c r="F229" s="9"/>
+    </x:row>
+    <x:row r="230">
+      <x:c r="A230" s="12"/>
+      <x:c r="B230" s="9"/>
+      <x:c r="C230" s="9"/>
+      <x:c r="D230" s="9"/>
+      <x:c r="E230" s="9"/>
+      <x:c r="F230" s="9"/>
+    </x:row>
+    <x:row r="231">
+      <x:c r="A231" s="12"/>
+      <x:c r="B231" s="9"/>
+      <x:c r="C231" s="9"/>
+      <x:c r="D231" s="9"/>
+      <x:c r="E231" s="9"/>
+      <x:c r="F231" s="9"/>
+    </x:row>
+    <x:row r="232">
+      <x:c r="A232" s="12"/>
+      <x:c r="B232" s="9"/>
+      <x:c r="C232" s="9"/>
+      <x:c r="D232" s="9"/>
+      <x:c r="E232" s="9"/>
+      <x:c r="F232" s="9"/>
+    </x:row>
+    <x:row r="233">
+      <x:c r="A233" s="12"/>
+      <x:c r="B233" s="9"/>
+      <x:c r="C233" s="9"/>
+      <x:c r="D233" s="9"/>
+      <x:c r="E233" s="9"/>
+      <x:c r="F233" s="9"/>
+    </x:row>
+    <x:row r="234">
+      <x:c r="A234" s="12"/>
+      <x:c r="B234" s="9"/>
+      <x:c r="C234" s="9"/>
+      <x:c r="D234" s="9"/>
+      <x:c r="E234" s="9"/>
+      <x:c r="F234" s="9"/>
+    </x:row>
+    <x:row r="235">
+      <x:c r="A235" s="12"/>
+      <x:c r="B235" s="9"/>
+      <x:c r="C235" s="9"/>
+      <x:c r="D235" s="9"/>
+      <x:c r="E235" s="9"/>
+      <x:c r="F235" s="9"/>
+    </x:row>
+    <x:row r="236">
+      <x:c r="A236" s="12"/>
+      <x:c r="B236" s="9"/>
+      <x:c r="C236" s="9"/>
+      <x:c r="D236" s="9"/>
+      <x:c r="E236" s="9"/>
+      <x:c r="F236" s="9"/>
+    </x:row>
+    <x:row r="237">
+      <x:c r="A237" s="12"/>
+      <x:c r="B237" s="9"/>
+      <x:c r="C237" s="9"/>
+      <x:c r="D237" s="9"/>
+      <x:c r="E237" s="9"/>
+      <x:c r="F237" s="9"/>
+    </x:row>
+    <x:row r="238">
+      <x:c r="A238" s="12"/>
+      <x:c r="B238" s="9"/>
+      <x:c r="C238" s="9"/>
+      <x:c r="D238" s="9"/>
+      <x:c r="E238" s="9"/>
+      <x:c r="F238" s="9"/>
+    </x:row>
+    <x:row r="239">
+      <x:c r="A239" s="12"/>
+      <x:c r="B239" s="9"/>
+      <x:c r="C239" s="9"/>
+      <x:c r="D239" s="9"/>
+      <x:c r="E239" s="9"/>
+      <x:c r="F239" s="9"/>
+    </x:row>
+    <x:row r="240">
+      <x:c r="A240" s="12"/>
+      <x:c r="B240" s="9"/>
+      <x:c r="C240" s="9"/>
+      <x:c r="D240" s="9"/>
+      <x:c r="E240" s="9"/>
+      <x:c r="F240" s="9"/>
+    </x:row>
+    <x:row r="241">
+      <x:c r="A241" s="12"/>
+      <x:c r="B241" s="9"/>
+      <x:c r="C241" s="9"/>
+      <x:c r="D241" s="9"/>
+      <x:c r="E241" s="9"/>
+      <x:c r="F241" s="9"/>
+    </x:row>
+    <x:row r="242">
+      <x:c r="A242" s="12"/>
+      <x:c r="B242" s="9"/>
+      <x:c r="C242" s="9"/>
+      <x:c r="D242" s="9"/>
+      <x:c r="E242" s="9"/>
+      <x:c r="F242" s="9"/>
+    </x:row>
+    <x:row r="243">
+      <x:c r="A243" s="12"/>
+      <x:c r="B243" s="9"/>
+      <x:c r="C243" s="9"/>
+      <x:c r="D243" s="9"/>
+      <x:c r="E243" s="9"/>
+      <x:c r="F243" s="9"/>
+    </x:row>
+    <x:row r="244">
+      <x:c r="A244" s="12"/>
+      <x:c r="B244" s="9"/>
+      <x:c r="C244" s="9"/>
+      <x:c r="D244" s="9"/>
+      <x:c r="E244" s="9"/>
+      <x:c r="F244" s="9"/>
+    </x:row>
+    <x:row r="245">
+      <x:c r="A245" s="12"/>
+      <x:c r="B245" s="9"/>
+      <x:c r="C245" s="9"/>
+      <x:c r="D245" s="9"/>
+      <x:c r="E245" s="9"/>
+      <x:c r="F245" s="9"/>
+    </x:row>
+    <x:row r="246">
+      <x:c r="A246" s="12"/>
+      <x:c r="B246" s="9"/>
+      <x:c r="C246" s="9"/>
+      <x:c r="D246" s="9"/>
+      <x:c r="E246" s="9"/>
+      <x:c r="F246" s="9"/>
+    </x:row>
+    <x:row r="247">
+      <x:c r="A247" s="12"/>
+      <x:c r="B247" s="9"/>
+      <x:c r="C247" s="9"/>
+      <x:c r="D247" s="9"/>
+      <x:c r="E247" s="9"/>
+      <x:c r="F247" s="9"/>
+    </x:row>
+    <x:row r="248">
+      <x:c r="A248" s="12"/>
+      <x:c r="B248" s="9"/>
+      <x:c r="C248" s="9"/>
+      <x:c r="D248" s="9"/>
+      <x:c r="E248" s="9"/>
+      <x:c r="F248" s="9"/>
+    </x:row>
+    <x:row r="249">
+      <x:c r="A249" s="12"/>
+      <x:c r="B249" s="9"/>
+      <x:c r="C249" s="9"/>
+      <x:c r="D249" s="9"/>
+      <x:c r="E249" s="9"/>
+      <x:c r="F249" s="9"/>
+    </x:row>
+    <x:row r="250">
+      <x:c r="A250" s="12"/>
+      <x:c r="B250" s="9"/>
+      <x:c r="C250" s="9"/>
+      <x:c r="D250" s="9"/>
+      <x:c r="E250" s="9"/>
+      <x:c r="F250" s="9"/>
+    </x:row>
+    <x:row r="251">
+      <x:c r="A251" s="12"/>
+      <x:c r="B251" s="9"/>
+      <x:c r="C251" s="9"/>
+      <x:c r="D251" s="9"/>
+      <x:c r="E251" s="9"/>
+      <x:c r="F251" s="9"/>
+    </x:row>
+    <x:row r="252">
+      <x:c r="A252" s="12"/>
+      <x:c r="B252" s="9"/>
+      <x:c r="C252" s="9"/>
+      <x:c r="D252" s="9"/>
+      <x:c r="E252" s="9"/>
+      <x:c r="F252" s="9"/>
+    </x:row>
+    <x:row r="253">
+      <x:c r="A253" s="12"/>
+      <x:c r="B253" s="9"/>
+      <x:c r="C253" s="9"/>
+      <x:c r="D253" s="9"/>
+      <x:c r="E253" s="9"/>
+      <x:c r="F253" s="9"/>
+    </x:row>
+    <x:row r="254">
+      <x:c r="A254" s="12"/>
+      <x:c r="B254" s="9"/>
+      <x:c r="C254" s="9"/>
+      <x:c r="D254" s="9"/>
+      <x:c r="E254" s="9"/>
+      <x:c r="F254" s="9"/>
+    </x:row>
+    <x:row r="255">
+      <x:c r="A255" s="12"/>
+      <x:c r="B255" s="9"/>
+      <x:c r="C255" s="9"/>
+      <x:c r="D255" s="9"/>
+      <x:c r="E255" s="9"/>
+      <x:c r="F255" s="9"/>
+    </x:row>
+    <x:row r="256">
+      <x:c r="A256" s="12"/>
+      <x:c r="B256" s="9"/>
+      <x:c r="C256" s="9"/>
+      <x:c r="D256" s="9"/>
+      <x:c r="E256" s="9"/>
+      <x:c r="F256" s="9"/>
+    </x:row>
+    <x:row r="257">
+      <x:c r="A257" s="12"/>
+      <x:c r="B257" s="9"/>
+      <x:c r="C257" s="9"/>
+      <x:c r="D257" s="9"/>
+      <x:c r="E257" s="9"/>
+      <x:c r="F257" s="9"/>
+    </x:row>
+    <x:row r="258">
+      <x:c r="A258" s="12"/>
+      <x:c r="B258" s="9"/>
+      <x:c r="C258" s="9"/>
+      <x:c r="D258" s="9"/>
+      <x:c r="E258" s="9"/>
+      <x:c r="F258" s="9"/>
+    </x:row>
+    <x:row r="259">
+      <x:c r="A259" s="12"/>
+      <x:c r="B259" s="9"/>
+      <x:c r="C259" s="9"/>
+      <x:c r="D259" s="9"/>
+      <x:c r="E259" s="9"/>
+      <x:c r="F259" s="9"/>
+    </x:row>
+    <x:row r="260">
+      <x:c r="A260" s="12"/>
+      <x:c r="B260" s="9"/>
+      <x:c r="C260" s="9"/>
+      <x:c r="D260" s="9"/>
+      <x:c r="E260" s="9"/>
+      <x:c r="F260" s="9"/>
+    </x:row>
+    <x:row r="261">
+      <x:c r="A261" s="12"/>
+      <x:c r="B261" s="9"/>
+      <x:c r="C261" s="9"/>
+      <x:c r="D261" s="9"/>
+      <x:c r="E261" s="9"/>
+      <x:c r="F261" s="9"/>
+    </x:row>
+    <x:row r="262">
+      <x:c r="A262" s="12"/>
+      <x:c r="B262" s="9"/>
+      <x:c r="C262" s="9"/>
+      <x:c r="D262" s="9"/>
+      <x:c r="E262" s="9"/>
+      <x:c r="F262" s="9"/>
+    </x:row>
+    <x:row r="263">
+      <x:c r="A263" s="12"/>
+      <x:c r="B263" s="9"/>
+      <x:c r="C263" s="9"/>
+      <x:c r="D263" s="9"/>
+      <x:c r="E263" s="9"/>
+      <x:c r="F263" s="9"/>
+    </x:row>
+    <x:row r="264">
+      <x:c r="A264" s="12"/>
+      <x:c r="B264" s="9"/>
+      <x:c r="C264" s="9"/>
+      <x:c r="D264" s="9"/>
+      <x:c r="E264" s="9"/>
+      <x:c r="F264" s="9"/>
+    </x:row>
+    <x:row r="265">
+      <x:c r="A265" s="12"/>
+      <x:c r="B265" s="9"/>
+      <x:c r="C265" s="9"/>
+      <x:c r="D265" s="9"/>
+      <x:c r="E265" s="9"/>
+      <x:c r="F265" s="9"/>
+    </x:row>
+    <x:row r="266">
+      <x:c r="A266" s="12"/>
+      <x:c r="B266" s="9"/>
+      <x:c r="C266" s="9"/>
+      <x:c r="D266" s="9"/>
+      <x:c r="E266" s="9"/>
+      <x:c r="F266" s="9"/>
+    </x:row>
+    <x:row r="267">
+      <x:c r="A267" s="12"/>
+      <x:c r="B267" s="9"/>
+      <x:c r="C267" s="9"/>
+      <x:c r="D267" s="9"/>
+      <x:c r="E267" s="9"/>
+      <x:c r="F267" s="9"/>
+    </x:row>
+    <x:row r="268">
+      <x:c r="A268" s="12"/>
+      <x:c r="B268" s="9"/>
+      <x:c r="C268" s="9"/>
+      <x:c r="D268" s="9"/>
+      <x:c r="E268" s="9"/>
+      <x:c r="F268" s="9"/>
+    </x:row>
+    <x:row r="269">
+      <x:c r="A269" s="12"/>
+      <x:c r="B269" s="9"/>
+      <x:c r="C269" s="9"/>
+      <x:c r="D269" s="9"/>
+      <x:c r="E269" s="9"/>
+      <x:c r="F269" s="9"/>
+    </x:row>
+    <x:row r="270">
+      <x:c r="A270" s="12"/>
+      <x:c r="B270" s="9"/>
+      <x:c r="C270" s="9"/>
+      <x:c r="D270" s="9"/>
+      <x:c r="E270" s="9"/>
+      <x:c r="F270" s="9"/>
+    </x:row>
+    <x:row r="271">
+      <x:c r="A271" s="12"/>
+      <x:c r="B271" s="9"/>
+      <x:c r="C271" s="9"/>
+      <x:c r="D271" s="9"/>
+      <x:c r="E271" s="9"/>
+      <x:c r="F271" s="9"/>
+    </x:row>
+    <x:row r="272">
+      <x:c r="A272" s="12"/>
+      <x:c r="B272" s="9"/>
+      <x:c r="C272" s="9"/>
+      <x:c r="D272" s="9"/>
+      <x:c r="E272" s="9"/>
+      <x:c r="F272" s="9"/>
+    </x:row>
+    <x:row r="273">
+      <x:c r="A273" s="12"/>
+      <x:c r="B273" s="9"/>
+      <x:c r="C273" s="9"/>
+      <x:c r="D273" s="9"/>
+      <x:c r="E273" s="9"/>
+      <x:c r="F273" s="9"/>
+    </x:row>
+    <x:row r="274">
+      <x:c r="A274" s="12"/>
+      <x:c r="B274" s="9"/>
+      <x:c r="C274" s="9"/>
+      <x:c r="D274" s="9"/>
+      <x:c r="E274" s="9"/>
+      <x:c r="F274" s="9"/>
+    </x:row>
+    <x:row r="275">
+      <x:c r="A275" s="12"/>
+      <x:c r="B275" s="9"/>
+      <x:c r="C275" s="9"/>
+      <x:c r="D275" s="9"/>
+      <x:c r="E275" s="9"/>
+      <x:c r="F275" s="9"/>
+    </x:row>
+    <x:row r="276">
+      <x:c r="A276" s="12"/>
+      <x:c r="B276" s="9"/>
+      <x:c r="C276" s="9"/>
+      <x:c r="D276" s="9"/>
+      <x:c r="E276" s="9"/>
+      <x:c r="F276" s="9"/>
+    </x:row>
+    <x:row r="277">
+      <x:c r="A277" s="12"/>
+      <x:c r="B277" s="9"/>
+      <x:c r="C277" s="9"/>
+      <x:c r="D277" s="9"/>
+      <x:c r="E277" s="9"/>
+      <x:c r="F277" s="9"/>
+    </x:row>
+    <x:row r="278">
+      <x:c r="A278" s="12"/>
+      <x:c r="B278" s="9"/>
+      <x:c r="C278" s="9"/>
+      <x:c r="D278" s="9"/>
+      <x:c r="E278" s="9"/>
+      <x:c r="F278" s="9"/>
+    </x:row>
+    <x:row r="279">
+      <x:c r="A279" s="12"/>
+      <x:c r="B279" s="9"/>
+      <x:c r="C279" s="9"/>
+      <x:c r="D279" s="9"/>
+      <x:c r="E279" s="9"/>
+      <x:c r="F279" s="9"/>
+    </x:row>
+    <x:row r="280">
+      <x:c r="A280" s="12"/>
+      <x:c r="B280" s="9"/>
+      <x:c r="C280" s="9"/>
+      <x:c r="D280" s="9"/>
+      <x:c r="E280" s="9"/>
+      <x:c r="F280" s="9"/>
+    </x:row>
+    <x:row r="281">
+      <x:c r="A281" s="12"/>
+      <x:c r="B281" s="9"/>
+      <x:c r="C281" s="9"/>
+      <x:c r="D281" s="9"/>
+      <x:c r="E281" s="9"/>
+      <x:c r="F281" s="9"/>
+    </x:row>
+    <x:row r="282">
+      <x:c r="A282" s="12"/>
+      <x:c r="B282" s="9"/>
+      <x:c r="C282" s="9"/>
+      <x:c r="D282" s="9"/>
+      <x:c r="E282" s="9"/>
+      <x:c r="F282" s="9"/>
+    </x:row>
+    <x:row r="283">
+      <x:c r="A283" s="12"/>
+      <x:c r="B283" s="9"/>
+      <x:c r="C283" s="9"/>
+      <x:c r="D283" s="9"/>
+      <x:c r="E283" s="9"/>
+      <x:c r="F283" s="9"/>
+    </x:row>
+    <x:row r="284">
+      <x:c r="A284" s="12"/>
+      <x:c r="B284" s="9"/>
+      <x:c r="C284" s="9"/>
+      <x:c r="D284" s="9"/>
+      <x:c r="E284" s="9"/>
+      <x:c r="F284" s="9"/>
+    </x:row>
+    <x:row r="285">
+      <x:c r="A285" s="12"/>
+      <x:c r="B285" s="9"/>
+      <x:c r="C285" s="9"/>
+      <x:c r="D285" s="9"/>
+      <x:c r="E285" s="9"/>
+      <x:c r="F285" s="9"/>
+    </x:row>
+    <x:row r="286">
+      <x:c r="A286" s="12"/>
+      <x:c r="B286" s="9"/>
+      <x:c r="C286" s="9"/>
+      <x:c r="D286" s="9"/>
+      <x:c r="E286" s="9"/>
+      <x:c r="F286" s="9"/>
+    </x:row>
+    <x:row r="287">
+      <x:c r="A287" s="12"/>
+      <x:c r="B287" s="9"/>
+      <x:c r="C287" s="9"/>
+      <x:c r="D287" s="9"/>
+      <x:c r="E287" s="9"/>
+      <x:c r="F287" s="9"/>
+    </x:row>
+    <x:row r="288">
+      <x:c r="A288" s="12"/>
+      <x:c r="B288" s="9"/>
+      <x:c r="C288" s="9"/>
+      <x:c r="D288" s="9"/>
+      <x:c r="E288" s="9"/>
+      <x:c r="F288" s="9"/>
+    </x:row>
+    <x:row r="289">
+      <x:c r="A289" s="12"/>
+      <x:c r="B289" s="9"/>
+      <x:c r="C289" s="9"/>
+      <x:c r="D289" s="9"/>
+      <x:c r="E289" s="9"/>
+      <x:c r="F289" s="9"/>
+    </x:row>
+    <x:row r="290">
+      <x:c r="A290" s="12"/>
+      <x:c r="B290" s="9"/>
+      <x:c r="C290" s="9"/>
+      <x:c r="D290" s="9"/>
+      <x:c r="E290" s="9"/>
+      <x:c r="F290" s="9"/>
+    </x:row>
+    <x:row r="291">
+      <x:c r="A291" s="12"/>
+      <x:c r="B291" s="9"/>
+      <x:c r="C291" s="9"/>
+      <x:c r="D291" s="9"/>
+      <x:c r="E291" s="9"/>
+      <x:c r="F291" s="9"/>
+    </x:row>
+    <x:row r="292">
+      <x:c r="A292" s="12"/>
+      <x:c r="B292" s="9"/>
+      <x:c r="C292" s="9"/>
+      <x:c r="D292" s="9"/>
+      <x:c r="E292" s="9"/>
+      <x:c r="F292" s="9"/>
+    </x:row>
+    <x:row r="293">
+      <x:c r="A293" s="12"/>
+      <x:c r="B293" s="9"/>
+      <x:c r="C293" s="9"/>
+      <x:c r="D293" s="9"/>
+      <x:c r="E293" s="9"/>
+      <x:c r="F293" s="9"/>
+    </x:row>
+    <x:row r="294">
+      <x:c r="A294" s="12"/>
+      <x:c r="B294" s="9"/>
+      <x:c r="C294" s="9"/>
+      <x:c r="D294" s="9"/>
+      <x:c r="E294" s="9"/>
+      <x:c r="F294" s="9"/>
+    </x:row>
+    <x:row r="295">
+      <x:c r="A295" s="12"/>
+      <x:c r="B295" s="9"/>
+      <x:c r="C295" s="9"/>
+      <x:c r="D295" s="9"/>
+      <x:c r="E295" s="9"/>
+      <x:c r="F295" s="9"/>
+    </x:row>
+    <x:row r="296">
+      <x:c r="A296" s="12"/>
+      <x:c r="B296" s="9"/>
+      <x:c r="C296" s="9"/>
+      <x:c r="D296" s="9"/>
+      <x:c r="E296" s="9"/>
+      <x:c r="F296" s="9"/>
+    </x:row>
+    <x:row r="297">
+      <x:c r="A297" s="12"/>
+      <x:c r="B297" s="9"/>
+      <x:c r="C297" s="9"/>
+      <x:c r="D297" s="9"/>
+      <x:c r="E297" s="9"/>
+      <x:c r="F297" s="9"/>
+    </x:row>
+    <x:row r="298">
+      <x:c r="A298" s="12"/>
+      <x:c r="B298" s="9"/>
+      <x:c r="C298" s="9"/>
+      <x:c r="D298" s="9"/>
+      <x:c r="E298" s="9"/>
+      <x:c r="F298" s="9"/>
+    </x:row>
+    <x:row r="299">
+      <x:c r="A299" s="12"/>
+      <x:c r="B299" s="9"/>
+      <x:c r="C299" s="9"/>
+      <x:c r="D299" s="9"/>
+      <x:c r="E299" s="9"/>
+      <x:c r="F299" s="9"/>
+    </x:row>
+    <x:row r="300">
+      <x:c r="A300" s="12"/>
+      <x:c r="B300" s="9"/>
+      <x:c r="C300" s="9"/>
+      <x:c r="D300" s="9"/>
+      <x:c r="E300" s="9"/>
+      <x:c r="F300" s="9"/>
+    </x:row>
+    <x:row r="301">
+      <x:c r="A301" s="12"/>
+      <x:c r="B301" s="9"/>
+      <x:c r="C301" s="9"/>
+      <x:c r="D301" s="9"/>
+      <x:c r="E301" s="9"/>
+      <x:c r="F301" s="9"/>
+    </x:row>
+    <x:row r="302">
+      <x:c r="A302" s="12"/>
+      <x:c r="B302" s="9"/>
+      <x:c r="C302" s="9"/>
+      <x:c r="D302" s="9"/>
+      <x:c r="E302" s="9"/>
+      <x:c r="F302" s="9"/>
+    </x:row>
+    <x:row r="303">
+      <x:c r="A303" s="12"/>
+      <x:c r="B303" s="9"/>
+      <x:c r="C303" s="9"/>
+      <x:c r="D303" s="9"/>
+      <x:c r="E303" s="9"/>
+      <x:c r="F303" s="9"/>
+    </x:row>
+    <x:row r="304">
+      <x:c r="A304" s="12"/>
+      <x:c r="B304" s="9"/>
+      <x:c r="C304" s="9"/>
+      <x:c r="D304" s="9"/>
+      <x:c r="E304" s="9"/>
+      <x:c r="F304" s="9"/>
+    </x:row>
+    <x:row r="305">
+      <x:c r="A305" s="12"/>
+      <x:c r="B305" s="9"/>
+      <x:c r="C305" s="9"/>
+      <x:c r="D305" s="9"/>
+      <x:c r="E305" s="9"/>
+      <x:c r="F305" s="9"/>
+    </x:row>
+    <x:row r="306">
+      <x:c r="A306" s="12"/>
+      <x:c r="B306" s="9"/>
+      <x:c r="C306" s="9"/>
+      <x:c r="D306" s="9"/>
+      <x:c r="E306" s="9"/>
+      <x:c r="F306" s="9"/>
+    </x:row>
+    <x:row r="307">
+      <x:c r="A307" s="12"/>
+      <x:c r="B307" s="9"/>
+      <x:c r="C307" s="9"/>
+      <x:c r="D307" s="9"/>
+      <x:c r="E307" s="9"/>
+      <x:c r="F307" s="9"/>
+    </x:row>
+    <x:row r="308">
+      <x:c r="A308" s="12"/>
+      <x:c r="B308" s="9"/>
+      <x:c r="C308" s="9"/>
+      <x:c r="D308" s="9"/>
+      <x:c r="E308" s="9"/>
+      <x:c r="F308" s="9"/>
+    </x:row>
+    <x:row r="309">
+      <x:c r="A309" s="12"/>
+      <x:c r="B309" s="9"/>
+      <x:c r="C309" s="9"/>
+      <x:c r="D309" s="9"/>
+      <x:c r="E309" s="9"/>
+      <x:c r="F309" s="9"/>
+    </x:row>
+    <x:row r="310">
+      <x:c r="A310" s="12"/>
+      <x:c r="B310" s="9"/>
+      <x:c r="C310" s="9"/>
+      <x:c r="D310" s="9"/>
+      <x:c r="E310" s="9"/>
+      <x:c r="F310" s="9"/>
+    </x:row>
+    <x:row r="311">
+      <x:c r="A311" s="12"/>
+      <x:c r="B311" s="9"/>
+      <x:c r="C311" s="9"/>
+      <x:c r="D311" s="9"/>
+      <x:c r="E311" s="9"/>
+      <x:c r="F311" s="9"/>
+    </x:row>
+    <x:row r="312">
+      <x:c r="A312" s="12"/>
+      <x:c r="B312" s="9"/>
+      <x:c r="C312" s="9"/>
+      <x:c r="D312" s="9"/>
+      <x:c r="E312" s="9"/>
+      <x:c r="F312" s="9"/>
+    </x:row>
+    <x:row r="313">
+      <x:c r="A313" s="12"/>
+      <x:c r="B313" s="9"/>
+      <x:c r="C313" s="9"/>
+      <x:c r="D313" s="9"/>
+      <x:c r="E313" s="9"/>
+      <x:c r="F313" s="9"/>
+    </x:row>
+    <x:row r="314">
+      <x:c r="A314" s="12"/>
+      <x:c r="B314" s="9"/>
+      <x:c r="C314" s="9"/>
+      <x:c r="D314" s="9"/>
+      <x:c r="E314" s="9"/>
+      <x:c r="F314" s="9"/>
+    </x:row>
+    <x:row r="315">
+      <x:c r="A315" s="12"/>
+      <x:c r="B315" s="9"/>
+      <x:c r="C315" s="9"/>
+      <x:c r="D315" s="9"/>
+      <x:c r="E315" s="9"/>
+      <x:c r="F315" s="9"/>
+    </x:row>
+    <x:row r="316">
+      <x:c r="A316" s="12"/>
+      <x:c r="B316" s="9"/>
+      <x:c r="C316" s="9"/>
+      <x:c r="D316" s="9"/>
+      <x:c r="E316" s="9"/>
+      <x:c r="F316" s="9"/>
+    </x:row>
+    <x:row r="317">
+      <x:c r="A317" s="12"/>
+      <x:c r="B317" s="9"/>
+      <x:c r="C317" s="9"/>
+      <x:c r="D317" s="9"/>
+      <x:c r="E317" s="9"/>
+      <x:c r="F317" s="9"/>
+    </x:row>
+    <x:row r="318">
+      <x:c r="A318" s="12"/>
+      <x:c r="B318" s="9"/>
+      <x:c r="C318" s="9"/>
+      <x:c r="D318" s="9"/>
+      <x:c r="E318" s="9"/>
+      <x:c r="F318" s="9"/>
+    </x:row>
+    <x:row r="319">
+      <x:c r="A319" s="12"/>
+      <x:c r="B319" s="9"/>
+      <x:c r="C319" s="9"/>
+      <x:c r="D319" s="9"/>
+      <x:c r="E319" s="9"/>
+      <x:c r="F319" s="9"/>
+    </x:row>
+    <x:row r="320">
+      <x:c r="A320" s="12"/>
+      <x:c r="B320" s="9"/>
+      <x:c r="C320" s="9"/>
+      <x:c r="D320" s="9"/>
+      <x:c r="E320" s="9"/>
+      <x:c r="F320" s="9"/>
+    </x:row>
+    <x:row r="321">
+      <x:c r="A321" s="12"/>
+      <x:c r="B321" s="9"/>
+      <x:c r="C321" s="9"/>
+      <x:c r="D321" s="9"/>
+      <x:c r="E321" s="9"/>
+      <x:c r="F321" s="9"/>
+    </x:row>
+    <x:row r="322">
+      <x:c r="A322" s="12"/>
+      <x:c r="B322" s="9"/>
+      <x:c r="C322" s="9"/>
+      <x:c r="D322" s="9"/>
+      <x:c r="E322" s="9"/>
+      <x:c r="F322" s="9"/>
+    </x:row>
+    <x:row r="323">
+      <x:c r="A323" s="12"/>
+      <x:c r="B323" s="9"/>
+      <x:c r="C323" s="9"/>
+      <x:c r="D323" s="9"/>
+      <x:c r="E323" s="9"/>
+      <x:c r="F323" s="9"/>
+    </x:row>
+    <x:row r="324">
+      <x:c r="A324" s="12"/>
+      <x:c r="B324" s="9"/>
+      <x:c r="C324" s="9"/>
+      <x:c r="D324" s="9"/>
+      <x:c r="E324" s="9"/>
+      <x:c r="F324" s="9"/>
+    </x:row>
+    <x:row r="325">
+      <x:c r="A325" s="12"/>
+      <x:c r="B325" s="9"/>
+      <x:c r="C325" s="9"/>
+      <x:c r="D325" s="9"/>
+      <x:c r="E325" s="9"/>
+      <x:c r="F325" s="9"/>
+    </x:row>
+    <x:row r="326">
+      <x:c r="A326" s="12"/>
+      <x:c r="B326" s="9"/>
+      <x:c r="C326" s="9"/>
+      <x:c r="D326" s="9"/>
+      <x:c r="E326" s="9"/>
+      <x:c r="F326" s="9"/>
+    </x:row>
+    <x:row r="327">
+      <x:c r="A327" s="12"/>
+      <x:c r="B327" s="9"/>
+      <x:c r="C327" s="9"/>
+      <x:c r="D327" s="9"/>
+      <x:c r="E327" s="9"/>
+      <x:c r="F327" s="9"/>
+    </x:row>
+    <x:row r="328">
+      <x:c r="A328" s="12"/>
+      <x:c r="B328" s="9"/>
+      <x:c r="C328" s="9"/>
+      <x:c r="D328" s="9"/>
+      <x:c r="E328" s="9"/>
+      <x:c r="F328" s="9"/>
+    </x:row>
+    <x:row r="329">
+      <x:c r="A329" s="12"/>
+      <x:c r="B329" s="9"/>
+      <x:c r="C329" s="9"/>
+      <x:c r="D329" s="9"/>
+      <x:c r="E329" s="9"/>
+      <x:c r="F329" s="9"/>
+    </x:row>
+    <x:row r="330">
+      <x:c r="A330" s="12"/>
+      <x:c r="B330" s="9"/>
+      <x:c r="C330" s="9"/>
+      <x:c r="D330" s="9"/>
+      <x:c r="E330" s="9"/>
+      <x:c r="F330" s="9"/>
+    </x:row>
+    <x:row r="331">
+      <x:c r="A331" s="12"/>
+      <x:c r="B331" s="9"/>
+      <x:c r="C331" s="9"/>
+      <x:c r="D331" s="9"/>
+      <x:c r="E331" s="9"/>
+      <x:c r="F331" s="9"/>
+    </x:row>
+    <x:row r="332">
+      <x:c r="A332" s="12"/>
+      <x:c r="B332" s="9"/>
+      <x:c r="C332" s="9"/>
+      <x:c r="D332" s="9"/>
+      <x:c r="E332" s="9"/>
+      <x:c r="F332" s="9"/>
+    </x:row>
+    <x:row r="333">
+      <x:c r="A333" s="12"/>
+      <x:c r="B333" s="9"/>
+      <x:c r="C333" s="9"/>
+      <x:c r="D333" s="9"/>
+      <x:c r="E333" s="9"/>
+      <x:c r="F333" s="9"/>
+    </x:row>
+    <x:row r="334">
+      <x:c r="A334" s="12"/>
+      <x:c r="B334" s="9"/>
+      <x:c r="C334" s="9"/>
+      <x:c r="D334" s="9"/>
+      <x:c r="E334" s="9"/>
+      <x:c r="F334" s="9"/>
+    </x:row>
+    <x:row r="335">
+      <x:c r="A335" s="12"/>
+      <x:c r="B335" s="9"/>
+      <x:c r="C335" s="9"/>
+      <x:c r="D335" s="9"/>
+      <x:c r="E335" s="9"/>
+      <x:c r="F335" s="9"/>
+    </x:row>
+    <x:row r="336">
+      <x:c r="A336" s="12"/>
+      <x:c r="B336" s="9"/>
+      <x:c r="C336" s="9"/>
+      <x:c r="D336" s="9"/>
+      <x:c r="E336" s="9"/>
+      <x:c r="F336" s="9"/>
+    </x:row>
+    <x:row r="337">
+      <x:c r="A337" s="12"/>
+      <x:c r="B337" s="9"/>
+      <x:c r="C337" s="9"/>
+      <x:c r="D337" s="9"/>
+      <x:c r="E337" s="9"/>
+      <x:c r="F337" s="9"/>
+    </x:row>
+    <x:row r="338">
+      <x:c r="A338" s="12"/>
+      <x:c r="B338" s="9"/>
+      <x:c r="C338" s="9"/>
+      <x:c r="D338" s="9"/>
+      <x:c r="E338" s="9"/>
+      <x:c r="F338" s="9"/>
+    </x:row>
+    <x:row r="339">
+      <x:c r="A339" s="12"/>
+      <x:c r="B339" s="9"/>
+      <x:c r="C339" s="9"/>
+      <x:c r="D339" s="9"/>
+      <x:c r="E339" s="9"/>
+      <x:c r="F339" s="9"/>
+    </x:row>
+    <x:row r="340">
+      <x:c r="A340" s="12"/>
+      <x:c r="B340" s="9"/>
+      <x:c r="C340" s="9"/>
+      <x:c r="D340" s="9"/>
+      <x:c r="E340" s="9"/>
+      <x:c r="F340" s="9"/>
+    </x:row>
+    <x:row r="341">
+      <x:c r="A341" s="12"/>
+      <x:c r="B341" s="9"/>
+      <x:c r="C341" s="9"/>
+      <x:c r="D341" s="9"/>
+      <x:c r="E341" s="9"/>
+      <x:c r="F341" s="9"/>
+    </x:row>
+    <x:row r="342">
+      <x:c r="A342" s="12"/>
+      <x:c r="B342" s="9"/>
+      <x:c r="C342" s="9"/>
+      <x:c r="D342" s="9"/>
+      <x:c r="E342" s="9"/>
+      <x:c r="F342" s="9"/>
+    </x:row>
+    <x:row r="343">
+      <x:c r="A343" s="12"/>
+      <x:c r="B343" s="9"/>
+      <x:c r="C343" s="9"/>
+      <x:c r="D343" s="9"/>
+      <x:c r="E343" s="9"/>
+      <x:c r="F343" s="9"/>
+    </x:row>
+    <x:row r="344">
+      <x:c r="A344" s="12"/>
+      <x:c r="B344" s="9"/>
+      <x:c r="C344" s="9"/>
+      <x:c r="D344" s="9"/>
+      <x:c r="E344" s="9"/>
+      <x:c r="F344" s="9"/>
+    </x:row>
+    <x:row r="345">
+      <x:c r="A345" s="12"/>
+      <x:c r="B345" s="9"/>
+      <x:c r="C345" s="9"/>
+      <x:c r="D345" s="9"/>
+      <x:c r="E345" s="9"/>
+      <x:c r="F345" s="9"/>
+    </x:row>
+    <x:row r="346">
+      <x:c r="A346" s="12"/>
+      <x:c r="B346" s="9"/>
+      <x:c r="C346" s="9"/>
+      <x:c r="D346" s="9"/>
+      <x:c r="E346" s="9"/>
+      <x:c r="F346" s="9"/>
+    </x:row>
+    <x:row r="347">
+      <x:c r="A347" s="12"/>
+      <x:c r="B347" s="9"/>
+      <x:c r="C347" s="9"/>
+      <x:c r="D347" s="9"/>
+      <x:c r="E347" s="9"/>
+      <x:c r="F347" s="9"/>
+    </x:row>
+    <x:row r="348">
+      <x:c r="A348" s="12"/>
+      <x:c r="B348" s="9"/>
+      <x:c r="C348" s="9"/>
+      <x:c r="D348" s="9"/>
+      <x:c r="E348" s="9"/>
+      <x:c r="F348" s="9"/>
+    </x:row>
+    <x:row r="349">
+      <x:c r="A349" s="12"/>
+      <x:c r="B349" s="9"/>
+      <x:c r="C349" s="9"/>
+      <x:c r="D349" s="9"/>
+      <x:c r="E349" s="9"/>
+      <x:c r="F349" s="9"/>
+    </x:row>
+    <x:row r="350">
+      <x:c r="A350" s="12"/>
+      <x:c r="B350" s="9"/>
+      <x:c r="C350" s="9"/>
+      <x:c r="D350" s="9"/>
+      <x:c r="E350" s="9"/>
+      <x:c r="F350" s="9"/>
+    </x:row>
+    <x:row r="351">
+      <x:c r="A351" s="12"/>
+      <x:c r="B351" s="9"/>
+      <x:c r="C351" s="9"/>
+      <x:c r="D351" s="9"/>
+      <x:c r="E351" s="9"/>
+      <x:c r="F351" s="9"/>
+    </x:row>
+    <x:row r="352">
+      <x:c r="A352" s="12"/>
+      <x:c r="B352" s="9"/>
+      <x:c r="C352" s="9"/>
+      <x:c r="D352" s="9"/>
+      <x:c r="E352" s="9"/>
+      <x:c r="F352" s="9"/>
+    </x:row>
+    <x:row r="353">
+      <x:c r="A353" s="12"/>
+      <x:c r="B353" s="9"/>
+      <x:c r="C353" s="9"/>
+      <x:c r="D353" s="9"/>
+      <x:c r="E353" s="9"/>
+      <x:c r="F353" s="9"/>
+    </x:row>
+    <x:row r="354">
+      <x:c r="A354" s="12"/>
+      <x:c r="B354" s="9"/>
+      <x:c r="C354" s="9"/>
+      <x:c r="D354" s="9"/>
+      <x:c r="E354" s="9"/>
+      <x:c r="F354" s="9"/>
+    </x:row>
+    <x:row r="355">
+      <x:c r="A355" s="12"/>
+      <x:c r="B355" s="9"/>
+      <x:c r="C355" s="9"/>
+      <x:c r="D355" s="9"/>
+      <x:c r="E355" s="9"/>
+      <x:c r="F355" s="9"/>
+    </x:row>
+    <x:row r="356">
+      <x:c r="A356" s="12"/>
+      <x:c r="B356" s="9"/>
+      <x:c r="C356" s="9"/>
+      <x:c r="D356" s="9"/>
+      <x:c r="E356" s="9"/>
+      <x:c r="F356" s="9"/>
+    </x:row>
+    <x:row r="357">
+      <x:c r="A357" s="12"/>
+      <x:c r="B357" s="9"/>
+      <x:c r="C357" s="9"/>
+      <x:c r="D357" s="9"/>
+      <x:c r="E357" s="9"/>
+      <x:c r="F357" s="9"/>
+    </x:row>
+    <x:row r="358">
+      <x:c r="A358" s="12"/>
+      <x:c r="B358" s="9"/>
+      <x:c r="C358" s="9"/>
+      <x:c r="D358" s="9"/>
+      <x:c r="E358" s="9"/>
+      <x:c r="F358" s="9"/>
+    </x:row>
+    <x:row r="359">
+      <x:c r="A359" s="12"/>
+      <x:c r="B359" s="9"/>
+      <x:c r="C359" s="9"/>
+      <x:c r="D359" s="9"/>
+      <x:c r="E359" s="9"/>
+      <x:c r="F359" s="9"/>
+    </x:row>
+    <x:row r="360">
+      <x:c r="A360" s="12"/>
+      <x:c r="B360" s="9"/>
+      <x:c r="C360" s="9"/>
+      <x:c r="D360" s="9"/>
+      <x:c r="E360" s="9"/>
+      <x:c r="F360" s="9"/>
+    </x:row>
+    <x:row r="361">
+      <x:c r="A361" s="12"/>
+      <x:c r="B361" s="9"/>
+      <x:c r="C361" s="9"/>
+      <x:c r="D361" s="9"/>
+      <x:c r="E361" s="9"/>
+      <x:c r="F361" s="9"/>
+    </x:row>
+    <x:row r="362">
+      <x:c r="A362" s="12"/>
+      <x:c r="B362" s="9"/>
+      <x:c r="C362" s="9"/>
+      <x:c r="D362" s="9"/>
+      <x:c r="E362" s="9"/>
+      <x:c r="F362" s="9"/>
+    </x:row>
+    <x:row r="363">
+      <x:c r="A363" s="12"/>
+      <x:c r="B363" s="9"/>
+      <x:c r="C363" s="9"/>
+      <x:c r="D363" s="9"/>
+      <x:c r="E363" s="9"/>
+      <x:c r="F363" s="9"/>
+    </x:row>
+    <x:row r="364">
+      <x:c r="A364" s="12"/>
+      <x:c r="B364" s="9"/>
+      <x:c r="C364" s="9"/>
+      <x:c r="D364" s="9"/>
+      <x:c r="E364" s="9"/>
+      <x:c r="F364" s="9"/>
+    </x:row>
+    <x:row r="365">
+      <x:c r="A365" s="12"/>
+      <x:c r="B365" s="9"/>
+      <x:c r="C365" s="9"/>
+      <x:c r="D365" s="9"/>
+      <x:c r="E365" s="9"/>
+      <x:c r="F365" s="9"/>
+    </x:row>
+    <x:row r="366">
+      <x:c r="A366" s="12"/>
+      <x:c r="B366" s="9"/>
+      <x:c r="C366" s="9"/>
+      <x:c r="D366" s="9"/>
+      <x:c r="E366" s="9"/>
+      <x:c r="F366" s="9"/>
+    </x:row>
+    <x:row r="367">
+      <x:c r="A367" s="12"/>
+      <x:c r="B367" s="9"/>
+      <x:c r="C367" s="9"/>
+      <x:c r="D367" s="9"/>
+      <x:c r="E367" s="9"/>
+      <x:c r="F367" s="9"/>
+    </x:row>
+    <x:row r="368">
+      <x:c r="A368" s="12"/>
+      <x:c r="B368" s="9"/>
+      <x:c r="C368" s="9"/>
+      <x:c r="D368" s="9"/>
+      <x:c r="E368" s="9"/>
+      <x:c r="F368" s="9"/>
+    </x:row>
+    <x:row r="369">
+      <x:c r="A369" s="12"/>
+      <x:c r="B369" s="9"/>
+      <x:c r="C369" s="9"/>
+      <x:c r="D369" s="9"/>
+      <x:c r="E369" s="9"/>
+      <x:c r="F369" s="9"/>
+    </x:row>
+    <x:row r="370">
+      <x:c r="A370" s="12"/>
+      <x:c r="B370" s="9"/>
+      <x:c r="C370" s="9"/>
+      <x:c r="D370" s="9"/>
+      <x:c r="E370" s="9"/>
+      <x:c r="F370" s="9"/>
+    </x:row>
+    <x:row r="371">
+      <x:c r="A371" s="12"/>
+      <x:c r="B371" s="9"/>
+      <x:c r="C371" s="9"/>
+      <x:c r="D371" s="9"/>
+      <x:c r="E371" s="9"/>
+      <x:c r="F371" s="9"/>
+    </x:row>
+    <x:row r="372">
+      <x:c r="A372" s="12"/>
+      <x:c r="B372" s="9"/>
+      <x:c r="C372" s="9"/>
+      <x:c r="D372" s="9"/>
+      <x:c r="E372" s="9"/>
+      <x:c r="F372" s="9"/>
+    </x:row>
+    <x:row r="373">
+      <x:c r="A373" s="12"/>
+      <x:c r="B373" s="9"/>
+      <x:c r="C373" s="9"/>
+      <x:c r="D373" s="9"/>
+      <x:c r="E373" s="9"/>
+      <x:c r="F373" s="9"/>
+    </x:row>
+    <x:row r="374">
+      <x:c r="A374" s="12"/>
+      <x:c r="B374" s="9"/>
+      <x:c r="C374" s="9"/>
+      <x:c r="D374" s="9"/>
+      <x:c r="E374" s="9"/>
+      <x:c r="F374" s="9"/>
+    </x:row>
+    <x:row r="375">
+      <x:c r="A375" s="12"/>
+      <x:c r="B375" s="9"/>
+      <x:c r="C375" s="9"/>
+      <x:c r="D375" s="9"/>
+      <x:c r="E375" s="9"/>
+      <x:c r="F375" s="9"/>
+    </x:row>
+    <x:row r="376">
+      <x:c r="A376" s="12"/>
+      <x:c r="B376" s="9"/>
+      <x:c r="C376" s="9"/>
+      <x:c r="D376" s="9"/>
+      <x:c r="E376" s="9"/>
+      <x:c r="F376" s="9"/>
+    </x:row>
+    <x:row r="377">
+      <x:c r="A377" s="12"/>
+      <x:c r="B377" s="9"/>
+      <x:c r="C377" s="9"/>
+      <x:c r="D377" s="9"/>
+      <x:c r="E377" s="9"/>
+      <x:c r="F377" s="9"/>
+    </x:row>
+    <x:row r="378">
+      <x:c r="A378" s="12"/>
+      <x:c r="B378" s="9"/>
+      <x:c r="C378" s="9"/>
+      <x:c r="D378" s="9"/>
+      <x:c r="E378" s="9"/>
+      <x:c r="F378" s="9"/>
+    </x:row>
+    <x:row r="379">
+      <x:c r="A379" s="12"/>
+      <x:c r="B379" s="9"/>
+      <x:c r="C379" s="9"/>
+      <x:c r="D379" s="9"/>
+      <x:c r="E379" s="9"/>
+      <x:c r="F379" s="9"/>
+    </x:row>
+    <x:row r="380">
+      <x:c r="A380" s="12"/>
+      <x:c r="B380" s="9"/>
+      <x:c r="C380" s="9"/>
+      <x:c r="D380" s="9"/>
+      <x:c r="E380" s="9"/>
+      <x:c r="F380" s="9"/>
+    </x:row>
+    <x:row r="381">
+      <x:c r="A381" s="12"/>
+      <x:c r="B381" s="9"/>
+      <x:c r="C381" s="9"/>
+      <x:c r="D381" s="9"/>
+      <x:c r="E381" s="9"/>
+      <x:c r="F381" s="9"/>
+    </x:row>
+    <x:row r="382">
+      <x:c r="A382" s="12"/>
+      <x:c r="B382" s="9"/>
+      <x:c r="C382" s="9"/>
+      <x:c r="D382" s="9"/>
+      <x:c r="E382" s="9"/>
+      <x:c r="F382" s="9"/>
+    </x:row>
+    <x:row r="383">
+      <x:c r="A383" s="12"/>
+      <x:c r="B383" s="9"/>
+      <x:c r="C383" s="9"/>
+      <x:c r="D383" s="9"/>
+      <x:c r="E383" s="9"/>
+      <x:c r="F383" s="9"/>
+    </x:row>
+    <x:row r="384">
+      <x:c r="A384" s="12"/>
+      <x:c r="B384" s="9"/>
+      <x:c r="C384" s="9"/>
+      <x:c r="D384" s="9"/>
+      <x:c r="E384" s="9"/>
+      <x:c r="F384" s="9"/>
+    </x:row>
+    <x:row r="385">
+      <x:c r="A385" s="12"/>
+      <x:c r="B385" s="9"/>
+      <x:c r="C385" s="9"/>
+      <x:c r="D385" s="9"/>
+      <x:c r="E385" s="9"/>
+      <x:c r="F385" s="9"/>
+    </x:row>
+    <x:row r="386">
+      <x:c r="A386" s="12"/>
+      <x:c r="B386" s="9"/>
+      <x:c r="C386" s="9"/>
+      <x:c r="D386" s="9"/>
+      <x:c r="E386" s="9"/>
+      <x:c r="F386" s="9"/>
+    </x:row>
+    <x:row r="387">
+      <x:c r="A387" s="12"/>
+      <x:c r="B387" s="9"/>
+      <x:c r="C387" s="9"/>
+      <x:c r="D387" s="9"/>
+      <x:c r="E387" s="9"/>
+      <x:c r="F387" s="9"/>
+    </x:row>
+    <x:row r="388">
+      <x:c r="A388" s="12"/>
+      <x:c r="B388" s="9"/>
+      <x:c r="C388" s="9"/>
+      <x:c r="D388" s="9"/>
+      <x:c r="E388" s="9"/>
+      <x:c r="F388" s="9"/>
+    </x:row>
+    <x:row r="389">
+      <x:c r="A389" s="12"/>
+      <x:c r="B389" s="9"/>
+      <x:c r="C389" s="9"/>
+      <x:c r="D389" s="9"/>
+      <x:c r="E389" s="9"/>
+      <x:c r="F389" s="9"/>
+    </x:row>
+    <x:row r="390">
+      <x:c r="A390" s="12"/>
+      <x:c r="B390" s="9"/>
+      <x:c r="C390" s="9"/>
+      <x:c r="D390" s="9"/>
+      <x:c r="E390" s="9"/>
+      <x:c r="F390" s="9"/>
+    </x:row>
+    <x:row r="391">
+      <x:c r="A391" s="12"/>
+      <x:c r="B391" s="9"/>
+      <x:c r="C391" s="9"/>
+      <x:c r="D391" s="9"/>
+      <x:c r="E391" s="9"/>
+      <x:c r="F391" s="9"/>
+    </x:row>
+    <x:row r="392">
+      <x:c r="A392" s="12"/>
+      <x:c r="B392" s="9"/>
+      <x:c r="C392" s="9"/>
+      <x:c r="D392" s="9"/>
+      <x:c r="E392" s="9"/>
+      <x:c r="F392" s="9"/>
+    </x:row>
+    <x:row r="393">
+      <x:c r="A393" s="12"/>
+      <x:c r="B393" s="9"/>
+      <x:c r="C393" s="9"/>
+      <x:c r="D393" s="9"/>
+      <x:c r="E393" s="9"/>
+      <x:c r="F393" s="9"/>
+    </x:row>
+    <x:row r="394">
+      <x:c r="A394" s="12"/>
+      <x:c r="B394" s="9"/>
+      <x:c r="C394" s="9"/>
+      <x:c r="D394" s="9"/>
+      <x:c r="E394" s="9"/>
+      <x:c r="F394" s="9"/>
+    </x:row>
+    <x:row r="395">
+      <x:c r="A395" s="12"/>
+      <x:c r="B395" s="9"/>
+      <x:c r="C395" s="9"/>
+      <x:c r="D395" s="9"/>
+      <x:c r="E395" s="9"/>
+      <x:c r="F395" s="9"/>
+    </x:row>
+    <x:row r="396">
+      <x:c r="A396" s="12"/>
+      <x:c r="B396" s="9"/>
+      <x:c r="C396" s="9"/>
+      <x:c r="D396" s="9"/>
+      <x:c r="E396" s="9"/>
+      <x:c r="F396" s="9"/>
+    </x:row>
+    <x:row r="397">
+      <x:c r="A397" s="12"/>
+      <x:c r="B397" s="9"/>
+      <x:c r="C397" s="9"/>
+      <x:c r="D397" s="9"/>
+      <x:c r="E397" s="9"/>
+      <x:c r="F397" s="9"/>
+    </x:row>
+    <x:row r="398">
+      <x:c r="A398" s="12"/>
+      <x:c r="B398" s="9"/>
+      <x:c r="C398" s="9"/>
+      <x:c r="D398" s="9"/>
+      <x:c r="E398" s="9"/>
+      <x:c r="F398" s="9"/>
+    </x:row>
+    <x:row r="399">
+      <x:c r="A399" s="12"/>
+      <x:c r="B399" s="9"/>
+      <x:c r="C399" s="9"/>
+      <x:c r="D399" s="9"/>
+      <x:c r="E399" s="9"/>
+      <x:c r="F399" s="9"/>
+    </x:row>
+    <x:row r="400">
+      <x:c r="A400" s="12"/>
+      <x:c r="B400" s="9"/>
+      <x:c r="C400" s="9"/>
+      <x:c r="D400" s="9"/>
+      <x:c r="E400" s="9"/>
+      <x:c r="F400" s="9"/>
+    </x:row>
+    <x:row r="401">
+      <x:c r="A401" s="12"/>
+      <x:c r="B401" s="9"/>
+      <x:c r="C401" s="9"/>
+      <x:c r="D401" s="9"/>
+      <x:c r="E401" s="9"/>
+      <x:c r="F401" s="9"/>
+    </x:row>
+    <x:row r="402">
+      <x:c r="A402" s="12"/>
+      <x:c r="B402" s="9"/>
+      <x:c r="C402" s="9"/>
+      <x:c r="D402" s="9"/>
+      <x:c r="E402" s="9"/>
+      <x:c r="F402" s="9"/>
+    </x:row>
+    <x:row r="403">
+      <x:c r="A403" s="12"/>
+      <x:c r="B403" s="9"/>
+      <x:c r="C403" s="9"/>
+      <x:c r="D403" s="9"/>
+      <x:c r="E403" s="9"/>
+      <x:c r="F403" s="9"/>
+    </x:row>
+    <x:row r="404">
+      <x:c r="A404" s="12"/>
+      <x:c r="B404" s="9"/>
+      <x:c r="C404" s="9"/>
+      <x:c r="D404" s="9"/>
+      <x:c r="E404" s="9"/>
+      <x:c r="F404" s="9"/>
+    </x:row>
+    <x:row r="405">
+      <x:c r="A405" s="12"/>
+      <x:c r="B405" s="9"/>
+      <x:c r="C405" s="9"/>
+      <x:c r="D405" s="9"/>
+      <x:c r="E405" s="9"/>
+      <x:c r="F405" s="9"/>
+    </x:row>
+    <x:row r="406">
+      <x:c r="A406" s="12"/>
+      <x:c r="B406" s="9"/>
+      <x:c r="C406" s="9"/>
+      <x:c r="D406" s="9"/>
+      <x:c r="E406" s="9"/>
+      <x:c r="F406" s="9"/>
+    </x:row>
+    <x:row r="407">
+      <x:c r="A407" s="12"/>
+      <x:c r="B407" s="9"/>
+      <x:c r="C407" s="9"/>
+      <x:c r="D407" s="9"/>
+      <x:c r="E407" s="9"/>
+      <x:c r="F407" s="9"/>
+    </x:row>
+    <x:row r="408">
+      <x:c r="A408" s="12"/>
+      <x:c r="B408" s="9"/>
+      <x:c r="C408" s="9"/>
+      <x:c r="D408" s="9"/>
+      <x:c r="E408" s="9"/>
+      <x:c r="F408" s="9"/>
+    </x:row>
+    <x:row r="409">
+      <x:c r="A409" s="12"/>
+      <x:c r="B409" s="9"/>
+      <x:c r="C409" s="9"/>
+      <x:c r="D409" s="9"/>
+      <x:c r="E409" s="9"/>
+      <x:c r="F409" s="9"/>
+    </x:row>
+    <x:row r="410">
+      <x:c r="A410" s="12"/>
+      <x:c r="B410" s="9"/>
+      <x:c r="C410" s="9"/>
+      <x:c r="D410" s="9"/>
+      <x:c r="E410" s="9"/>
+      <x:c r="F410" s="9"/>
+    </x:row>
+    <x:row r="411">
+      <x:c r="A411" s="12"/>
+      <x:c r="B411" s="9"/>
+      <x:c r="C411" s="9"/>
+      <x:c r="D411" s="9"/>
+      <x:c r="E411" s="9"/>
+      <x:c r="F411" s="9"/>
+    </x:row>
+    <x:row r="412">
+      <x:c r="A412" s="12"/>
+      <x:c r="B412" s="9"/>
+      <x:c r="C412" s="9"/>
+      <x:c r="D412" s="9"/>
+      <x:c r="E412" s="9"/>
+      <x:c r="F412" s="9"/>
+    </x:row>
+    <x:row r="413">
+      <x:c r="A413" s="12"/>
+      <x:c r="B413" s="9"/>
+      <x:c r="C413" s="9"/>
+      <x:c r="D413" s="9"/>
+      <x:c r="E413" s="9"/>
+      <x:c r="F413" s="9"/>
+    </x:row>
+    <x:row r="414">
+      <x:c r="A414" s="12"/>
+      <x:c r="B414" s="9"/>
+      <x:c r="C414" s="9"/>
+      <x:c r="D414" s="9"/>
+      <x:c r="E414" s="9"/>
+      <x:c r="F414" s="9"/>
+    </x:row>
+    <x:row r="415">
+      <x:c r="A415" s="12"/>
+      <x:c r="B415" s="9"/>
+      <x:c r="C415" s="9"/>
+      <x:c r="D415" s="9"/>
+      <x:c r="E415" s="9"/>
+      <x:c r="F415" s="9"/>
+    </x:row>
+    <x:row r="416">
+      <x:c r="A416" s="12"/>
+      <x:c r="B416" s="9"/>
+      <x:c r="C416" s="9"/>
+      <x:c r="D416" s="9"/>
+      <x:c r="E416" s="9"/>
+      <x:c r="F416" s="9"/>
+    </x:row>
+    <x:row r="417">
+      <x:c r="A417" s="12"/>
+      <x:c r="B417" s="9"/>
+      <x:c r="C417" s="9"/>
+      <x:c r="D417" s="9"/>
+      <x:c r="E417" s="9"/>
+      <x:c r="F417" s="9"/>
+    </x:row>
+    <x:row r="418">
+      <x:c r="A418" s="12"/>
+      <x:c r="B418" s="9"/>
+      <x:c r="C418" s="9"/>
+      <x:c r="D418" s="9"/>
+      <x:c r="E418" s="9"/>
+      <x:c r="F418" s="9"/>
+    </x:row>
+    <x:row r="419">
+      <x:c r="A419" s="12"/>
+      <x:c r="B419" s="9"/>
+      <x:c r="C419" s="9"/>
+      <x:c r="D419" s="9"/>
+      <x:c r="E419" s="9"/>
+      <x:c r="F419" s="9"/>
+    </x:row>
+    <x:row r="420">
+      <x:c r="A420" s="12"/>
+      <x:c r="B420" s="9"/>
+      <x:c r="C420" s="9"/>
+      <x:c r="D420" s="9"/>
+      <x:c r="E420" s="9"/>
+      <x:c r="F420" s="9"/>
+    </x:row>
+    <x:row r="421">
+      <x:c r="A421" s="12"/>
+      <x:c r="B421" s="9"/>
+      <x:c r="C421" s="9"/>
+      <x:c r="D421" s="9"/>
+      <x:c r="E421" s="9"/>
+      <x:c r="F421" s="9"/>
+    </x:row>
+    <x:row r="422">
+      <x:c r="A422" s="12"/>
+      <x:c r="B422" s="9"/>
+      <x:c r="C422" s="9"/>
+      <x:c r="D422" s="9"/>
+      <x:c r="E422" s="9"/>
+      <x:c r="F422" s="9"/>
+    </x:row>
+    <x:row r="423">
+      <x:c r="A423" s="12"/>
+      <x:c r="B423" s="9"/>
+      <x:c r="C423" s="9"/>
+      <x:c r="D423" s="9"/>
+      <x:c r="E423" s="9"/>
+      <x:c r="F423" s="9"/>
+    </x:row>
+    <x:row r="424">
+      <x:c r="A424" s="12"/>
+      <x:c r="B424" s="9"/>
+      <x:c r="C424" s="9"/>
+      <x:c r="D424" s="9"/>
+      <x:c r="E424" s="9"/>
+      <x:c r="F424" s="9"/>
+    </x:row>
+    <x:row r="425">
+      <x:c r="A425" s="12"/>
+      <x:c r="B425" s="9"/>
+      <x:c r="C425" s="9"/>
+      <x:c r="D425" s="9"/>
+      <x:c r="E425" s="9"/>
+      <x:c r="F425" s="9"/>
+    </x:row>
+    <x:row r="426">
+      <x:c r="A426" s="12"/>
+      <x:c r="B426" s="9"/>
+      <x:c r="C426" s="9"/>
+      <x:c r="D426" s="9"/>
+      <x:c r="E426" s="9"/>
+      <x:c r="F426" s="9"/>
+    </x:row>
+    <x:row r="427">
+      <x:c r="A427" s="12"/>
+      <x:c r="B427" s="9"/>
+      <x:c r="C427" s="9"/>
+      <x:c r="D427" s="9"/>
+      <x:c r="E427" s="9"/>
+      <x:c r="F427" s="9"/>
+    </x:row>
+    <x:row r="428">
+      <x:c r="A428" s="12"/>
+      <x:c r="B428" s="9"/>
+      <x:c r="C428" s="9"/>
+      <x:c r="D428" s="9"/>
+      <x:c r="E428" s="9"/>
+      <x:c r="F428" s="9"/>
+    </x:row>
+    <x:row r="429">
+      <x:c r="A429" s="12"/>
+      <x:c r="B429" s="9"/>
+      <x:c r="C429" s="9"/>
+      <x:c r="D429" s="9"/>
+      <x:c r="E429" s="9"/>
+      <x:c r="F429" s="9"/>
+    </x:row>
+    <x:row r="430">
+      <x:c r="A430" s="12"/>
+      <x:c r="B430" s="9"/>
+      <x:c r="C430" s="9"/>
+      <x:c r="D430" s="9"/>
+      <x:c r="E430" s="9"/>
+      <x:c r="F430" s="9"/>
+    </x:row>
+    <x:row r="431">
+      <x:c r="A431" s="12"/>
+      <x:c r="B431" s="9"/>
+      <x:c r="C431" s="9"/>
+      <x:c r="D431" s="9"/>
+      <x:c r="E431" s="9"/>
+      <x:c r="F431" s="9"/>
+    </x:row>
+    <x:row r="432">
+      <x:c r="A432" s="12"/>
+      <x:c r="B432" s="9"/>
+      <x:c r="C432" s="9"/>
+      <x:c r="D432" s="9"/>
+      <x:c r="E432" s="9"/>
+      <x:c r="F432" s="9"/>
+    </x:row>
+    <x:row r="433">
+      <x:c r="A433" s="12"/>
+      <x:c r="B433" s="9"/>
+      <x:c r="C433" s="9"/>
+      <x:c r="D433" s="9"/>
+      <x:c r="E433" s="9"/>
+      <x:c r="F433" s="9"/>
+    </x:row>
+    <x:row r="434">
+      <x:c r="A434" s="12"/>
+      <x:c r="B434" s="9"/>
+      <x:c r="C434" s="9"/>
+      <x:c r="D434" s="9"/>
+      <x:c r="E434" s="9"/>
+      <x:c r="F434" s="9"/>
+    </x:row>
+    <x:row r="435">
+      <x:c r="A435" s="12"/>
+      <x:c r="B435" s="9"/>
+      <x:c r="C435" s="9"/>
+      <x:c r="D435" s="9"/>
+      <x:c r="E435" s="9"/>
+      <x:c r="F435" s="9"/>
+    </x:row>
+    <x:row r="436">
+      <x:c r="A436" s="12"/>
+      <x:c r="B436" s="9"/>
+      <x:c r="C436" s="9"/>
+      <x:c r="D436" s="9"/>
+      <x:c r="E436" s="9"/>
+      <x:c r="F436" s="9"/>
+    </x:row>
+    <x:row r="437">
+      <x:c r="A437" s="12"/>
+      <x:c r="B437" s="9"/>
+      <x:c r="C437" s="9"/>
+      <x:c r="D437" s="9"/>
+      <x:c r="E437" s="9"/>
+      <x:c r="F437" s="9"/>
+    </x:row>
+    <x:row r="438">
+      <x:c r="A438" s="12"/>
+      <x:c r="B438" s="9"/>
+      <x:c r="C438" s="9"/>
+      <x:c r="D438" s="9"/>
+      <x:c r="E438" s="9"/>
+      <x:c r="F438" s="9"/>
+    </x:row>
+    <x:row r="439">
+      <x:c r="A439" s="12"/>
+      <x:c r="B439" s="9"/>
+      <x:c r="C439" s="9"/>
+      <x:c r="D439" s="9"/>
+      <x:c r="E439" s="9"/>
+      <x:c r="F439" s="9"/>
+    </x:row>
+    <x:row r="440">
+      <x:c r="A440" s="12"/>
+      <x:c r="B440" s="9"/>
+      <x:c r="C440" s="9"/>
+      <x:c r="D440" s="9"/>
+      <x:c r="E440" s="9"/>
+      <x:c r="F440" s="9"/>
+    </x:row>
+    <x:row r="441">
+      <x:c r="A441" s="12"/>
+      <x:c r="B441" s="9"/>
+      <x:c r="C441" s="9"/>
+      <x:c r="D441" s="9"/>
+      <x:c r="E441" s="9"/>
+      <x:c r="F441" s="9"/>
+    </x:row>
+    <x:row r="442">
+      <x:c r="A442" s="12"/>
+      <x:c r="B442" s="9"/>
+      <x:c r="C442" s="9"/>
+      <x:c r="D442" s="9"/>
+      <x:c r="E442" s="9"/>
+      <x:c r="F442" s="9"/>
+    </x:row>
+    <x:row r="443">
+      <x:c r="A443" s="12"/>
+      <x:c r="B443" s="9"/>
+      <x:c r="C443" s="9"/>
+      <x:c r="D443" s="9"/>
+      <x:c r="E443" s="9"/>
+      <x:c r="F443" s="9"/>
+    </x:row>
+    <x:row r="444">
+      <x:c r="A444" s="12"/>
+      <x:c r="B444" s="9"/>
+      <x:c r="C444" s="9"/>
+      <x:c r="D444" s="9"/>
+      <x:c r="E444" s="9"/>
+      <x:c r="F444" s="9"/>
+    </x:row>
+    <x:row r="445">
+      <x:c r="A445" s="12"/>
+      <x:c r="B445" s="9"/>
+      <x:c r="C445" s="9"/>
+      <x:c r="D445" s="9"/>
+      <x:c r="E445" s="9"/>
+      <x:c r="F445" s="9"/>
+    </x:row>
+    <x:row r="446">
+      <x:c r="A446" s="12"/>
+      <x:c r="B446" s="9"/>
+      <x:c r="C446" s="9"/>
+      <x:c r="D446" s="9"/>
+      <x:c r="E446" s="9"/>
+      <x:c r="F446" s="9"/>
+    </x:row>
+    <x:row r="447">
+      <x:c r="A447" s="12"/>
+      <x:c r="B447" s="9"/>
+      <x:c r="C447" s="9"/>
+      <x:c r="D447" s="9"/>
+      <x:c r="E447" s="9"/>
+      <x:c r="F447" s="9"/>
+    </x:row>
+    <x:row r="448">
+      <x:c r="A448" s="12"/>
+      <x:c r="B448" s="9"/>
+      <x:c r="C448" s="9"/>
+      <x:c r="D448" s="9"/>
+      <x:c r="E448" s="9"/>
+      <x:c r="F448" s="9"/>
+    </x:row>
+    <x:row r="449">
+      <x:c r="A449" s="12"/>
+      <x:c r="B449" s="9"/>
+      <x:c r="C449" s="9"/>
+      <x:c r="D449" s="9"/>
+      <x:c r="E449" s="9"/>
+      <x:c r="F449" s="9"/>
+    </x:row>
+    <x:row r="450">
+      <x:c r="A450" s="12"/>
+      <x:c r="B450" s="9"/>
+      <x:c r="C450" s="9"/>
+      <x:c r="D450" s="9"/>
+      <x:c r="E450" s="9"/>
+      <x:c r="F450" s="9"/>
+    </x:row>
+    <x:row r="451">
+      <x:c r="A451" s="12"/>
+      <x:c r="B451" s="9"/>
+      <x:c r="C451" s="9"/>
+      <x:c r="D451" s="9"/>
+      <x:c r="E451" s="9"/>
+      <x:c r="F451" s="9"/>
+    </x:row>
+    <x:row r="452">
+      <x:c r="A452" s="12"/>
+      <x:c r="B452" s="9"/>
+      <x:c r="C452" s="9"/>
+      <x:c r="D452" s="9"/>
+      <x:c r="E452" s="9"/>
+      <x:c r="F452" s="9"/>
+    </x:row>
+    <x:row r="453">
+      <x:c r="A453" s="12"/>
+      <x:c r="B453" s="9"/>
+      <x:c r="C453" s="9"/>
+      <x:c r="D453" s="9"/>
+      <x:c r="E453" s="9"/>
+      <x:c r="F453" s="9"/>
+    </x:row>
+    <x:row r="454">
+      <x:c r="A454" s="12"/>
+      <x:c r="B454" s="9"/>
+      <x:c r="C454" s="9"/>
+      <x:c r="D454" s="9"/>
+      <x:c r="E454" s="9"/>
+      <x:c r="F454" s="9"/>
+    </x:row>
+    <x:row r="455">
+      <x:c r="A455" s="12"/>
+      <x:c r="B455" s="9"/>
+      <x:c r="C455" s="9"/>
+      <x:c r="D455" s="9"/>
+      <x:c r="E455" s="9"/>
+      <x:c r="F455" s="9"/>
+    </x:row>
+    <x:row r="456">
+      <x:c r="A456" s="12"/>
+      <x:c r="B456" s="9"/>
+      <x:c r="C456" s="9"/>
+      <x:c r="D456" s="9"/>
+      <x:c r="E456" s="9"/>
+      <x:c r="F456" s="9"/>
+    </x:row>
+    <x:row r="457">
+      <x:c r="A457" s="12"/>
+      <x:c r="B457" s="9"/>
+      <x:c r="C457" s="9"/>
+      <x:c r="D457" s="9"/>
+      <x:c r="E457" s="9"/>
+      <x:c r="F457" s="9"/>
+    </x:row>
+    <x:row r="458">
+      <x:c r="A458" s="12"/>
+      <x:c r="B458" s="9"/>
+      <x:c r="C458" s="9"/>
+      <x:c r="D458" s="9"/>
+      <x:c r="E458" s="9"/>
+      <x:c r="F458" s="9"/>
+    </x:row>
+    <x:row r="459">
+      <x:c r="A459" s="12"/>
+      <x:c r="B459" s="9"/>
+      <x:c r="C459" s="9"/>
+      <x:c r="D459" s="9"/>
+      <x:c r="E459" s="9"/>
+      <x:c r="F459" s="9"/>
+    </x:row>
+    <x:row r="460">
+      <x:c r="A460" s="12"/>
+      <x:c r="B460" s="9"/>
+      <x:c r="C460" s="9"/>
+      <x:c r="D460" s="9"/>
+      <x:c r="E460" s="9"/>
+      <x:c r="F460" s="9"/>
+    </x:row>
+    <x:row r="461">
+      <x:c r="A461" s="12"/>
+      <x:c r="B461" s="9"/>
+      <x:c r="C461" s="9"/>
+      <x:c r="D461" s="9"/>
+      <x:c r="E461" s="9"/>
+      <x:c r="F461" s="9"/>
+    </x:row>
+    <x:row r="462">
+      <x:c r="A462" s="12"/>
+      <x:c r="B462" s="9"/>
+      <x:c r="C462" s="9"/>
+      <x:c r="D462" s="9"/>
+      <x:c r="E462" s="9"/>
+      <x:c r="F462" s="9"/>
+    </x:row>
+    <x:row r="463">
+      <x:c r="A463" s="12"/>
+      <x:c r="B463" s="9"/>
+      <x:c r="C463" s="9"/>
+      <x:c r="D463" s="9"/>
+      <x:c r="E463" s="9"/>
+      <x:c r="F463" s="9"/>
+    </x:row>
+    <x:row r="464">
+      <x:c r="A464" s="12"/>
+      <x:c r="B464" s="9"/>
+      <x:c r="C464" s="9"/>
+      <x:c r="D464" s="9"/>
+      <x:c r="E464" s="9"/>
+      <x:c r="F464" s="9"/>
+    </x:row>
+    <x:row r="465">
+      <x:c r="A465" s="12"/>
+      <x:c r="B465" s="9"/>
+      <x:c r="C465" s="9"/>
+      <x:c r="D465" s="9"/>
+      <x:c r="E465" s="9"/>
+      <x:c r="F465" s="9"/>
+    </x:row>
+    <x:row r="466">
+      <x:c r="A466" s="12"/>
+      <x:c r="B466" s="9"/>
+      <x:c r="C466" s="9"/>
+      <x:c r="D466" s="9"/>
+      <x:c r="E466" s="9"/>
+      <x:c r="F466" s="9"/>
+    </x:row>
+    <x:row r="467">
+      <x:c r="A467" s="12"/>
+      <x:c r="B467" s="9"/>
+      <x:c r="C467" s="9"/>
+      <x:c r="D467" s="9"/>
+      <x:c r="E467" s="9"/>
+      <x:c r="F467" s="9"/>
+    </x:row>
+    <x:row r="468">
+      <x:c r="A468" s="12"/>
+      <x:c r="B468" s="9"/>
+      <x:c r="C468" s="9"/>
+      <x:c r="D468" s="9"/>
+      <x:c r="E468" s="9"/>
+      <x:c r="F468" s="9"/>
+    </x:row>
+    <x:row r="469">
+      <x:c r="A469" s="12"/>
+      <x:c r="B469" s="9"/>
+      <x:c r="C469" s="9"/>
+      <x:c r="D469" s="9"/>
+      <x:c r="E469" s="9"/>
+      <x:c r="F469" s="9"/>
+    </x:row>
+    <x:row r="470">
+      <x:c r="A470" s="12"/>
+      <x:c r="B470" s="9"/>
+      <x:c r="C470" s="9"/>
+      <x:c r="D470" s="9"/>
+      <x:c r="E470" s="9"/>
+      <x:c r="F470" s="9"/>
+    </x:row>
+    <x:row r="471">
+      <x:c r="A471" s="12"/>
+      <x:c r="B471" s="9"/>
+      <x:c r="C471" s="9"/>
+      <x:c r="D471" s="9"/>
+      <x:c r="E471" s="9"/>
+      <x:c r="F471" s="9"/>
+    </x:row>
+    <x:row r="472">
+      <x:c r="A472" s="12"/>
+      <x:c r="B472" s="9"/>
+      <x:c r="C472" s="9"/>
+      <x:c r="D472" s="9"/>
+      <x:c r="E472" s="9"/>
+      <x:c r="F472" s="9"/>
+    </x:row>
+    <x:row r="473">
+      <x:c r="A473" s="12"/>
+      <x:c r="B473" s="9"/>
+      <x:c r="C473" s="9"/>
+      <x:c r="D473" s="9"/>
+      <x:c r="E473" s="9"/>
+      <x:c r="F473" s="9"/>
+    </x:row>
+    <x:row r="474">
+      <x:c r="A474" s="12"/>
+      <x:c r="B474" s="9"/>
+      <x:c r="C474" s="9"/>
+      <x:c r="D474" s="9"/>
+      <x:c r="E474" s="9"/>
+      <x:c r="F474" s="9"/>
+    </x:row>
+    <x:row r="475">
+      <x:c r="A475" s="12"/>
+      <x:c r="B475" s="9"/>
+      <x:c r="C475" s="9"/>
+      <x:c r="D475" s="9"/>
+      <x:c r="E475" s="9"/>
+      <x:c r="F475" s="9"/>
+    </x:row>
+    <x:row r="476">
+      <x:c r="A476" s="12"/>
+      <x:c r="B476" s="9"/>
+      <x:c r="C476" s="9"/>
+      <x:c r="D476" s="9"/>
+      <x:c r="E476" s="9"/>
+      <x:c r="F476" s="9"/>
+    </x:row>
+    <x:row r="477">
+      <x:c r="A477" s="12"/>
+      <x:c r="B477" s="9"/>
+      <x:c r="C477" s="9"/>
+      <x:c r="D477" s="9"/>
+      <x:c r="E477" s="9"/>
+      <x:c r="F477" s="9"/>
+    </x:row>
+    <x:row r="478">
+      <x:c r="A478" s="12"/>
+      <x:c r="B478" s="9"/>
+      <x:c r="C478" s="9"/>
+      <x:c r="D478" s="9"/>
+      <x:c r="E478" s="9"/>
+      <x:c r="F478" s="9"/>
+    </x:row>
+    <x:row r="479">
+      <x:c r="A479" s="12"/>
+      <x:c r="B479" s="9"/>
+      <x:c r="C479" s="9"/>
+      <x:c r="D479" s="9"/>
+      <x:c r="E479" s="9"/>
+      <x:c r="F479" s="9"/>
+    </x:row>
+    <x:row r="480">
+      <x:c r="A480" s="12"/>
+      <x:c r="B480" s="9"/>
+      <x:c r="C480" s="9"/>
+      <x:c r="D480" s="9"/>
+      <x:c r="E480" s="9"/>
+      <x:c r="F480" s="9"/>
+    </x:row>
+    <x:row r="481">
+      <x:c r="A481" s="12"/>
+      <x:c r="B481" s="9"/>
+      <x:c r="C481" s="9"/>
+      <x:c r="D481" s="9"/>
+      <x:c r="E481" s="9"/>
+      <x:c r="F481" s="9"/>
+    </x:row>
+    <x:row r="482">
+      <x:c r="A482" s="12"/>
+      <x:c r="B482" s="9"/>
+      <x:c r="C482" s="9"/>
+      <x:c r="D482" s="9"/>
+      <x:c r="E482" s="9"/>
+      <x:c r="F482" s="9"/>
+    </x:row>
+    <x:row r="483">
+      <x:c r="A483" s="12"/>
+      <x:c r="B483" s="9"/>
+      <x:c r="C483" s="9"/>
+      <x:c r="D483" s="9"/>
+      <x:c r="E483" s="9"/>
+      <x:c r="F483" s="9"/>
+    </x:row>
+    <x:row r="484">
+      <x:c r="A484" s="12"/>
+      <x:c r="B484" s="9"/>
+      <x:c r="C484" s="9"/>
+      <x:c r="D484" s="9"/>
+      <x:c r="E484" s="9"/>
+      <x:c r="F484" s="9"/>
+    </x:row>
+    <x:row r="485">
+      <x:c r="A485" s="12"/>
+      <x:c r="B485" s="9"/>
+      <x:c r="C485" s="9"/>
+      <x:c r="D485" s="9"/>
+      <x:c r="E485" s="9"/>
+      <x:c r="F485" s="9"/>
+    </x:row>
+    <x:row r="486">
+      <x:c r="A486" s="12"/>
+      <x:c r="B486" s="9"/>
+      <x:c r="C486" s="9"/>
+      <x:c r="D486" s="9"/>
+      <x:c r="E486" s="9"/>
+      <x:c r="F486" s="9"/>
+    </x:row>
+    <x:row r="487">
+      <x:c r="A487" s="12"/>
+      <x:c r="B487" s="9"/>
+      <x:c r="C487" s="9"/>
+      <x:c r="D487" s="9"/>
+      <x:c r="E487" s="9"/>
+      <x:c r="F487" s="9"/>
+    </x:row>
+    <x:row r="488">
+      <x:c r="A488" s="12"/>
+      <x:c r="B488" s="9"/>
+      <x:c r="C488" s="9"/>
+      <x:c r="D488" s="9"/>
+      <x:c r="E488" s="9"/>
+      <x:c r="F488" s="9"/>
+    </x:row>
+    <x:row r="489">
+      <x:c r="A489" s="12"/>
+      <x:c r="B489" s="9"/>
+      <x:c r="C489" s="9"/>
+      <x:c r="D489" s="9"/>
+      <x:c r="E489" s="9"/>
+      <x:c r="F489" s="9"/>
+    </x:row>
+    <x:row r="490">
+      <x:c r="A490" s="12"/>
+      <x:c r="B490" s="9"/>
+      <x:c r="C490" s="9"/>
+      <x:c r="D490" s="9"/>
+      <x:c r="E490" s="9"/>
+      <x:c r="F490" s="9"/>
+    </x:row>
+    <x:row r="491">
+      <x:c r="A491" s="12"/>
+      <x:c r="B491" s="9"/>
+      <x:c r="C491" s="9"/>
+      <x:c r="D491" s="9"/>
+      <x:c r="E491" s="9"/>
+      <x:c r="F491" s="9"/>
+    </x:row>
+    <x:row r="492">
+      <x:c r="A492" s="12"/>
+      <x:c r="B492" s="9"/>
+      <x:c r="C492" s="9"/>
+      <x:c r="D492" s="9"/>
+      <x:c r="E492" s="9"/>
+      <x:c r="F492" s="9"/>
+    </x:row>
+    <x:row r="493">
+      <x:c r="A493" s="12"/>
+      <x:c r="B493" s="9"/>
+      <x:c r="C493" s="9"/>
+      <x:c r="D493" s="9"/>
+      <x:c r="E493" s="9"/>
+      <x:c r="F493" s="9"/>
+    </x:row>
+    <x:row r="494">
+      <x:c r="A494" s="12"/>
+      <x:c r="B494" s="9"/>
+      <x:c r="C494" s="9"/>
+      <x:c r="D494" s="9"/>
+      <x:c r="E494" s="9"/>
+      <x:c r="F494" s="9"/>
+    </x:row>
+    <x:row r="495">
+      <x:c r="A495" s="12"/>
+      <x:c r="B495" s="9"/>
+      <x:c r="C495" s="9"/>
+      <x:c r="D495" s="9"/>
+      <x:c r="E495" s="9"/>
+      <x:c r="F495" s="9"/>
+    </x:row>
+    <x:row r="496">
+      <x:c r="A496" s="12"/>
+      <x:c r="B496" s="9"/>
+      <x:c r="C496" s="9"/>
+      <x:c r="D496" s="9"/>
+      <x:c r="E496" s="9"/>
+      <x:c r="F496" s="9"/>
+    </x:row>
+    <x:row r="497">
+      <x:c r="A497" s="12"/>
+      <x:c r="B497" s="9"/>
+      <x:c r="C497" s="9"/>
+      <x:c r="D497" s="9"/>
+      <x:c r="E497" s="9"/>
+      <x:c r="F497" s="9"/>
+    </x:row>
+    <x:row r="498">
+      <x:c r="A498" s="12"/>
+      <x:c r="B498" s="9"/>
+      <x:c r="C498" s="9"/>
+      <x:c r="D498" s="9"/>
+      <x:c r="E498" s="9"/>
+      <x:c r="F498" s="9"/>
+    </x:row>
+    <x:row r="499">
+      <x:c r="A499" s="12"/>
+      <x:c r="B499" s="9"/>
+      <x:c r="C499" s="9"/>
+      <x:c r="D499" s="9"/>
+      <x:c r="E499" s="9"/>
+      <x:c r="F499" s="9"/>
+    </x:row>
+    <x:row r="500">
+      <x:c r="A500" s="12"/>
+      <x:c r="B500" s="9"/>
+      <x:c r="C500" s="9"/>
+      <x:c r="D500" s="9"/>
+      <x:c r="E500" s="9"/>
+      <x:c r="F500" s="9"/>
     </x:row>
   </x:sheetData>
+  <x:dataValidations count="4">
+    <x:dataValidation type="list" sqref="B2:B500">
+      <x:formula1>"Servicio,Actividad"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="C2:C500">
+      <x:formula1>'Servicios'!$A$2:$A$200</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="D2:D500">
+      <x:formula1>'Lista Servidores'!$A$2:$A$500</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="E2:E500">
+      <x:formula1>'Estados'!$A$2:$A$100</x:formula1>
+    </x:dataValidation>
+  </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf161b2d1d2d04c51"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd43aaf65c09c4c35"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1511,142 +5007,353 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="19.3799991607666" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="7.269999980926514" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="58" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="12" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="21" t="str">
+        <x:v>Parametro</x:v>
+      </x:c>
+      <x:c r="B1" s="21" t="str">
+        <x:v>Valor</x:v>
+      </x:c>
+      <x:c r="C1" s="21" t="str">
+        <x:v>Descripción</x:v>
+      </x:c>
+      <x:c r="D1" s="21" t="str">
+        <x:v>Editable</x:v>
+      </x:c>
+      <x:c r="E1" s="22"/>
+      <x:c r="F1" s="22"/>
+      <x:c r="G1" s="22"/>
+      <x:c r="H1" s="22"/>
+      <x:c r="I1" s="22"/>
+      <x:c r="J1" s="22"/>
+      <x:c r="K1" s="22"/>
+      <x:c r="L1" s="22"/>
+      <x:c r="M1" s="22"/>
+      <x:c r="N1" s="22"/>
+      <x:c r="O1" s="22"/>
+      <x:c r="P1" s="22"/>
+      <x:c r="Q1" s="22"/>
+      <x:c r="R1" s="22"/>
+      <x:c r="S1" s="22"/>
+      <x:c r="T1" s="22"/>
+      <x:c r="U1" s="22"/>
+      <x:c r="V1" s="22"/>
+      <x:c r="W1" s="22"/>
+      <x:c r="X1" s="22"/>
+      <x:c r="Y1" s="22"/>
+      <x:c r="Z1" s="22"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="9" t="str">
+        <x:v>CantidadGrupos</x:v>
+      </x:c>
+      <x:c r="B2" s="23" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C2" t="str">
+        <x:v>Total de grupos de servicio.</x:v>
+      </x:c>
+      <x:c r="D2" t="str">
+        <x:v>Sí</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="9" t="str">
+        <x:v>FechaBaseRotacion</x:v>
+      </x:c>
+      <x:c r="B3" s="12" t="n">
+        <x:v>46173</x:v>
+      </x:c>
+      <x:c r="C3" t="str">
+        <x:v>Domingo de la semana conocida. Base fija para calcular la rotación.</x:v>
+      </x:c>
+      <x:c r="D3" t="str">
+        <x:v>Sí</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="9" t="str">
+        <x:v>GrupoBaseRotacion</x:v>
+      </x:c>
+      <x:c r="B4" s="23" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C4" t="str">
+        <x:v>Grupo que sirvió en la semana base.</x:v>
+      </x:c>
+      <x:c r="D4" t="str">
+        <x:v>Sí</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="9" t="str">
+        <x:v>InicioSemana</x:v>
+      </x:c>
+      <x:c r="B5" s="24" t="str">
+        <x:v>Domingo</x:v>
+      </x:c>
+      <x:c r="C5" t="str">
+        <x:v>La app trabaja de domingo a sábado.</x:v>
+      </x:c>
+      <x:c r="D5" t="str">
+        <x:v>No</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="str">
+        <x:v>FechaSemanaActual</x:v>
+      </x:c>
+      <x:c r="B6" s="13" t="n">
+        <x:f>TODAY()-WEEKDAY(TODAY(),1)+1</x:f>
+        <x:v>46173</x:v>
+      </x:c>
+      <x:c r="C6" t="str">
+        <x:v>Domingo de la semana actual. En Excel se actualiza al abrir/recalcular.</x:v>
+      </x:c>
+      <x:c r="D6" t="str">
+        <x:v>No</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="str">
+        <x:v>GrupoActivoActual</x:v>
+      </x:c>
+      <x:c r="B7" s="25" t="e">
+        <x:f>MOD(B3-1+INT((B6-B2)/7),B1)+1</x:f>
+      </x:c>
+      <x:c r="C7" t="str">
+        <x:v>Grupo que sirve esta semana según la rotación.</x:v>
+      </x:c>
+      <x:c r="D7" t="str">
+        <x:v>No</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" t="str">
+        <x:v>FechaReferenciaSemana</x:v>
+      </x:c>
+      <x:c r="B8" s="13" t="n">
+        <x:f>B2</x:f>
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C8" t="str">
+        <x:v>Compatibilidad: igual a FechaBaseRotacion.</x:v>
+      </x:c>
+      <x:c r="D8" t="str">
+        <x:v>No</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" t="str">
+        <x:v>GrupoReferencia</x:v>
+      </x:c>
+      <x:c r="B9" s="25" t="n">
+        <x:f>B3</x:f>
+        <x:v>46173</x:v>
+      </x:c>
+      <x:c r="C9" t="str">
+        <x:v>Compatibilidad: igual a GrupoBaseRotacion.</x:v>
+      </x:c>
+      <x:c r="D9" t="str">
+        <x:v>No</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5da7c9639cba4eb1"/>
+  </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="46" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="46" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" s="22" t="str">
-        <x:v>Parametro</x:v>
+        <x:v>Nombre servidor</x:v>
       </x:c>
       <x:c r="B1" s="22" t="str">
-        <x:v>Valor</x:v>
-      </x:c>
-      <x:c r="C1" s="25" t="str">
-        <x:v>Descripción</x:v>
-      </x:c>
-      <x:c r="D1" s="25" t="str">
-        <x:v>Editable</x:v>
-      </x:c>
+        <x:v>Activo</x:v>
+      </x:c>
+      <x:c r="C1" s="22" t="str">
+        <x:v>Notas</x:v>
+      </x:c>
+      <x:c r="D1" s="22"/>
+      <x:c r="E1" s="21" t="str">
+        <x:v>Cómo usar esta hoja</x:v>
+      </x:c>
+      <x:c r="F1" s="21" t="str"/>
+      <x:c r="G1" s="22"/>
+      <x:c r="H1" s="22"/>
+      <x:c r="I1" s="22"/>
+      <x:c r="J1" s="22"/>
+      <x:c r="K1" s="22"/>
+      <x:c r="L1" s="22"/>
+      <x:c r="M1" s="22"/>
+      <x:c r="N1" s="22"/>
+      <x:c r="O1" s="22"/>
+      <x:c r="P1" s="22"/>
+      <x:c r="Q1" s="22"/>
+      <x:c r="R1" s="22"/>
+      <x:c r="S1" s="22"/>
+      <x:c r="T1" s="22"/>
+      <x:c r="U1" s="22"/>
+      <x:c r="V1" s="22"/>
+      <x:c r="W1" s="22"/>
+      <x:c r="X1" s="22"/>
+      <x:c r="Y1" s="22"/>
+      <x:c r="Z1" s="22"/>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="9" t="str">
-        <x:v>CantidadGrupos</x:v>
-      </x:c>
-      <x:c r="B2" s="17" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C2" t="str">
-        <x:v>Total de grupos de servicio.</x:v>
-      </x:c>
-      <x:c r="D2" t="str">
+      <x:c r="A2" t="str">
+        <x:v>Julio Ochoa</x:v>
+      </x:c>
+      <x:c r="B2" t="str">
         <x:v>Sí</x:v>
       </x:c>
+      <x:c r="C2" t="str"/>
+      <x:c r="E2" s="9" t="str">
+        <x:v>1.</x:v>
+      </x:c>
+      <x:c r="F2" s="9" t="str">
+        <x:v>Escribe aquí todos los nombres oficiales de servidores.</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="9" t="str">
-        <x:v>FechaBaseRotacion</x:v>
-      </x:c>
-      <x:c r="B3" s="18" t="n">
-        <x:v>46173</x:v>
-      </x:c>
-      <x:c r="C3" t="str">
-        <x:v>Domingo de la semana conocida. Base fija para calcular la rotación.</x:v>
-      </x:c>
-      <x:c r="D3" t="str">
+      <x:c r="A3" t="str">
+        <x:v>Libni De O.</x:v>
+      </x:c>
+      <x:c r="B3" t="str">
         <x:v>Sí</x:v>
       </x:c>
+      <x:c r="C3" t="str"/>
+      <x:c r="E3" s="9" t="str">
+        <x:v>2.</x:v>
+      </x:c>
+      <x:c r="F3" s="9" t="str">
+        <x:v>Luego aparecerán en las listas desplegables de Servidores y Registro Servicios.</x:v>
+      </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="9" t="str">
-        <x:v>GrupoBaseRotacion</x:v>
-      </x:c>
-      <x:c r="B4" s="17" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C4" t="str">
-        <x:v>Grupo que sirvió en la semana base.</x:v>
-      </x:c>
-      <x:c r="D4" t="str">
+      <x:c r="A4" t="str">
+        <x:v>Sara T</x:v>
+      </x:c>
+      <x:c r="B4" t="str">
         <x:v>Sí</x:v>
       </x:c>
+      <x:c r="C4" t="str"/>
+      <x:c r="E4" s="9" t="str">
+        <x:v>3.</x:v>
+      </x:c>
+      <x:c r="F4" s="9" t="str">
+        <x:v>Usa siempre el mismo nombre para evitar duplicados por escritura diferente.</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="9" t="str">
-        <x:v>InicioSemana</x:v>
-      </x:c>
-      <x:c r="B5" s="19" t="str">
-        <x:v>Domingo</x:v>
-      </x:c>
-      <x:c r="C5" t="str">
-        <x:v>La app trabaja de domingo a sábado.</x:v>
-      </x:c>
-      <x:c r="D5" t="str">
-        <x:v>No</x:v>
+      <x:c r="A5" t="str">
+        <x:v>Jose T</x:v>
+      </x:c>
+      <x:c r="B5" t="str">
+        <x:v>Sí</x:v>
+      </x:c>
+      <x:c r="C5" t="str"/>
+      <x:c r="E5" s="9" t="str">
+        <x:v>4.</x:v>
+      </x:c>
+      <x:c r="F5" s="9" t="str">
+        <x:v>No borres el encabezado de la fila 1.</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" t="str">
-        <x:v>FechaSemanaActual</x:v>
-      </x:c>
-      <x:c r="B6" s="20" t="e">
-        <x:f>HOY()-DIASEM(HOY(),1)+1</x:f>
-      </x:c>
-      <x:c r="C6" t="str">
-        <x:v>Domingo de la semana actual. En Excel se actualiza al abrir/recalcular.</x:v>
-      </x:c>
-      <x:c r="D6" t="str">
-        <x:v>No</x:v>
+        <x:v>Gaby Linares</x:v>
+      </x:c>
+      <x:c r="B6" t="str">
+        <x:v>Sí</x:v>
+      </x:c>
+      <x:c r="C6" t="str"/>
+      <x:c r="E6" s="9" t="str">
+        <x:v>5.</x:v>
+      </x:c>
+      <x:c r="F6" s="9" t="str">
+        <x:v>La app valida si un nombre usado no existe en esta lista.</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" t="str">
-        <x:v>GrupoActivoActual</x:v>
-      </x:c>
-      <x:c r="B7" s="21" t="e">
-        <x:f>RESIDUO(B3-1+ENTERO((B6-B2)/7),B1)+1</x:f>
-      </x:c>
-      <x:c r="C7" t="str">
-        <x:v>Grupo que sirve esta semana según la rotación.</x:v>
-      </x:c>
-      <x:c r="D7" t="str">
-        <x:v>No</x:v>
-      </x:c>
+        <x:v>Clara</x:v>
+      </x:c>
+      <x:c r="B7" t="str">
+        <x:v>Sí</x:v>
+      </x:c>
+      <x:c r="C7" t="str"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" t="str">
-        <x:v>FechaReferenciaSemana</x:v>
-      </x:c>
-      <x:c r="B8" s="20" t="n">
-        <x:f>B2</x:f>
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C8" t="str">
-        <x:v>Compatibilidad: igual a FechaBaseRotacion.</x:v>
-      </x:c>
-      <x:c r="D8" t="str">
-        <x:v>No</x:v>
-      </x:c>
+        <x:v>Pablo</x:v>
+      </x:c>
+      <x:c r="B8" t="str">
+        <x:v>Sí</x:v>
+      </x:c>
+      <x:c r="C8" t="str"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" t="str">
-        <x:v>GrupoReferencia</x:v>
-      </x:c>
-      <x:c r="B9" s="21" t="n">
-        <x:f>B3</x:f>
-        <x:v>46173</x:v>
-      </x:c>
-      <x:c r="C9" t="str">
-        <x:v>Compatibilidad: igual a GrupoBaseRotacion.</x:v>
-      </x:c>
-      <x:c r="D9" t="str">
-        <x:v>No</x:v>
-      </x:c>
+        <x:v>Abby</x:v>
+      </x:c>
+      <x:c r="B9" t="str">
+        <x:v>Sí</x:v>
+      </x:c>
+      <x:c r="C9" t="str"/>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" t="str">
+        <x:v>Vero</x:v>
+      </x:c>
+      <x:c r="B10" t="str">
+        <x:v>Sí</x:v>
+      </x:c>
+      <x:c r="C10" t="str"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" t="str">
+        <x:v>Karen</x:v>
+      </x:c>
+      <x:c r="B11" t="str">
+        <x:v>Sí</x:v>
+      </x:c>
+      <x:c r="C11" t="str"/>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" t="str">
+        <x:v>Kathy</x:v>
+      </x:c>
+      <x:c r="B12" t="str">
+        <x:v>Sí</x:v>
+      </x:c>
+      <x:c r="C12" t="str"/>
     </x:row>
   </x:sheetData>
+  <x:dataValidations count="1">
+    <x:dataValidation type="list" sqref="B2:B500">
+      <x:formula1>"Sí,No"</x:formula1>
+    </x:dataValidation>
+  </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf2b4ff0304024aa4"/>
-  </x:tableParts>
 </x:worksheet>
 </file>
--- a/calendario_iglesia_datos.xlsx
+++ b/calendario_iglesia_datos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jaop_\Documents\Oasis\Calendario Actividades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26DDD5C9-73BE-432D-BD72-5B0A99015E00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDE51B88-AB50-4E92-B199-0471A981B623}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13776" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Servidores" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
     <sheet name="Ventas Martes" sheetId="8" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Registro Servicios'!$A$1:$F$309</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Registro Servicios'!$A$1:$F$333</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,14 +39,14 @@
       </xcalcf:calcFeatures>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId11" roundtripDataChecksum="YucdZtZsV39OxxxUhzVJE0ptMpC3BjIuyB4OHVYAThc="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId12" roundtripDataChecksum="+0o1foaWuJX+bLYdk27MnEIHBlG76BUpmGPgdgIeqRA="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1557" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1525" uniqueCount="166">
   <si>
     <t>Servidor</t>
   </si>
@@ -246,6 +246,9 @@
     <t>Reunión</t>
   </si>
   <si>
+    <t>Ventas Martes</t>
+  </si>
+  <si>
     <t>Estado</t>
   </si>
   <si>
@@ -360,18 +363,6 @@
     <t>Clara Alvarado</t>
   </si>
   <si>
-    <t>Débora Quiroa</t>
-  </si>
-  <si>
-    <t>Pastora Ester</t>
-  </si>
-  <si>
-    <t>Cristy González</t>
-  </si>
-  <si>
-    <t>Jorge Porix</t>
-  </si>
-  <si>
     <t>Reunión de Coordinadoras</t>
   </si>
   <si>
@@ -400,6 +391,24 @@
   </si>
   <si>
     <t>Reunión de Intercesión</t>
+  </si>
+  <si>
+    <t>Grupo 2</t>
+  </si>
+  <si>
+    <t>Grupo 3</t>
+  </si>
+  <si>
+    <t>Grupo 4</t>
+  </si>
+  <si>
+    <t>Grupo 5</t>
+  </si>
+  <si>
+    <t>Grupo 6</t>
+  </si>
+  <si>
+    <t>Grupo 1</t>
   </si>
   <si>
     <t>Parametro</t>
@@ -501,6 +510,12 @@
     <t>La app valida si un nombre usado no existe en esta lista.</t>
   </si>
   <si>
+    <t>Jorge Porix</t>
+  </si>
+  <si>
+    <t>Cristy González</t>
+  </si>
+  <si>
     <t>Hansi Villatoro</t>
   </si>
   <si>
@@ -510,169 +525,25 @@
     <t>Valentina Villatoro</t>
   </si>
   <si>
-    <t>Ventas Martes</t>
+    <t>Débora Quiroa</t>
   </si>
   <si>
-    <t>Amalia</t>
+    <t>Pastora Ester</t>
   </si>
   <si>
-    <t>Grupo 1</t>
+    <t>Clara Echeverria</t>
   </si>
   <si>
-    <t>Elisa L</t>
+    <t>Veronica Polanco</t>
   </si>
   <si>
-    <t>Fabiola</t>
+    <t>Debora Quiroa</t>
   </si>
   <si>
-    <t>Heidy</t>
+    <t>Libi de Ochoa</t>
   </si>
   <si>
-    <t>Damaris</t>
-  </si>
-  <si>
-    <t>Grupo 2</t>
-  </si>
-  <si>
-    <t>Marina</t>
-  </si>
-  <si>
-    <t>Libi</t>
-  </si>
-  <si>
-    <t>Marines</t>
-  </si>
-  <si>
-    <t>Grupo 3</t>
-  </si>
-  <si>
-    <t>Yoaida</t>
-  </si>
-  <si>
-    <t>Elisabeth</t>
-  </si>
-  <si>
-    <t>Debora</t>
-  </si>
-  <si>
-    <t>Karen V</t>
-  </si>
-  <si>
-    <t>Grupo 4</t>
-  </si>
-  <si>
-    <t>Clara Ech</t>
-  </si>
-  <si>
-    <t>Vero</t>
-  </si>
-  <si>
-    <t>P Esther</t>
-  </si>
-  <si>
-    <t>Grupo 5</t>
-  </si>
-  <si>
-    <t>Silvia</t>
-  </si>
-  <si>
-    <t>Clarita</t>
-  </si>
-  <si>
-    <t>Yani</t>
-  </si>
-  <si>
-    <t>Victor</t>
-  </si>
-  <si>
-    <t>Grupo 6</t>
-  </si>
-  <si>
-    <t>Maura</t>
-  </si>
-  <si>
-    <t>Pablo</t>
-  </si>
-  <si>
-    <t>Eli</t>
-  </si>
-  <si>
-    <t>2026-07-07</t>
-  </si>
-  <si>
-    <t>2026-07-14</t>
-  </si>
-  <si>
-    <t>2026-07-21</t>
-  </si>
-  <si>
-    <t>2026-07-28</t>
-  </si>
-  <si>
-    <t>2026-08-04</t>
-  </si>
-  <si>
-    <t>2026-08-11</t>
-  </si>
-  <si>
-    <t>2026-08-18</t>
-  </si>
-  <si>
-    <t>2026-08-25</t>
-  </si>
-  <si>
-    <t>2026-09-01</t>
-  </si>
-  <si>
-    <t>2026-09-08</t>
-  </si>
-  <si>
-    <t>2026-09-15</t>
-  </si>
-  <si>
-    <t>2026-09-22</t>
-  </si>
-  <si>
-    <t>2026-09-29</t>
-  </si>
-  <si>
-    <t>2026-10-06</t>
-  </si>
-  <si>
-    <t>2026-10-13</t>
-  </si>
-  <si>
-    <t>2026-10-20</t>
-  </si>
-  <si>
-    <t>2026-10-27</t>
-  </si>
-  <si>
-    <t>2026-11-03</t>
-  </si>
-  <si>
-    <t>2026-11-10</t>
-  </si>
-  <si>
-    <t>2026-11-17</t>
-  </si>
-  <si>
-    <t>2026-11-24</t>
-  </si>
-  <si>
-    <t>2026-12-01</t>
-  </si>
-  <si>
-    <t>2026-12-08</t>
-  </si>
-  <si>
-    <t>2026-12-15</t>
-  </si>
-  <si>
-    <t>2026-12-22</t>
-  </si>
-  <si>
-    <t>2026-12-29</t>
+    <t>Pastora Esther</t>
   </si>
 </sst>
 </file>
@@ -702,12 +573,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Carlito"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Carlito"/>
     </font>
@@ -716,10 +581,15 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Carlito"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -734,8 +604,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor theme="4"/>
+        <fgColor rgb="FF156082"/>
+        <bgColor rgb="FF156082"/>
       </patternFill>
     </fill>
     <fill>
@@ -748,6 +618,12 @@
       <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor theme="0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFC1E4F5"/>
       </patternFill>
     </fill>
   </fills>
@@ -785,27 +661,25 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -817,8 +691,10 @@
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4783,7 +4659,7 @@
     </row>
     <row r="12" spans="1:26" ht="13.5" customHeight="1">
       <c r="A12" s="4" t="s">
-        <v>154</v>
+        <v>66</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>52</v>
@@ -7272,27 +7148,27 @@
   <sheetData>
     <row r="1" spans="1:1" ht="13.5" customHeight="1">
       <c r="A1" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="13.5" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="13.5" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="13.5" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:1" ht="13.5" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="13.5" customHeight="1"/>
@@ -8311,15 +8187,15 @@
   <sheetData>
     <row r="1" spans="1:2" ht="13.5" customHeight="1">
       <c r="A1" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="13.5" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B2" s="3">
         <v>1</v>
@@ -8327,7 +8203,7 @@
     </row>
     <row r="3" spans="1:2" ht="13.5" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B3" s="3">
         <v>2</v>
@@ -8335,7 +8211,7 @@
     </row>
     <row r="4" spans="1:2" ht="13.5" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B4" s="3">
         <v>3</v>
@@ -8343,7 +8219,7 @@
     </row>
     <row r="5" spans="1:2" ht="13.5" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B5" s="3">
         <v>4</v>
@@ -8351,7 +8227,7 @@
     </row>
     <row r="6" spans="1:2" ht="13.5" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B6" s="3">
         <v>5</v>
@@ -8359,7 +8235,7 @@
     </row>
     <row r="7" spans="1:2" ht="13.5" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B7" s="3">
         <v>6</v>
@@ -8367,7 +8243,7 @@
     </row>
     <row r="8" spans="1:2" ht="13.5" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B8" s="3">
         <v>7</v>
@@ -8375,7 +8251,7 @@
     </row>
     <row r="9" spans="1:2" ht="13.5" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B9" s="3">
         <v>8</v>
@@ -8383,7 +8259,7 @@
     </row>
     <row r="10" spans="1:2" ht="13.5" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B10" s="3">
         <v>9</v>
@@ -8391,7 +8267,7 @@
     </row>
     <row r="11" spans="1:2" ht="13.5" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B11" s="3">
         <v>10</v>
@@ -8399,7 +8275,7 @@
     </row>
     <row r="12" spans="1:2" ht="13.5" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B12" s="3">
         <v>11</v>
@@ -8407,7 +8283,7 @@
     </row>
     <row r="13" spans="1:2" ht="13.5" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B13" s="3">
         <v>12</v>
@@ -9411,44 +9287,44 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:Z858"/>
+  <dimension ref="A1:Z830"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.59765625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="10.19921875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.09765625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.3984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.8984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="32.19921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.19921875" customWidth="1"/>
+    <col min="2" max="2" width="16.09765625" customWidth="1"/>
+    <col min="3" max="3" width="20.3984375" customWidth="1"/>
+    <col min="4" max="4" width="18.5" customWidth="1"/>
+    <col min="5" max="5" width="10.8984375" customWidth="1"/>
+    <col min="6" max="6" width="32.19921875" customWidth="1"/>
     <col min="7" max="7" width="8.69921875" customWidth="1"/>
-    <col min="8" max="8" width="17" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="27" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17" customWidth="1"/>
+    <col min="9" max="9" width="27" customWidth="1"/>
     <col min="10" max="10" width="28" customWidth="1"/>
     <col min="11" max="26" width="8.69921875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="13.5" customHeight="1">
       <c r="A1" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D1" s="6" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G1" s="2"/>
       <c r="H1" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
@@ -9483,14 +9359,14 @@
         <v>32</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F2" s="8"/>
       <c r="H2" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J2" s="3"/>
     </row>
@@ -9508,14 +9384,14 @@
         <v>16</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F3" s="10"/>
       <c r="H3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J3" s="3"/>
     </row>
@@ -9533,14 +9409,14 @@
         <v>25</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F4" s="8"/>
       <c r="H4" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J4" s="3"/>
     </row>
@@ -9558,14 +9434,14 @@
         <v>37</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F5" s="10"/>
       <c r="H5" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J5" s="3"/>
     </row>
@@ -9580,17 +9456,17 @@
         <v>56</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F6" s="8"/>
       <c r="H6" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="J6" s="3"/>
     </row>
@@ -9608,7 +9484,7 @@
         <v>24</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F7" s="10"/>
     </row>
@@ -9626,7 +9502,7 @@
         <v>39</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F8" s="8"/>
     </row>
@@ -9644,7 +9520,7 @@
         <v>6</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F9" s="10"/>
     </row>
@@ -9662,7 +9538,7 @@
         <v>34</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F10" s="8"/>
     </row>
@@ -9680,7 +9556,7 @@
         <v>16</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F11" s="10"/>
     </row>
@@ -9698,7 +9574,7 @@
         <v>25</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F12" s="8"/>
     </row>
@@ -9716,7 +9592,7 @@
         <v>7</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F13" s="10"/>
     </row>
@@ -9734,7 +9610,7 @@
         <v>14</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F14" s="8"/>
     </row>
@@ -9752,7 +9628,7 @@
         <v>8</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F15" s="10"/>
     </row>
@@ -9770,7 +9646,7 @@
         <v>4</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F16" s="8"/>
     </row>
@@ -9785,10 +9661,10 @@
         <v>56</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F17" s="10"/>
     </row>
@@ -9806,7 +9682,7 @@
         <v>25</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F18" s="8"/>
     </row>
@@ -9824,7 +9700,7 @@
         <v>17</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F19" s="10"/>
     </row>
@@ -9842,7 +9718,7 @@
         <v>28</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F20" s="8"/>
     </row>
@@ -9860,7 +9736,7 @@
         <v>6</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F21" s="10"/>
     </row>
@@ -9878,7 +9754,7 @@
         <v>13</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F22" s="8"/>
     </row>
@@ -9896,7 +9772,7 @@
         <v>51</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F23" s="10"/>
     </row>
@@ -9914,7 +9790,7 @@
         <v>19</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F24" s="8"/>
     </row>
@@ -9932,7 +9808,7 @@
         <v>6</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F25" s="10"/>
     </row>
@@ -9950,7 +9826,7 @@
         <v>51</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F26" s="8"/>
     </row>
@@ -9968,7 +9844,7 @@
         <v>13</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F27" s="10"/>
     </row>
@@ -9986,7 +9862,7 @@
         <v>13</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F28" s="8"/>
     </row>
@@ -10004,7 +9880,7 @@
         <v>14</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F29" s="10"/>
     </row>
@@ -10020,10 +9896,10 @@
       </c>
       <c r="D30" s="8"/>
       <c r="E30" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="13.5" customHeight="1">
@@ -10038,10 +9914,10 @@
       </c>
       <c r="D31" s="10"/>
       <c r="E31" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F31" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="13.5" customHeight="1">
@@ -10056,10 +9932,10 @@
       </c>
       <c r="D32" s="8"/>
       <c r="E32" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="13.5" customHeight="1">
@@ -10074,10 +9950,10 @@
       </c>
       <c r="D33" s="10"/>
       <c r="E33" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F33" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="13.5" customHeight="1">
@@ -10092,7 +9968,7 @@
       </c>
       <c r="D34" s="8"/>
       <c r="E34" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F34" s="8"/>
     </row>
@@ -10110,7 +9986,7 @@
         <v>34</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F35" s="10"/>
     </row>
@@ -10128,7 +10004,7 @@
         <v>16</v>
       </c>
       <c r="E36" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F36" s="8"/>
     </row>
@@ -10143,10 +10019,10 @@
         <v>56</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F37" s="10"/>
     </row>
@@ -10164,7 +10040,7 @@
         <v>25</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F38" s="8"/>
     </row>
@@ -10179,10 +10055,10 @@
         <v>56</v>
       </c>
       <c r="D39" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F39" s="10"/>
     </row>
@@ -10200,7 +10076,7 @@
         <v>37</v>
       </c>
       <c r="E40" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F40" s="8"/>
     </row>
@@ -10215,10 +10091,10 @@
         <v>56</v>
       </c>
       <c r="D41" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F41" s="10"/>
     </row>
@@ -10236,7 +10112,7 @@
         <v>24</v>
       </c>
       <c r="E42" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F42" s="8"/>
     </row>
@@ -10254,7 +10130,7 @@
         <v>28</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F43" s="10"/>
     </row>
@@ -10272,7 +10148,7 @@
         <v>13</v>
       </c>
       <c r="E44" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F44" s="8"/>
     </row>
@@ -10290,7 +10166,7 @@
         <v>32</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F45" s="10"/>
     </row>
@@ -10308,7 +10184,7 @@
         <v>34</v>
       </c>
       <c r="E46" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F46" s="8"/>
     </row>
@@ -10323,10 +10199,10 @@
         <v>56</v>
       </c>
       <c r="D47" s="10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F47" s="10"/>
     </row>
@@ -10344,7 +10220,7 @@
         <v>25</v>
       </c>
       <c r="E48" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F48" s="8"/>
     </row>
@@ -10362,7 +10238,7 @@
         <v>37</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F49" s="10"/>
     </row>
@@ -10377,10 +10253,10 @@
         <v>56</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E50" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F50" s="8"/>
     </row>
@@ -10398,7 +10274,7 @@
         <v>17</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F51" s="10"/>
     </row>
@@ -10416,7 +10292,7 @@
         <v>39</v>
       </c>
       <c r="E52" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F52" s="8"/>
     </row>
@@ -10434,7 +10310,7 @@
         <v>13</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F53" s="10"/>
     </row>
@@ -10452,7 +10328,7 @@
         <v>25</v>
       </c>
       <c r="E54" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F54" s="8"/>
     </row>
@@ -10467,10 +10343,10 @@
         <v>56</v>
       </c>
       <c r="D55" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F55" s="10"/>
     </row>
@@ -10488,7 +10364,7 @@
         <v>17</v>
       </c>
       <c r="E56" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F56" s="8"/>
     </row>
@@ -10506,7 +10382,7 @@
         <v>16</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F57" s="10"/>
     </row>
@@ -10524,7 +10400,7 @@
         <v>37</v>
       </c>
       <c r="E58" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F58" s="8"/>
     </row>
@@ -10539,10 +10415,10 @@
         <v>56</v>
       </c>
       <c r="D59" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F59" s="10"/>
     </row>
@@ -10560,7 +10436,7 @@
         <v>39</v>
       </c>
       <c r="E60" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F60" s="8"/>
     </row>
@@ -10578,7 +10454,7 @@
         <v>19</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F61" s="10"/>
     </row>
@@ -10596,7 +10472,7 @@
         <v>28</v>
       </c>
       <c r="E62" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F62" s="8"/>
     </row>
@@ -10614,7 +10490,7 @@
         <v>4</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F63" s="10"/>
     </row>
@@ -10629,10 +10505,10 @@
         <v>56</v>
       </c>
       <c r="D64" s="8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E64" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F64" s="8"/>
     </row>
@@ -10650,7 +10526,7 @@
         <v>25</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F65" s="10"/>
     </row>
@@ -10668,7 +10544,7 @@
         <v>37</v>
       </c>
       <c r="E66" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F66" s="8"/>
     </row>
@@ -10683,10 +10559,10 @@
         <v>56</v>
       </c>
       <c r="D67" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F67" s="10"/>
     </row>
@@ -10704,7 +10580,7 @@
         <v>24</v>
       </c>
       <c r="E68" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F68" s="8"/>
     </row>
@@ -10722,7 +10598,7 @@
         <v>13</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F69" s="10"/>
     </row>
@@ -10740,7 +10616,7 @@
         <v>28</v>
       </c>
       <c r="E70" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F70" s="8"/>
     </row>
@@ -10758,7 +10634,7 @@
         <v>32</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F71" s="10"/>
     </row>
@@ -10773,10 +10649,10 @@
         <v>56</v>
       </c>
       <c r="D72" s="8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E72" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F72" s="8"/>
     </row>
@@ -10794,7 +10670,7 @@
         <v>25</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F73" s="10"/>
     </row>
@@ -10812,7 +10688,7 @@
         <v>6</v>
       </c>
       <c r="E74" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F74" s="8"/>
     </row>
@@ -10830,7 +10706,7 @@
         <v>14</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F75" s="10"/>
     </row>
@@ -10848,7 +10724,7 @@
         <v>8</v>
       </c>
       <c r="E76" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F76" s="8"/>
     </row>
@@ -10866,7 +10742,7 @@
         <v>34</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F77" s="10"/>
     </row>
@@ -10881,10 +10757,10 @@
         <v>56</v>
       </c>
       <c r="D78" s="8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E78" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F78" s="8"/>
     </row>
@@ -10902,7 +10778,7 @@
         <v>25</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F79" s="10"/>
     </row>
@@ -10920,7 +10796,7 @@
         <v>37</v>
       </c>
       <c r="E80" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F80" s="8"/>
     </row>
@@ -10935,10 +10811,10 @@
         <v>56</v>
       </c>
       <c r="D81" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F81" s="10"/>
     </row>
@@ -10956,7 +10832,7 @@
         <v>24</v>
       </c>
       <c r="E82" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F82" s="8"/>
     </row>
@@ -10974,7 +10850,7 @@
         <v>6</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F83" s="10"/>
     </row>
@@ -10992,7 +10868,7 @@
         <v>7</v>
       </c>
       <c r="E84" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F84" s="8"/>
     </row>
@@ -11010,7 +10886,7 @@
         <v>32</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F85" s="10"/>
     </row>
@@ -11028,7 +10904,7 @@
         <v>16</v>
       </c>
       <c r="E86" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F86" s="8"/>
     </row>
@@ -11043,10 +10919,10 @@
         <v>56</v>
       </c>
       <c r="D87" s="10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F87" s="10"/>
     </row>
@@ -11061,10 +10937,10 @@
         <v>56</v>
       </c>
       <c r="D88" s="8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E88" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F88" s="8"/>
     </row>
@@ -11082,7 +10958,7 @@
         <v>37</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F89" s="10"/>
     </row>
@@ -11097,10 +10973,10 @@
         <v>56</v>
       </c>
       <c r="D90" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E90" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F90" s="8"/>
     </row>
@@ -11118,7 +10994,7 @@
         <v>39</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F91" s="10"/>
     </row>
@@ -11136,7 +11012,7 @@
         <v>17</v>
       </c>
       <c r="E92" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F92" s="8"/>
     </row>
@@ -11154,7 +11030,7 @@
         <v>8</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F93" s="10"/>
     </row>
@@ -11172,7 +11048,7 @@
         <v>34</v>
       </c>
       <c r="E94" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F94" s="8"/>
     </row>
@@ -11190,7 +11066,7 @@
         <v>16</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F95" s="10"/>
     </row>
@@ -11205,10 +11081,10 @@
         <v>56</v>
       </c>
       <c r="D96" s="8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E96" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F96" s="8"/>
     </row>
@@ -11226,7 +11102,7 @@
         <v>37</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F97" s="10"/>
     </row>
@@ -11241,10 +11117,10 @@
         <v>56</v>
       </c>
       <c r="D98" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E98" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F98" s="8"/>
     </row>
@@ -11262,7 +11138,7 @@
         <v>7</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F99" s="10"/>
     </row>
@@ -11280,7 +11156,7 @@
         <v>19</v>
       </c>
       <c r="E100" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F100" s="8"/>
     </row>
@@ -11298,7 +11174,7 @@
         <v>13</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F101" s="10"/>
     </row>
@@ -11316,7 +11192,7 @@
         <v>6</v>
       </c>
       <c r="E102" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F102" s="8"/>
     </row>
@@ -11331,10 +11207,10 @@
         <v>56</v>
       </c>
       <c r="D103" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F103" s="10"/>
     </row>
@@ -11349,10 +11225,10 @@
         <v>56</v>
       </c>
       <c r="D104" s="8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E104" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F104" s="8"/>
     </row>
@@ -11370,7 +11246,7 @@
         <v>16</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F105" s="10"/>
     </row>
@@ -11388,7 +11264,7 @@
         <v>37</v>
       </c>
       <c r="E106" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F106" s="8"/>
     </row>
@@ -11403,10 +11279,10 @@
         <v>56</v>
       </c>
       <c r="D107" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F107" s="10"/>
     </row>
@@ -11424,7 +11300,7 @@
         <v>17</v>
       </c>
       <c r="E108" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F108" s="8"/>
     </row>
@@ -11442,7 +11318,7 @@
         <v>8</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F109" s="10"/>
     </row>
@@ -11460,7 +11336,7 @@
         <v>7</v>
       </c>
       <c r="E110" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F110" s="8"/>
     </row>
@@ -11475,10 +11351,10 @@
         <v>56</v>
       </c>
       <c r="D111" s="10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F111" s="10"/>
     </row>
@@ -11493,10 +11369,10 @@
         <v>56</v>
       </c>
       <c r="D112" s="8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E112" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F112" s="8"/>
     </row>
@@ -11514,7 +11390,7 @@
         <v>25</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F113" s="10"/>
     </row>
@@ -11532,7 +11408,7 @@
         <v>37</v>
       </c>
       <c r="E114" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F114" s="8"/>
     </row>
@@ -11547,10 +11423,10 @@
         <v>56</v>
       </c>
       <c r="D115" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F115" s="10"/>
     </row>
@@ -11568,7 +11444,7 @@
         <v>4</v>
       </c>
       <c r="E116" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F116" s="8"/>
     </row>
@@ -11586,7 +11462,7 @@
         <v>24</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F117" s="10"/>
     </row>
@@ -11604,7 +11480,7 @@
         <v>19</v>
       </c>
       <c r="E118" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F118" s="8"/>
     </row>
@@ -11619,10 +11495,10 @@
         <v>56</v>
       </c>
       <c r="D119" s="10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F119" s="10"/>
     </row>
@@ -11640,7 +11516,7 @@
         <v>16</v>
       </c>
       <c r="E120" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F120" s="8"/>
     </row>
@@ -11658,7 +11534,7 @@
         <v>25</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F121" s="10"/>
     </row>
@@ -11676,7 +11552,7 @@
         <v>37</v>
       </c>
       <c r="E122" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F122" s="8"/>
     </row>
@@ -11691,10 +11567,10 @@
         <v>56</v>
       </c>
       <c r="D123" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F123" s="10"/>
     </row>
@@ -11712,7 +11588,7 @@
         <v>6</v>
       </c>
       <c r="E124" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F124" s="8"/>
     </row>
@@ -11730,7 +11606,7 @@
         <v>8</v>
       </c>
       <c r="E125" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F125" s="10"/>
     </row>
@@ -11748,7 +11624,7 @@
         <v>14</v>
       </c>
       <c r="E126" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F126" s="8"/>
     </row>
@@ -11766,7 +11642,7 @@
         <v>32</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F127" s="10"/>
     </row>
@@ -11784,7 +11660,7 @@
         <v>39</v>
       </c>
       <c r="E128" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F128" s="8"/>
     </row>
@@ -11802,7 +11678,7 @@
         <v>51</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F129" s="10"/>
     </row>
@@ -11820,7 +11696,7 @@
         <v>19</v>
       </c>
       <c r="E130" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F130" s="8"/>
     </row>
@@ -11838,7 +11714,7 @@
         <v>13</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F131" s="10"/>
     </row>
@@ -11856,7 +11732,7 @@
         <v>51</v>
       </c>
       <c r="E132" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F132" s="8"/>
     </row>
@@ -11874,7 +11750,7 @@
         <v>32</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F133" s="10"/>
     </row>
@@ -11892,7 +11768,7 @@
         <v>51</v>
       </c>
       <c r="E134" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F134" s="8"/>
     </row>
@@ -11910,7 +11786,7 @@
         <v>39</v>
       </c>
       <c r="E135" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F135" s="10"/>
     </row>
@@ -11928,7 +11804,7 @@
         <v>13</v>
       </c>
       <c r="E136" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F136" s="8"/>
     </row>
@@ -11946,7 +11822,7 @@
         <v>39</v>
       </c>
       <c r="E137" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F137" s="10"/>
     </row>
@@ -11964,7 +11840,7 @@
         <v>51</v>
       </c>
       <c r="E138" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F138" s="8"/>
     </row>
@@ -11982,7 +11858,7 @@
         <v>6</v>
       </c>
       <c r="E139" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F139" s="10"/>
     </row>
@@ -12000,7 +11876,7 @@
         <v>32</v>
       </c>
       <c r="E140" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F140" s="8"/>
     </row>
@@ -12018,7 +11894,7 @@
         <v>39</v>
       </c>
       <c r="E141" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F141" s="10"/>
     </row>
@@ -12036,7 +11912,7 @@
         <v>19</v>
       </c>
       <c r="E142" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F142" s="8"/>
     </row>
@@ -12054,7 +11930,7 @@
         <v>13</v>
       </c>
       <c r="E143" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F143" s="10"/>
     </row>
@@ -12072,7 +11948,7 @@
         <v>13</v>
       </c>
       <c r="E144" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F144" s="8"/>
     </row>
@@ -12090,7 +11966,7 @@
         <v>51</v>
       </c>
       <c r="E145" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F145" s="10"/>
     </row>
@@ -12108,7 +11984,7 @@
         <v>19</v>
       </c>
       <c r="E146" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F146" s="8"/>
     </row>
@@ -12126,7 +12002,7 @@
         <v>6</v>
       </c>
       <c r="E147" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F147" s="10"/>
     </row>
@@ -12144,7 +12020,7 @@
         <v>15</v>
       </c>
       <c r="E148" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F148" s="8"/>
     </row>
@@ -12162,7 +12038,7 @@
         <v>18</v>
       </c>
       <c r="E149" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F149" s="10"/>
     </row>
@@ -12180,7 +12056,7 @@
         <v>34</v>
       </c>
       <c r="E150" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F150" s="8"/>
     </row>
@@ -12198,7 +12074,7 @@
         <v>31</v>
       </c>
       <c r="E151" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F151" s="10"/>
     </row>
@@ -12216,7 +12092,7 @@
         <v>27</v>
       </c>
       <c r="E152" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F152" s="8"/>
     </row>
@@ -12234,7 +12110,7 @@
         <v>24</v>
       </c>
       <c r="E153" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F153" s="10"/>
     </row>
@@ -12252,7 +12128,7 @@
         <v>26</v>
       </c>
       <c r="E154" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F154" s="8"/>
     </row>
@@ -12270,7 +12146,7 @@
         <v>8</v>
       </c>
       <c r="E155" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F155" s="10"/>
     </row>
@@ -12281,14 +12157,14 @@
       <c r="B156" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="C156" s="12" t="s">
+      <c r="C156" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="D156" s="12" t="s">
+      <c r="D156" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="E156" s="12"/>
-      <c r="F156" s="13"/>
+      <c r="E156" s="11"/>
+      <c r="F156" s="11"/>
     </row>
     <row r="157" spans="1:6" ht="13.5" customHeight="1">
       <c r="A157" s="7">
@@ -12297,14 +12173,14 @@
       <c r="B157" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="C157" s="11" t="s">
+      <c r="C157" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="D157" s="11" t="s">
+      <c r="D157" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="E157" s="11"/>
-      <c r="F157" s="14"/>
+      <c r="E157" s="12"/>
+      <c r="F157" s="12"/>
     </row>
     <row r="158" spans="1:6" ht="13.5" customHeight="1">
       <c r="A158" s="9">
@@ -12313,14 +12189,14 @@
       <c r="B158" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="C158" s="12" t="s">
+      <c r="C158" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="D158" s="12" t="s">
+      <c r="D158" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="E158" s="12"/>
-      <c r="F158" s="13"/>
+      <c r="E158" s="11"/>
+      <c r="F158" s="11"/>
     </row>
     <row r="159" spans="1:6" ht="13.5" customHeight="1">
       <c r="A159" s="7">
@@ -12329,14 +12205,14 @@
       <c r="B159" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="C159" s="11" t="s">
+      <c r="C159" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="D159" s="11" t="s">
+      <c r="D159" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="E159" s="11"/>
-      <c r="F159" s="14"/>
+      <c r="E159" s="12"/>
+      <c r="F159" s="12"/>
     </row>
     <row r="160" spans="1:6" ht="13.5" customHeight="1">
       <c r="A160" s="9">
@@ -12345,14 +12221,14 @@
       <c r="B160" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="C160" s="12" t="s">
+      <c r="C160" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="D160" s="12" t="s">
+      <c r="D160" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="E160" s="12"/>
-      <c r="F160" s="13"/>
+      <c r="E160" s="11"/>
+      <c r="F160" s="11"/>
     </row>
     <row r="161" spans="1:6" ht="13.5" customHeight="1">
       <c r="A161" s="7">
@@ -12361,14 +12237,14 @@
       <c r="B161" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="C161" s="11" t="s">
+      <c r="C161" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="D161" s="11" t="s">
+      <c r="D161" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="E161" s="11"/>
-      <c r="F161" s="14"/>
+      <c r="E161" s="12"/>
+      <c r="F161" s="12"/>
     </row>
     <row r="162" spans="1:6" ht="13.5" customHeight="1">
       <c r="A162" s="9">
@@ -12377,14 +12253,14 @@
       <c r="B162" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="C162" s="12" t="s">
+      <c r="C162" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="D162" s="12" t="s">
+      <c r="D162" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="E162" s="12"/>
-      <c r="F162" s="13"/>
+      <c r="E162" s="11"/>
+      <c r="F162" s="11"/>
     </row>
     <row r="163" spans="1:6" ht="13.5" customHeight="1">
       <c r="A163" s="7">
@@ -12393,189 +12269,189 @@
       <c r="B163" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="C163" s="11" t="s">
+      <c r="C163" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="D163" s="11" t="s">
+      <c r="D163" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="E163" s="11"/>
-      <c r="F163" s="14"/>
+      <c r="E163" s="12"/>
+      <c r="F163" s="12"/>
     </row>
     <row r="164" spans="1:6" ht="13.5" customHeight="1">
       <c r="A164" s="9">
         <v>46192</v>
       </c>
-      <c r="B164" s="12" t="s">
+      <c r="B164" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="C164" s="12" t="s">
+      <c r="C164" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="D164" s="12"/>
-      <c r="E164" s="12"/>
-      <c r="F164" s="13" t="s">
-        <v>108</v>
+      <c r="D164" s="11"/>
+      <c r="E164" s="11"/>
+      <c r="F164" s="11" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="165" spans="1:6" ht="13.5" customHeight="1">
       <c r="A165" s="7">
         <v>46193</v>
       </c>
-      <c r="B165" s="11" t="s">
+      <c r="B165" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="C165" s="11" t="s">
+      <c r="C165" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="D165" s="11"/>
-      <c r="E165" s="11"/>
-      <c r="F165" s="14" t="s">
-        <v>109</v>
+      <c r="D165" s="12"/>
+      <c r="E165" s="12"/>
+      <c r="F165" s="12" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="166" spans="1:6" ht="13.5" customHeight="1">
       <c r="A166" s="9">
         <v>46195</v>
       </c>
-      <c r="B166" s="12" t="s">
+      <c r="B166" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="C166" s="12" t="s">
+      <c r="C166" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="D166" s="12"/>
-      <c r="E166" s="12"/>
-      <c r="F166" s="13" t="s">
-        <v>110</v>
+      <c r="D166" s="11"/>
+      <c r="E166" s="11"/>
+      <c r="F166" s="11" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="167" spans="1:6" ht="13.5" customHeight="1">
       <c r="A167" s="7">
         <v>46204</v>
       </c>
-      <c r="B167" s="11" t="s">
+      <c r="B167" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="C167" s="11" t="s">
+      <c r="C167" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="D167" s="11"/>
-      <c r="E167" s="11"/>
-      <c r="F167" s="14" t="s">
-        <v>100</v>
+      <c r="D167" s="12"/>
+      <c r="E167" s="12"/>
+      <c r="F167" s="12" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="168" spans="1:6" ht="13.5" customHeight="1">
       <c r="A168" s="9">
         <v>46189</v>
       </c>
-      <c r="B168" s="12" t="s">
+      <c r="B168" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="C168" s="12" t="s">
+      <c r="C168" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="D168" s="12"/>
-      <c r="E168" s="12"/>
-      <c r="F168" s="13" t="s">
-        <v>111</v>
+      <c r="D168" s="11"/>
+      <c r="E168" s="11"/>
+      <c r="F168" s="11" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="169" spans="1:6" ht="13.5" customHeight="1">
       <c r="A169" s="7">
         <v>46221</v>
       </c>
-      <c r="B169" s="11" t="s">
+      <c r="B169" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="C169" s="11" t="s">
+      <c r="C169" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="D169" s="11"/>
-      <c r="E169" s="11"/>
-      <c r="F169" s="14" t="s">
-        <v>112</v>
+      <c r="D169" s="12"/>
+      <c r="E169" s="12"/>
+      <c r="F169" s="12" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="170" spans="1:6" ht="13.5" customHeight="1">
       <c r="A170" s="9">
         <v>46201</v>
       </c>
-      <c r="B170" s="12" t="s">
+      <c r="B170" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="C170" s="12" t="s">
+      <c r="C170" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="D170" s="12"/>
-      <c r="E170" s="12"/>
-      <c r="F170" s="13" t="s">
-        <v>113</v>
+      <c r="D170" s="11"/>
+      <c r="E170" s="11"/>
+      <c r="F170" s="11" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="171" spans="1:6" ht="13.5" customHeight="1">
       <c r="A171" s="7">
         <v>46221</v>
       </c>
-      <c r="B171" s="11" t="s">
+      <c r="B171" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="C171" s="11" t="s">
+      <c r="C171" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="D171" s="11"/>
-      <c r="E171" s="11"/>
-      <c r="F171" s="14" t="s">
-        <v>114</v>
+      <c r="D171" s="12"/>
+      <c r="E171" s="12"/>
+      <c r="F171" s="12" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="172" spans="1:6" ht="13.5" customHeight="1">
       <c r="A172" s="9">
         <v>46228</v>
       </c>
-      <c r="B172" s="12" t="s">
+      <c r="B172" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="C172" s="12" t="s">
+      <c r="C172" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="D172" s="12"/>
-      <c r="E172" s="12"/>
-      <c r="F172" s="13" t="s">
-        <v>115</v>
+      <c r="D172" s="11"/>
+      <c r="E172" s="11"/>
+      <c r="F172" s="11" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="173" spans="1:6" ht="13.5" customHeight="1">
       <c r="A173" s="7">
         <v>46214</v>
       </c>
-      <c r="B173" s="11" t="s">
+      <c r="B173" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="C173" s="11" t="s">
+      <c r="C173" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="D173" s="11"/>
-      <c r="E173" s="11"/>
-      <c r="F173" s="14" t="s">
-        <v>116</v>
+      <c r="D173" s="12"/>
+      <c r="E173" s="12"/>
+      <c r="F173" s="12" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="174" spans="1:6" ht="13.5" customHeight="1">
       <c r="A174" s="9">
         <v>46190</v>
       </c>
-      <c r="B174" s="12" t="s">
+      <c r="B174" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="C174" s="12" t="s">
+      <c r="C174" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="D174" s="12"/>
-      <c r="E174" s="12"/>
-      <c r="F174" s="13" t="s">
-        <v>117</v>
+      <c r="D174" s="11"/>
+      <c r="E174" s="11"/>
+      <c r="F174" s="11" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="175" spans="1:6" ht="13.5" customHeight="1">
@@ -12588,11 +12464,11 @@
       <c r="C175" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D175" s="11" t="s">
+      <c r="D175" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="E175" s="11"/>
-      <c r="F175" s="14"/>
+      <c r="E175" s="12"/>
+      <c r="F175" s="12"/>
     </row>
     <row r="176" spans="1:6" ht="13.5" customHeight="1">
       <c r="A176" s="9">
@@ -12604,11 +12480,11 @@
       <c r="C176" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="D176" s="12" t="s">
-        <v>98</v>
-      </c>
-      <c r="E176" s="12"/>
-      <c r="F176" s="13"/>
+      <c r="D176" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="E176" s="11"/>
+      <c r="F176" s="11"/>
     </row>
     <row r="177" spans="1:6" ht="13.5" customHeight="1">
       <c r="A177" s="7">
@@ -12620,11 +12496,11 @@
       <c r="C177" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D177" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="E177" s="11"/>
-      <c r="F177" s="14"/>
+      <c r="D177" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="E177" s="12"/>
+      <c r="F177" s="12"/>
     </row>
     <row r="178" spans="1:6" ht="13.5" customHeight="1">
       <c r="A178" s="9">
@@ -12636,11 +12512,11 @@
       <c r="C178" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="D178" s="12" t="s">
+      <c r="D178" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="E178" s="12"/>
-      <c r="F178" s="13"/>
+      <c r="E178" s="11"/>
+      <c r="F178" s="11"/>
     </row>
     <row r="179" spans="1:6" ht="13.5" customHeight="1">
       <c r="A179" s="7">
@@ -12652,11 +12528,11 @@
       <c r="C179" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D179" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="E179" s="11"/>
-      <c r="F179" s="14"/>
+      <c r="D179" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E179" s="12"/>
+      <c r="F179" s="12"/>
     </row>
     <row r="180" spans="1:6" ht="13.5" customHeight="1">
       <c r="A180" s="9">
@@ -12668,11 +12544,11 @@
       <c r="C180" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="D180" s="12" t="s">
+      <c r="D180" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="E180" s="12"/>
-      <c r="F180" s="13"/>
+      <c r="E180" s="11"/>
+      <c r="F180" s="11"/>
     </row>
     <row r="181" spans="1:6" ht="13.5" customHeight="1">
       <c r="A181" s="7">
@@ -12684,11 +12560,11 @@
       <c r="C181" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D181" s="11" t="s">
+      <c r="D181" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="E181" s="11"/>
-      <c r="F181" s="14"/>
+      <c r="E181" s="12"/>
+      <c r="F181" s="12"/>
     </row>
     <row r="182" spans="1:6" ht="13.5" customHeight="1">
       <c r="A182" s="9">
@@ -12700,11 +12576,11 @@
       <c r="C182" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="D182" s="12" t="s">
+      <c r="D182" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="E182" s="12"/>
-      <c r="F182" s="13"/>
+      <c r="E182" s="11"/>
+      <c r="F182" s="11"/>
     </row>
     <row r="183" spans="1:6" ht="13.5" customHeight="1">
       <c r="A183" s="7">
@@ -12716,11 +12592,11 @@
       <c r="C183" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D183" s="11" t="s">
+      <c r="D183" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="E183" s="11"/>
-      <c r="F183" s="14"/>
+      <c r="E183" s="12"/>
+      <c r="F183" s="12"/>
     </row>
     <row r="184" spans="1:6" ht="13.5" customHeight="1">
       <c r="A184" s="9">
@@ -12732,11 +12608,11 @@
       <c r="C184" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="D184" s="12" t="s">
-        <v>98</v>
-      </c>
-      <c r="E184" s="12"/>
-      <c r="F184" s="13"/>
+      <c r="D184" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="E184" s="11"/>
+      <c r="F184" s="11"/>
     </row>
     <row r="185" spans="1:6" ht="13.5" customHeight="1">
       <c r="A185" s="7">
@@ -12748,11 +12624,11 @@
       <c r="C185" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D185" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="E185" s="11"/>
-      <c r="F185" s="14"/>
+      <c r="D185" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="E185" s="12"/>
+      <c r="F185" s="12"/>
     </row>
     <row r="186" spans="1:6" ht="13.5" customHeight="1">
       <c r="A186" s="9">
@@ -12764,11 +12640,11 @@
       <c r="C186" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="D186" s="12" t="s">
+      <c r="D186" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="E186" s="12"/>
-      <c r="F186" s="13"/>
+      <c r="E186" s="11"/>
+      <c r="F186" s="11"/>
     </row>
     <row r="187" spans="1:6" ht="13.5" customHeight="1">
       <c r="A187" s="7">
@@ -12780,11 +12656,11 @@
       <c r="C187" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D187" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="E187" s="11"/>
-      <c r="F187" s="14"/>
+      <c r="D187" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E187" s="12"/>
+      <c r="F187" s="12"/>
     </row>
     <row r="188" spans="1:6" ht="13.5" customHeight="1">
       <c r="A188" s="9">
@@ -12796,11 +12672,11 @@
       <c r="C188" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="D188" s="12" t="s">
+      <c r="D188" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="E188" s="12"/>
-      <c r="F188" s="13"/>
+      <c r="E188" s="11"/>
+      <c r="F188" s="11"/>
     </row>
     <row r="189" spans="1:6" ht="13.5" customHeight="1">
       <c r="A189" s="7">
@@ -12812,11 +12688,11 @@
       <c r="C189" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D189" s="11" t="s">
+      <c r="D189" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="E189" s="11"/>
-      <c r="F189" s="14"/>
+      <c r="E189" s="12"/>
+      <c r="F189" s="12"/>
     </row>
     <row r="190" spans="1:6" ht="13.5" customHeight="1">
       <c r="A190" s="9">
@@ -12828,11 +12704,11 @@
       <c r="C190" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="D190" s="15" t="s">
+      <c r="D190" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="E190" s="12"/>
-      <c r="F190" s="13"/>
+      <c r="E190" s="11"/>
+      <c r="F190" s="11"/>
     </row>
     <row r="191" spans="1:6" ht="13.5" customHeight="1">
       <c r="A191" s="7">
@@ -12844,11 +12720,11 @@
       <c r="C191" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D191" s="11" t="s">
+      <c r="D191" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="E191" s="11"/>
-      <c r="F191" s="14"/>
+      <c r="E191" s="12"/>
+      <c r="F191" s="12"/>
     </row>
     <row r="192" spans="1:6" ht="13.5" customHeight="1">
       <c r="A192" s="9">
@@ -12860,11 +12736,11 @@
       <c r="C192" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="D192" s="12" t="s">
+      <c r="D192" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="E192" s="12"/>
-      <c r="F192" s="13"/>
+      <c r="E192" s="11"/>
+      <c r="F192" s="11"/>
     </row>
     <row r="193" spans="1:6" ht="13.5" customHeight="1">
       <c r="A193" s="7">
@@ -12876,11 +12752,11 @@
       <c r="C193" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D193" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="E193" s="11"/>
-      <c r="F193" s="14"/>
+      <c r="D193" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="E193" s="12"/>
+      <c r="F193" s="12"/>
     </row>
     <row r="194" spans="1:6" ht="13.5" customHeight="1">
       <c r="A194" s="9">
@@ -12892,11 +12768,11 @@
       <c r="C194" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="D194" s="12" t="s">
+      <c r="D194" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="E194" s="12"/>
-      <c r="F194" s="13"/>
+      <c r="E194" s="11"/>
+      <c r="F194" s="11"/>
     </row>
     <row r="195" spans="1:6" ht="13.5" customHeight="1">
       <c r="A195" s="7">
@@ -12908,11 +12784,11 @@
       <c r="C195" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D195" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="E195" s="11"/>
-      <c r="F195" s="14"/>
+      <c r="D195" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E195" s="12"/>
+      <c r="F195" s="12"/>
     </row>
     <row r="196" spans="1:6" ht="13.5" customHeight="1">
       <c r="A196" s="9">
@@ -12924,11 +12800,11 @@
       <c r="C196" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="D196" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="E196" s="12"/>
-      <c r="F196" s="13"/>
+      <c r="D196" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="E196" s="11"/>
+      <c r="F196" s="11"/>
     </row>
     <row r="197" spans="1:6" ht="13.5" customHeight="1">
       <c r="A197" s="7">
@@ -12940,11 +12816,11 @@
       <c r="C197" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D197" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="E197" s="11"/>
-      <c r="F197" s="14"/>
+      <c r="D197" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="E197" s="12"/>
+      <c r="F197" s="12"/>
     </row>
     <row r="198" spans="1:6" ht="13.5" customHeight="1">
       <c r="A198" s="9">
@@ -12956,11 +12832,11 @@
       <c r="C198" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="D198" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="E198" s="12"/>
-      <c r="F198" s="13"/>
+      <c r="D198" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="E198" s="11"/>
+      <c r="F198" s="11"/>
     </row>
     <row r="199" spans="1:6" ht="13.5" customHeight="1">
       <c r="A199" s="7">
@@ -12972,11 +12848,11 @@
       <c r="C199" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D199" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="E199" s="11"/>
-      <c r="F199" s="14"/>
+      <c r="D199" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="E199" s="12"/>
+      <c r="F199" s="12"/>
     </row>
     <row r="200" spans="1:6" ht="13.5" customHeight="1">
       <c r="A200" s="9">
@@ -12988,11 +12864,11 @@
       <c r="C200" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="D200" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="E200" s="12"/>
-      <c r="F200" s="13"/>
+      <c r="D200" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="E200" s="11"/>
+      <c r="F200" s="11"/>
     </row>
     <row r="201" spans="1:6" ht="13.5" customHeight="1">
       <c r="A201" s="7">
@@ -13004,11 +12880,11 @@
       <c r="C201" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D201" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="E201" s="11"/>
-      <c r="F201" s="14"/>
+      <c r="D201" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="E201" s="12"/>
+      <c r="F201" s="12"/>
     </row>
     <row r="202" spans="1:6" ht="13.5" customHeight="1">
       <c r="A202" s="9">
@@ -13020,11 +12896,11 @@
       <c r="C202" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="D202" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="E202" s="12"/>
-      <c r="F202" s="13"/>
+      <c r="D202" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="E202" s="11"/>
+      <c r="F202" s="11"/>
     </row>
     <row r="203" spans="1:6" ht="13.5" customHeight="1">
       <c r="A203" s="7">
@@ -13036,11 +12912,11 @@
       <c r="C203" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D203" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="E203" s="11"/>
-      <c r="F203" s="14"/>
+      <c r="D203" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E203" s="12"/>
+      <c r="F203" s="12"/>
     </row>
     <row r="204" spans="1:6" ht="13.5" customHeight="1">
       <c r="A204" s="9">
@@ -13052,15 +12928,15 @@
       <c r="C204" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="D204" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="E204" s="12"/>
-      <c r="F204" s="13"/>
+      <c r="D204" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="E204" s="11"/>
+      <c r="F204" s="11"/>
     </row>
     <row r="205" spans="1:6" ht="13.5" customHeight="1">
       <c r="A205" s="7">
-        <v>46212</v>
+        <v>46215</v>
       </c>
       <c r="B205" s="8" t="s">
         <v>52</v>
@@ -13068,15 +12944,15 @@
       <c r="C205" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D205" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="E205" s="11"/>
-      <c r="F205" s="14"/>
+      <c r="D205" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="E205" s="12"/>
+      <c r="F205" s="12"/>
     </row>
     <row r="206" spans="1:6" ht="13.5" customHeight="1">
       <c r="A206" s="9">
-        <v>46212</v>
+        <v>46215</v>
       </c>
       <c r="B206" s="10" t="s">
         <v>52</v>
@@ -13084,11 +12960,11 @@
       <c r="C206" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="D206" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="E206" s="12"/>
-      <c r="F206" s="13"/>
+      <c r="D206" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="E206" s="11"/>
+      <c r="F206" s="11"/>
     </row>
     <row r="207" spans="1:6" ht="13.5" customHeight="1">
       <c r="A207" s="7">
@@ -13100,11 +12976,11 @@
       <c r="C207" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D207" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="E207" s="11"/>
-      <c r="F207" s="14"/>
+      <c r="D207" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="E207" s="12"/>
+      <c r="F207" s="12"/>
     </row>
     <row r="208" spans="1:6" ht="13.5" customHeight="1">
       <c r="A208" s="9">
@@ -13116,11 +12992,11 @@
       <c r="C208" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="D208" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="E208" s="12"/>
-      <c r="F208" s="13"/>
+      <c r="D208" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="E208" s="11"/>
+      <c r="F208" s="11"/>
     </row>
     <row r="209" spans="1:6" ht="13.5" customHeight="1">
       <c r="A209" s="7">
@@ -13132,11 +13008,11 @@
       <c r="C209" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D209" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="E209" s="11"/>
-      <c r="F209" s="14"/>
+      <c r="D209" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E209" s="12"/>
+      <c r="F209" s="12"/>
     </row>
     <row r="210" spans="1:6" ht="13.5" customHeight="1">
       <c r="A210" s="9">
@@ -13148,11 +13024,11 @@
       <c r="C210" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="D210" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="E210" s="12"/>
-      <c r="F210" s="13"/>
+      <c r="D210" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E210" s="11"/>
+      <c r="F210" s="11"/>
     </row>
     <row r="211" spans="1:6" ht="13.5" customHeight="1">
       <c r="A211" s="7">
@@ -13164,11 +13040,11 @@
       <c r="C211" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D211" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="E211" s="11"/>
-      <c r="F211" s="14"/>
+      <c r="D211" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E211" s="12"/>
+      <c r="F211" s="12"/>
     </row>
     <row r="212" spans="1:6" ht="13.5" customHeight="1">
       <c r="A212" s="9">
@@ -13180,15 +13056,15 @@
       <c r="C212" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="D212" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="E212" s="12"/>
-      <c r="F212" s="13"/>
+      <c r="D212" s="23" t="s">
+        <v>99</v>
+      </c>
+      <c r="E212" s="11"/>
+      <c r="F212" s="11"/>
     </row>
     <row r="213" spans="1:6" ht="13.5" customHeight="1">
       <c r="A213" s="7">
-        <v>46215</v>
+        <v>46217</v>
       </c>
       <c r="B213" s="8" t="s">
         <v>52</v>
@@ -13196,15 +13072,15 @@
       <c r="C213" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D213" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="E213" s="11"/>
-      <c r="F213" s="14"/>
+      <c r="D213" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="E213" s="12"/>
+      <c r="F213" s="12"/>
     </row>
     <row r="214" spans="1:6" ht="13.5" customHeight="1">
       <c r="A214" s="9">
-        <v>46215</v>
+        <v>46217</v>
       </c>
       <c r="B214" s="10" t="s">
         <v>52</v>
@@ -13212,11 +13088,11 @@
       <c r="C214" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="D214" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="E214" s="12"/>
-      <c r="F214" s="13"/>
+      <c r="D214" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="E214" s="11"/>
+      <c r="F214" s="11"/>
     </row>
     <row r="215" spans="1:6" ht="13.5" customHeight="1">
       <c r="A215" s="7">
@@ -13228,11 +13104,11 @@
       <c r="C215" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D215" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="E215" s="11"/>
-      <c r="F215" s="14"/>
+      <c r="D215" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="E215" s="12"/>
+      <c r="F215" s="12"/>
     </row>
     <row r="216" spans="1:6" ht="13.5" customHeight="1">
       <c r="A216" s="9">
@@ -13244,11 +13120,11 @@
       <c r="C216" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="D216" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="E216" s="12"/>
-      <c r="F216" s="13"/>
+      <c r="D216" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="E216" s="11"/>
+      <c r="F216" s="11"/>
     </row>
     <row r="217" spans="1:6" ht="13.5" customHeight="1">
       <c r="A217" s="7">
@@ -13260,11 +13136,11 @@
       <c r="C217" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D217" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="E217" s="11"/>
-      <c r="F217" s="14"/>
+      <c r="D217" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E217" s="12"/>
+      <c r="F217" s="12"/>
     </row>
     <row r="218" spans="1:6" ht="13.5" customHeight="1">
       <c r="A218" s="9">
@@ -13276,11 +13152,11 @@
       <c r="C218" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="D218" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="E218" s="12"/>
-      <c r="F218" s="13"/>
+      <c r="D218" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="E218" s="11"/>
+      <c r="F218" s="11"/>
     </row>
     <row r="219" spans="1:6" ht="13.5" customHeight="1">
       <c r="A219" s="7">
@@ -13292,11 +13168,11 @@
       <c r="C219" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D219" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="E219" s="11"/>
-      <c r="F219" s="14"/>
+      <c r="D219" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="E219" s="12"/>
+      <c r="F219" s="12"/>
     </row>
     <row r="220" spans="1:6" ht="13.5" customHeight="1">
       <c r="A220" s="9">
@@ -13308,15 +13184,15 @@
       <c r="C220" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="D220" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E220" s="12"/>
-      <c r="F220" s="13"/>
+      <c r="D220" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="E220" s="11"/>
+      <c r="F220" s="11"/>
     </row>
     <row r="221" spans="1:6" ht="13.5" customHeight="1">
       <c r="A221" s="7">
-        <v>46217</v>
+        <v>46219</v>
       </c>
       <c r="B221" s="8" t="s">
         <v>52</v>
@@ -13324,15 +13200,15 @@
       <c r="C221" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D221" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="E221" s="11"/>
-      <c r="F221" s="14"/>
+      <c r="D221" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="E221" s="12"/>
+      <c r="F221" s="12"/>
     </row>
     <row r="222" spans="1:6" ht="13.5" customHeight="1">
       <c r="A222" s="9">
-        <v>46217</v>
+        <v>46219</v>
       </c>
       <c r="B222" s="10" t="s">
         <v>52</v>
@@ -13340,11 +13216,11 @@
       <c r="C222" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="D222" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E222" s="12"/>
-      <c r="F222" s="13"/>
+      <c r="D222" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="E222" s="11"/>
+      <c r="F222" s="11"/>
     </row>
     <row r="223" spans="1:6" ht="13.5" customHeight="1">
       <c r="A223" s="7">
@@ -13356,11 +13232,11 @@
       <c r="C223" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D223" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="E223" s="11"/>
-      <c r="F223" s="14"/>
+      <c r="D223" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="E223" s="12"/>
+      <c r="F223" s="12"/>
     </row>
     <row r="224" spans="1:6" ht="13.5" customHeight="1">
       <c r="A224" s="9">
@@ -13372,11 +13248,11 @@
       <c r="C224" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="D224" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="E224" s="12"/>
-      <c r="F224" s="13"/>
+      <c r="D224" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="E224" s="11"/>
+      <c r="F224" s="11"/>
     </row>
     <row r="225" spans="1:6" ht="13.5" customHeight="1">
       <c r="A225" s="7">
@@ -13388,11 +13264,11 @@
       <c r="C225" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D225" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="E225" s="11"/>
-      <c r="F225" s="14"/>
+      <c r="D225" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E225" s="12"/>
+      <c r="F225" s="12"/>
     </row>
     <row r="226" spans="1:6" ht="13.5" customHeight="1">
       <c r="A226" s="9">
@@ -13404,11 +13280,11 @@
       <c r="C226" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="D226" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="E226" s="12"/>
-      <c r="F226" s="13"/>
+      <c r="D226" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E226" s="11"/>
+      <c r="F226" s="11"/>
     </row>
     <row r="227" spans="1:6" ht="13.5" customHeight="1">
       <c r="A227" s="7">
@@ -13420,11 +13296,11 @@
       <c r="C227" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D227" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="E227" s="11"/>
-      <c r="F227" s="14"/>
+      <c r="D227" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="E227" s="12"/>
+      <c r="F227" s="12"/>
     </row>
     <row r="228" spans="1:6" ht="13.5" customHeight="1">
       <c r="A228" s="9">
@@ -13436,15 +13312,15 @@
       <c r="C228" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="D228" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E228" s="12"/>
-      <c r="F228" s="13"/>
+      <c r="D228" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="E228" s="11"/>
+      <c r="F228" s="11"/>
     </row>
     <row r="229" spans="1:6" ht="13.5" customHeight="1">
       <c r="A229" s="7">
-        <v>46219</v>
+        <v>46222</v>
       </c>
       <c r="B229" s="8" t="s">
         <v>52</v>
@@ -13452,15 +13328,15 @@
       <c r="C229" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D229" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="E229" s="11"/>
-      <c r="F229" s="14"/>
+      <c r="D229" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="E229" s="12"/>
+      <c r="F229" s="12"/>
     </row>
     <row r="230" spans="1:6" ht="13.5" customHeight="1">
       <c r="A230" s="9">
-        <v>46219</v>
+        <v>46222</v>
       </c>
       <c r="B230" s="10" t="s">
         <v>52</v>
@@ -13468,11 +13344,11 @@
       <c r="C230" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="D230" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="E230" s="12"/>
-      <c r="F230" s="13"/>
+      <c r="D230" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="E230" s="11"/>
+      <c r="F230" s="11"/>
     </row>
     <row r="231" spans="1:6" ht="13.5" customHeight="1">
       <c r="A231" s="7">
@@ -13484,11 +13360,11 @@
       <c r="C231" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D231" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="E231" s="11"/>
-      <c r="F231" s="14"/>
+      <c r="D231" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="E231" s="12"/>
+      <c r="F231" s="12"/>
     </row>
     <row r="232" spans="1:6" ht="13.5" customHeight="1">
       <c r="A232" s="9">
@@ -13500,11 +13376,11 @@
       <c r="C232" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="D232" s="12" t="s">
-        <v>98</v>
-      </c>
-      <c r="E232" s="12"/>
-      <c r="F232" s="13"/>
+      <c r="D232" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="E232" s="11"/>
+      <c r="F232" s="11"/>
     </row>
     <row r="233" spans="1:6" ht="13.5" customHeight="1">
       <c r="A233" s="7">
@@ -13516,11 +13392,11 @@
       <c r="C233" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D233" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="E233" s="11"/>
-      <c r="F233" s="14"/>
+      <c r="D233" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="E233" s="12"/>
+      <c r="F233" s="12"/>
     </row>
     <row r="234" spans="1:6" ht="13.5" customHeight="1">
       <c r="A234" s="9">
@@ -13532,11 +13408,11 @@
       <c r="C234" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="D234" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="E234" s="12"/>
-      <c r="F234" s="13"/>
+      <c r="D234" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="E234" s="11"/>
+      <c r="F234" s="11"/>
     </row>
     <row r="235" spans="1:6" ht="13.5" customHeight="1">
       <c r="A235" s="7">
@@ -13548,11 +13424,11 @@
       <c r="C235" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D235" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="E235" s="11"/>
-      <c r="F235" s="14"/>
+      <c r="D235" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="E235" s="12"/>
+      <c r="F235" s="12"/>
     </row>
     <row r="236" spans="1:6" ht="13.5" customHeight="1">
       <c r="A236" s="9">
@@ -13564,11 +13440,11 @@
       <c r="C236" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="D236" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="E236" s="12"/>
-      <c r="F236" s="13"/>
+      <c r="D236" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="E236" s="11"/>
+      <c r="F236" s="11"/>
     </row>
     <row r="237" spans="1:6" ht="13.5" customHeight="1">
       <c r="A237" s="7">
@@ -13580,15 +13456,15 @@
       <c r="C237" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D237" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="E237" s="11"/>
-      <c r="F237" s="14"/>
+      <c r="D237" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="E237" s="12"/>
+      <c r="F237" s="12"/>
     </row>
     <row r="238" spans="1:6" ht="13.5" customHeight="1">
       <c r="A238" s="9">
-        <v>46222</v>
+        <v>46224</v>
       </c>
       <c r="B238" s="10" t="s">
         <v>52</v>
@@ -13596,15 +13472,15 @@
       <c r="C238" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="D238" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="E238" s="12"/>
-      <c r="F238" s="13"/>
+      <c r="D238" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="E238" s="11"/>
+      <c r="F238" s="11"/>
     </row>
     <row r="239" spans="1:6" ht="13.5" customHeight="1">
       <c r="A239" s="7">
-        <v>46222</v>
+        <v>46224</v>
       </c>
       <c r="B239" s="8" t="s">
         <v>52</v>
@@ -13612,11 +13488,11 @@
       <c r="C239" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D239" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="E239" s="11"/>
-      <c r="F239" s="14"/>
+      <c r="D239" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="E239" s="12"/>
+      <c r="F239" s="12"/>
     </row>
     <row r="240" spans="1:6" ht="13.5" customHeight="1">
       <c r="A240" s="9">
@@ -13628,11 +13504,11 @@
       <c r="C240" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="D240" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="E240" s="12"/>
-      <c r="F240" s="13"/>
+      <c r="D240" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="E240" s="11"/>
+      <c r="F240" s="11"/>
     </row>
     <row r="241" spans="1:6" ht="13.5" customHeight="1">
       <c r="A241" s="7">
@@ -13644,11 +13520,11 @@
       <c r="C241" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D241" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="E241" s="11"/>
-      <c r="F241" s="14"/>
+      <c r="D241" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="E241" s="12"/>
+      <c r="F241" s="12"/>
     </row>
     <row r="242" spans="1:6" ht="13.5" customHeight="1">
       <c r="A242" s="9">
@@ -13660,11 +13536,11 @@
       <c r="C242" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="D242" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="E242" s="12"/>
-      <c r="F242" s="13"/>
+      <c r="D242" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="E242" s="11"/>
+      <c r="F242" s="11"/>
     </row>
     <row r="243" spans="1:6" ht="13.5" customHeight="1">
       <c r="A243" s="7">
@@ -13676,11 +13552,11 @@
       <c r="C243" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D243" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="E243" s="11"/>
-      <c r="F243" s="14"/>
+      <c r="D243" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E243" s="12"/>
+      <c r="F243" s="12"/>
     </row>
     <row r="244" spans="1:6" ht="13.5" customHeight="1">
       <c r="A244" s="9">
@@ -13692,11 +13568,11 @@
       <c r="C244" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="D244" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="E244" s="12"/>
-      <c r="F244" s="13"/>
+      <c r="D244" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="E244" s="11"/>
+      <c r="F244" s="11"/>
     </row>
     <row r="245" spans="1:6" ht="13.5" customHeight="1">
       <c r="A245" s="7">
@@ -13708,15 +13584,15 @@
       <c r="C245" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D245" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="E245" s="11"/>
-      <c r="F245" s="14"/>
+      <c r="D245" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="E245" s="12"/>
+      <c r="F245" s="12"/>
     </row>
     <row r="246" spans="1:6" ht="13.5" customHeight="1">
       <c r="A246" s="9">
-        <v>46224</v>
+        <v>46226</v>
       </c>
       <c r="B246" s="10" t="s">
         <v>52</v>
@@ -13724,15 +13600,15 @@
       <c r="C246" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="D246" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="E246" s="12"/>
-      <c r="F246" s="13"/>
+      <c r="D246" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="E246" s="11"/>
+      <c r="F246" s="11"/>
     </row>
     <row r="247" spans="1:6" ht="13.5" customHeight="1">
       <c r="A247" s="7">
-        <v>46224</v>
+        <v>46226</v>
       </c>
       <c r="B247" s="8" t="s">
         <v>52</v>
@@ -13740,11 +13616,11 @@
       <c r="C247" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D247" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="E247" s="11"/>
-      <c r="F247" s="14"/>
+      <c r="D247" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="E247" s="12"/>
+      <c r="F247" s="12"/>
     </row>
     <row r="248" spans="1:6" ht="13.5" customHeight="1">
       <c r="A248" s="9">
@@ -13756,11 +13632,11 @@
       <c r="C248" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="D248" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="E248" s="12"/>
-      <c r="F248" s="13"/>
+      <c r="D248" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="E248" s="11"/>
+      <c r="F248" s="11"/>
     </row>
     <row r="249" spans="1:6" ht="13.5" customHeight="1">
       <c r="A249" s="7">
@@ -13772,11 +13648,11 @@
       <c r="C249" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D249" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="E249" s="11"/>
-      <c r="F249" s="14"/>
+      <c r="D249" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="E249" s="12"/>
+      <c r="F249" s="12"/>
     </row>
     <row r="250" spans="1:6" ht="13.5" customHeight="1">
       <c r="A250" s="9">
@@ -13788,11 +13664,11 @@
       <c r="C250" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="D250" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="E250" s="12"/>
-      <c r="F250" s="13"/>
+      <c r="D250" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="E250" s="11"/>
+      <c r="F250" s="11"/>
     </row>
     <row r="251" spans="1:6" ht="13.5" customHeight="1">
       <c r="A251" s="7">
@@ -13804,11 +13680,11 @@
       <c r="C251" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D251" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="E251" s="11"/>
-      <c r="F251" s="14"/>
+      <c r="D251" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E251" s="12"/>
+      <c r="F251" s="12"/>
     </row>
     <row r="252" spans="1:6" ht="13.5" customHeight="1">
       <c r="A252" s="9">
@@ -13820,11 +13696,11 @@
       <c r="C252" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="D252" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="E252" s="12"/>
-      <c r="F252" s="13"/>
+      <c r="D252" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="E252" s="11"/>
+      <c r="F252" s="11"/>
     </row>
     <row r="253" spans="1:6" ht="13.5" customHeight="1">
       <c r="A253" s="7">
@@ -13836,11 +13712,11 @@
       <c r="C253" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D253" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="E253" s="11"/>
-      <c r="F253" s="14"/>
+      <c r="D253" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E253" s="12"/>
+      <c r="F253" s="12"/>
     </row>
     <row r="254" spans="1:6" ht="13.5" customHeight="1">
       <c r="A254" s="9">
@@ -13852,15 +13728,15 @@
       <c r="C254" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="D254" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="E254" s="12"/>
-      <c r="F254" s="13"/>
+      <c r="D254" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="E254" s="11"/>
+      <c r="F254" s="11"/>
     </row>
     <row r="255" spans="1:6" ht="13.5" customHeight="1">
       <c r="A255" s="7">
-        <v>46226</v>
+        <v>46229</v>
       </c>
       <c r="B255" s="8" t="s">
         <v>52</v>
@@ -13868,15 +13744,15 @@
       <c r="C255" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D255" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="E255" s="11"/>
-      <c r="F255" s="14"/>
+      <c r="D255" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="E255" s="12"/>
+      <c r="F255" s="12"/>
     </row>
     <row r="256" spans="1:6" ht="13.5" customHeight="1">
       <c r="A256" s="9">
-        <v>46226</v>
+        <v>46229</v>
       </c>
       <c r="B256" s="10" t="s">
         <v>52</v>
@@ -13884,11 +13760,11 @@
       <c r="C256" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="D256" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="E256" s="12"/>
-      <c r="F256" s="13"/>
+      <c r="D256" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="E256" s="11"/>
+      <c r="F256" s="11"/>
     </row>
     <row r="257" spans="1:6" ht="13.5" customHeight="1">
       <c r="A257" s="7">
@@ -13900,11 +13776,11 @@
       <c r="C257" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D257" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="E257" s="11"/>
-      <c r="F257" s="14"/>
+      <c r="D257" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="E257" s="12"/>
+      <c r="F257" s="12"/>
     </row>
     <row r="258" spans="1:6" ht="13.5" customHeight="1">
       <c r="A258" s="9">
@@ -13916,11 +13792,11 @@
       <c r="C258" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="D258" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="E258" s="12"/>
-      <c r="F258" s="13"/>
+      <c r="D258" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="E258" s="11"/>
+      <c r="F258" s="11"/>
     </row>
     <row r="259" spans="1:6" ht="13.5" customHeight="1">
       <c r="A259" s="7">
@@ -13932,11 +13808,11 @@
       <c r="C259" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D259" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="E259" s="11"/>
-      <c r="F259" s="14"/>
+      <c r="D259" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="E259" s="12"/>
+      <c r="F259" s="12"/>
     </row>
     <row r="260" spans="1:6" ht="13.5" customHeight="1">
       <c r="A260" s="9">
@@ -13948,11 +13824,11 @@
       <c r="C260" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="D260" s="12" t="s">
-        <v>98</v>
-      </c>
-      <c r="E260" s="12"/>
-      <c r="F260" s="13"/>
+      <c r="D260" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="E260" s="11"/>
+      <c r="F260" s="11"/>
     </row>
     <row r="261" spans="1:6" ht="13.5" customHeight="1">
       <c r="A261" s="7">
@@ -13964,11 +13840,11 @@
       <c r="C261" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D261" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="E261" s="11"/>
-      <c r="F261" s="14"/>
+      <c r="D261" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E261" s="12"/>
+      <c r="F261" s="12"/>
     </row>
     <row r="262" spans="1:6" ht="13.5" customHeight="1">
       <c r="A262" s="9">
@@ -13980,11 +13856,11 @@
       <c r="C262" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="D262" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="E262" s="12"/>
-      <c r="F262" s="13"/>
+      <c r="D262" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E262" s="11"/>
+      <c r="F262" s="11"/>
     </row>
     <row r="263" spans="1:6" ht="13.5" customHeight="1">
       <c r="A263" s="7">
@@ -13996,15 +13872,15 @@
       <c r="C263" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D263" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="E263" s="11"/>
-      <c r="F263" s="14"/>
+      <c r="D263" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="E263" s="12"/>
+      <c r="F263" s="12"/>
     </row>
     <row r="264" spans="1:6" ht="13.5" customHeight="1">
       <c r="A264" s="9">
-        <v>46229</v>
+        <v>46231</v>
       </c>
       <c r="B264" s="10" t="s">
         <v>52</v>
@@ -14012,15 +13888,15 @@
       <c r="C264" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="D264" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="E264" s="12"/>
-      <c r="F264" s="13"/>
+      <c r="D264" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="E264" s="11"/>
+      <c r="F264" s="11"/>
     </row>
     <row r="265" spans="1:6" ht="13.5" customHeight="1">
       <c r="A265" s="7">
-        <v>46229</v>
+        <v>46231</v>
       </c>
       <c r="B265" s="8" t="s">
         <v>52</v>
@@ -14028,11 +13904,11 @@
       <c r="C265" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D265" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="E265" s="11"/>
-      <c r="F265" s="14"/>
+      <c r="D265" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="E265" s="12"/>
+      <c r="F265" s="12"/>
     </row>
     <row r="266" spans="1:6" ht="13.5" customHeight="1">
       <c r="A266" s="9">
@@ -14044,11 +13920,11 @@
       <c r="C266" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="D266" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="E266" s="12"/>
-      <c r="F266" s="13"/>
+      <c r="D266" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="E266" s="11"/>
+      <c r="F266" s="11"/>
     </row>
     <row r="267" spans="1:6" ht="13.5" customHeight="1">
       <c r="A267" s="7">
@@ -14060,11 +13936,11 @@
       <c r="C267" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D267" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="E267" s="11"/>
-      <c r="F267" s="14"/>
+      <c r="D267" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="E267" s="12"/>
+      <c r="F267" s="12"/>
     </row>
     <row r="268" spans="1:6" ht="13.5" customHeight="1">
       <c r="A268" s="9">
@@ -14076,11 +13952,11 @@
       <c r="C268" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="D268" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="E268" s="12"/>
-      <c r="F268" s="13"/>
+      <c r="D268" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="E268" s="11"/>
+      <c r="F268" s="11"/>
     </row>
     <row r="269" spans="1:6" ht="13.5" customHeight="1">
       <c r="A269" s="7">
@@ -14092,11 +13968,11 @@
       <c r="C269" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D269" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="E269" s="11"/>
-      <c r="F269" s="14"/>
+      <c r="D269" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E269" s="12"/>
+      <c r="F269" s="12"/>
     </row>
     <row r="270" spans="1:6" ht="13.5" customHeight="1">
       <c r="A270" s="9">
@@ -14108,11 +13984,11 @@
       <c r="C270" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="D270" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="E270" s="12"/>
-      <c r="F270" s="13"/>
+      <c r="D270" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="E270" s="11"/>
+      <c r="F270" s="11"/>
     </row>
     <row r="271" spans="1:6" ht="13.5" customHeight="1">
       <c r="A271" s="7">
@@ -14124,11 +14000,11 @@
       <c r="C271" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D271" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="E271" s="11"/>
-      <c r="F271" s="14"/>
+      <c r="D271" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E271" s="12"/>
+      <c r="F271" s="12"/>
     </row>
     <row r="272" spans="1:6" ht="13.5" customHeight="1">
       <c r="A272" s="9">
@@ -14140,15 +14016,15 @@
       <c r="C272" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="D272" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E272" s="12"/>
-      <c r="F272" s="13"/>
+      <c r="D272" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="E272" s="11"/>
+      <c r="F272" s="11"/>
     </row>
     <row r="273" spans="1:6" ht="13.5" customHeight="1">
       <c r="A273" s="7">
-        <v>46231</v>
+        <v>46233</v>
       </c>
       <c r="B273" s="8" t="s">
         <v>52</v>
@@ -14156,15 +14032,15 @@
       <c r="C273" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D273" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="E273" s="11"/>
-      <c r="F273" s="14"/>
+      <c r="D273" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="E273" s="12"/>
+      <c r="F273" s="12"/>
     </row>
     <row r="274" spans="1:6" ht="13.5" customHeight="1">
       <c r="A274" s="9">
-        <v>46231</v>
+        <v>46233</v>
       </c>
       <c r="B274" s="10" t="s">
         <v>52</v>
@@ -14172,11 +14048,11 @@
       <c r="C274" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="D274" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="E274" s="12"/>
-      <c r="F274" s="13"/>
+      <c r="D274" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="E274" s="11"/>
+      <c r="F274" s="11"/>
     </row>
     <row r="275" spans="1:6" ht="13.5" customHeight="1">
       <c r="A275" s="7">
@@ -14188,11 +14064,11 @@
       <c r="C275" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D275" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="E275" s="11"/>
-      <c r="F275" s="14"/>
+      <c r="D275" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="E275" s="12"/>
+      <c r="F275" s="12"/>
     </row>
     <row r="276" spans="1:6" ht="13.5" customHeight="1">
       <c r="A276" s="9">
@@ -14204,11 +14080,11 @@
       <c r="C276" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="D276" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="E276" s="12"/>
-      <c r="F276" s="13"/>
+      <c r="D276" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="E276" s="11"/>
+      <c r="F276" s="11"/>
     </row>
     <row r="277" spans="1:6" ht="13.5" customHeight="1">
       <c r="A277" s="7">
@@ -14220,11 +14096,11 @@
       <c r="C277" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D277" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="E277" s="11"/>
-      <c r="F277" s="14"/>
+      <c r="D277" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="E277" s="12"/>
+      <c r="F277" s="12"/>
     </row>
     <row r="278" spans="1:6" ht="13.5" customHeight="1">
       <c r="A278" s="9">
@@ -14236,11 +14112,11 @@
       <c r="C278" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="D278" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="E278" s="12"/>
-      <c r="F278" s="13"/>
+      <c r="D278" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="E278" s="11"/>
+      <c r="F278" s="11"/>
     </row>
     <row r="279" spans="1:6" ht="13.5" customHeight="1">
       <c r="A279" s="7">
@@ -14252,11 +14128,11 @@
       <c r="C279" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D279" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="E279" s="11"/>
-      <c r="F279" s="14"/>
+      <c r="D279" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="E279" s="12"/>
+      <c r="F279" s="12"/>
     </row>
     <row r="280" spans="1:6" ht="13.5" customHeight="1">
       <c r="A280" s="9">
@@ -14268,11 +14144,11 @@
       <c r="C280" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="D280" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="E280" s="12"/>
-      <c r="F280" s="13"/>
+      <c r="D280" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="E280" s="11"/>
+      <c r="F280" s="11"/>
     </row>
     <row r="281" spans="1:6" ht="13.5" customHeight="1">
       <c r="A281" s="7">
@@ -14284,47 +14160,47 @@
       <c r="C281" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D281" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="E281" s="11"/>
-      <c r="F281" s="14"/>
+      <c r="D281" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="E281" s="12"/>
+      <c r="F281" s="12"/>
     </row>
     <row r="282" spans="1:6" ht="13.5" customHeight="1">
       <c r="A282" s="9">
-        <v>46233</v>
+        <v>46205</v>
       </c>
       <c r="B282" s="10" t="s">
         <v>52</v>
       </c>
       <c r="C282" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="D282" s="12" t="s">
-        <v>98</v>
-      </c>
-      <c r="E282" s="12"/>
-      <c r="F282" s="13"/>
+        <v>55</v>
+      </c>
+      <c r="D282" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="E282" s="11"/>
+      <c r="F282" s="11"/>
     </row>
     <row r="283" spans="1:6" ht="13.5" customHeight="1">
       <c r="A283" s="7">
-        <v>46233</v>
+        <v>46205</v>
       </c>
       <c r="B283" s="8" t="s">
         <v>52</v>
       </c>
       <c r="C283" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="D283" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="E283" s="11"/>
-      <c r="F283" s="14"/>
+        <v>55</v>
+      </c>
+      <c r="D283" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E283" s="12"/>
+      <c r="F283" s="12"/>
     </row>
     <row r="284" spans="1:6" ht="13.5" customHeight="1">
       <c r="A284" s="9">
-        <v>46205</v>
+        <v>46208</v>
       </c>
       <c r="B284" s="10" t="s">
         <v>52</v>
@@ -14332,15 +14208,15 @@
       <c r="C284" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="D284" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="E284" s="12"/>
-      <c r="F284" s="13"/>
+      <c r="D284" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="E284" s="11"/>
+      <c r="F284" s="11"/>
     </row>
     <row r="285" spans="1:6" ht="13.5" customHeight="1">
       <c r="A285" s="7">
-        <v>46205</v>
+        <v>46208</v>
       </c>
       <c r="B285" s="8" t="s">
         <v>52</v>
@@ -14348,15 +14224,15 @@
       <c r="C285" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="D285" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="E285" s="11"/>
-      <c r="F285" s="14"/>
+      <c r="D285" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E285" s="12"/>
+      <c r="F285" s="12"/>
     </row>
     <row r="286" spans="1:6" ht="13.5" customHeight="1">
       <c r="A286" s="9">
-        <v>46208</v>
+        <v>46210</v>
       </c>
       <c r="B286" s="10" t="s">
         <v>52</v>
@@ -14364,15 +14240,15 @@
       <c r="C286" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="D286" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="E286" s="12"/>
-      <c r="F286" s="13"/>
+      <c r="D286" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="E286" s="11"/>
+      <c r="F286" s="11"/>
     </row>
     <row r="287" spans="1:6" ht="13.5" customHeight="1">
       <c r="A287" s="7">
-        <v>46208</v>
+        <v>46210</v>
       </c>
       <c r="B287" s="8" t="s">
         <v>52</v>
@@ -14380,15 +14256,15 @@
       <c r="C287" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="D287" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="E287" s="11"/>
-      <c r="F287" s="14"/>
+      <c r="D287" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="E287" s="12"/>
+      <c r="F287" s="12"/>
     </row>
     <row r="288" spans="1:6" ht="13.5" customHeight="1">
       <c r="A288" s="9">
-        <v>46210</v>
+        <v>46212</v>
       </c>
       <c r="B288" s="10" t="s">
         <v>52</v>
@@ -14396,15 +14272,15 @@
       <c r="C288" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="D288" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E288" s="12"/>
-      <c r="F288" s="13"/>
+      <c r="D288" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="E288" s="11"/>
+      <c r="F288" s="11"/>
     </row>
     <row r="289" spans="1:6" ht="13.5" customHeight="1">
       <c r="A289" s="7">
-        <v>46210</v>
+        <v>46212</v>
       </c>
       <c r="B289" s="8" t="s">
         <v>52</v>
@@ -14412,15 +14288,15 @@
       <c r="C289" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="D289" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="E289" s="11"/>
-      <c r="F289" s="14"/>
+      <c r="D289" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="E289" s="12"/>
+      <c r="F289" s="12"/>
     </row>
     <row r="290" spans="1:6" ht="13.5" customHeight="1">
       <c r="A290" s="9">
-        <v>46212</v>
+        <v>46215</v>
       </c>
       <c r="B290" s="10" t="s">
         <v>52</v>
@@ -14428,15 +14304,15 @@
       <c r="C290" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="D290" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="E290" s="12"/>
-      <c r="F290" s="13"/>
+      <c r="D290" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="E290" s="11"/>
+      <c r="F290" s="11"/>
     </row>
     <row r="291" spans="1:6" ht="13.5" customHeight="1">
       <c r="A291" s="7">
-        <v>46212</v>
+        <v>46215</v>
       </c>
       <c r="B291" s="8" t="s">
         <v>52</v>
@@ -14444,15 +14320,15 @@
       <c r="C291" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="D291" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="E291" s="11"/>
-      <c r="F291" s="14"/>
+      <c r="D291" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="E291" s="12"/>
+      <c r="F291" s="12"/>
     </row>
     <row r="292" spans="1:6" ht="13.5" customHeight="1">
       <c r="A292" s="9">
-        <v>46215</v>
+        <v>46217</v>
       </c>
       <c r="B292" s="10" t="s">
         <v>52</v>
@@ -14460,15 +14336,13 @@
       <c r="C292" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="D292" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="E292" s="12"/>
-      <c r="F292" s="13"/>
+      <c r="D292" s="11"/>
+      <c r="E292" s="11"/>
+      <c r="F292" s="11"/>
     </row>
     <row r="293" spans="1:6" ht="13.5" customHeight="1">
       <c r="A293" s="7">
-        <v>46215</v>
+        <v>46217</v>
       </c>
       <c r="B293" s="8" t="s">
         <v>52</v>
@@ -14476,15 +14350,13 @@
       <c r="C293" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="D293" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="E293" s="11"/>
-      <c r="F293" s="14"/>
+      <c r="D293" s="12"/>
+      <c r="E293" s="12"/>
+      <c r="F293" s="12"/>
     </row>
     <row r="294" spans="1:6" ht="13.5" customHeight="1">
       <c r="A294" s="9">
-        <v>46217</v>
+        <v>46219</v>
       </c>
       <c r="B294" s="10" t="s">
         <v>52</v>
@@ -14492,13 +14364,13 @@
       <c r="C294" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="D294" s="12"/>
-      <c r="E294" s="12"/>
-      <c r="F294" s="13"/>
+      <c r="D294" s="11"/>
+      <c r="E294" s="11"/>
+      <c r="F294" s="11"/>
     </row>
     <row r="295" spans="1:6" ht="13.5" customHeight="1">
       <c r="A295" s="7">
-        <v>46217</v>
+        <v>46219</v>
       </c>
       <c r="B295" s="8" t="s">
         <v>52</v>
@@ -14506,13 +14378,13 @@
       <c r="C295" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="D295" s="11"/>
-      <c r="E295" s="11"/>
-      <c r="F295" s="14"/>
+      <c r="D295" s="12"/>
+      <c r="E295" s="12"/>
+      <c r="F295" s="12"/>
     </row>
     <row r="296" spans="1:6" ht="13.5" customHeight="1">
       <c r="A296" s="9">
-        <v>46219</v>
+        <v>46222</v>
       </c>
       <c r="B296" s="10" t="s">
         <v>52</v>
@@ -14520,13 +14392,13 @@
       <c r="C296" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="D296" s="12"/>
-      <c r="E296" s="12"/>
-      <c r="F296" s="13"/>
+      <c r="D296" s="11"/>
+      <c r="E296" s="11"/>
+      <c r="F296" s="11"/>
     </row>
     <row r="297" spans="1:6" ht="13.5" customHeight="1">
       <c r="A297" s="7">
-        <v>46219</v>
+        <v>46222</v>
       </c>
       <c r="B297" s="8" t="s">
         <v>52</v>
@@ -14534,13 +14406,13 @@
       <c r="C297" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="D297" s="11"/>
-      <c r="E297" s="11"/>
-      <c r="F297" s="14"/>
+      <c r="D297" s="12"/>
+      <c r="E297" s="12"/>
+      <c r="F297" s="12"/>
     </row>
     <row r="298" spans="1:6" ht="13.5" customHeight="1">
       <c r="A298" s="9">
-        <v>46222</v>
+        <v>46224</v>
       </c>
       <c r="B298" s="10" t="s">
         <v>52</v>
@@ -14548,13 +14420,13 @@
       <c r="C298" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="D298" s="12"/>
-      <c r="E298" s="12"/>
-      <c r="F298" s="13"/>
+      <c r="D298" s="11"/>
+      <c r="E298" s="11"/>
+      <c r="F298" s="11"/>
     </row>
     <row r="299" spans="1:6" ht="13.5" customHeight="1">
       <c r="A299" s="7">
-        <v>46222</v>
+        <v>46224</v>
       </c>
       <c r="B299" s="8" t="s">
         <v>52</v>
@@ -14562,13 +14434,13 @@
       <c r="C299" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="D299" s="11"/>
-      <c r="E299" s="11"/>
-      <c r="F299" s="14"/>
+      <c r="D299" s="12"/>
+      <c r="E299" s="12"/>
+      <c r="F299" s="12"/>
     </row>
     <row r="300" spans="1:6" ht="13.5" customHeight="1">
       <c r="A300" s="9">
-        <v>46224</v>
+        <v>46226</v>
       </c>
       <c r="B300" s="10" t="s">
         <v>52</v>
@@ -14576,13 +14448,13 @@
       <c r="C300" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="D300" s="12"/>
-      <c r="E300" s="12"/>
-      <c r="F300" s="13"/>
+      <c r="D300" s="11"/>
+      <c r="E300" s="11"/>
+      <c r="F300" s="11"/>
     </row>
     <row r="301" spans="1:6" ht="13.5" customHeight="1">
       <c r="A301" s="7">
-        <v>46224</v>
+        <v>46226</v>
       </c>
       <c r="B301" s="8" t="s">
         <v>52</v>
@@ -14590,13 +14462,13 @@
       <c r="C301" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="D301" s="11"/>
-      <c r="E301" s="11"/>
-      <c r="F301" s="14"/>
+      <c r="D301" s="12"/>
+      <c r="E301" s="12"/>
+      <c r="F301" s="12"/>
     </row>
     <row r="302" spans="1:6" ht="13.5" customHeight="1">
       <c r="A302" s="9">
-        <v>46226</v>
+        <v>46229</v>
       </c>
       <c r="B302" s="10" t="s">
         <v>52</v>
@@ -14604,13 +14476,13 @@
       <c r="C302" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="D302" s="12"/>
-      <c r="E302" s="12"/>
-      <c r="F302" s="13"/>
+      <c r="D302" s="11"/>
+      <c r="E302" s="11"/>
+      <c r="F302" s="11"/>
     </row>
     <row r="303" spans="1:6" ht="13.5" customHeight="1">
       <c r="A303" s="7">
-        <v>46226</v>
+        <v>46229</v>
       </c>
       <c r="B303" s="8" t="s">
         <v>52</v>
@@ -14618,13 +14490,13 @@
       <c r="C303" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="D303" s="11"/>
-      <c r="E303" s="11"/>
-      <c r="F303" s="14"/>
+      <c r="D303" s="12"/>
+      <c r="E303" s="12"/>
+      <c r="F303" s="12"/>
     </row>
     <row r="304" spans="1:6" ht="13.5" customHeight="1">
       <c r="A304" s="9">
-        <v>46229</v>
+        <v>46231</v>
       </c>
       <c r="B304" s="10" t="s">
         <v>52</v>
@@ -14632,13 +14504,13 @@
       <c r="C304" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="D304" s="12"/>
-      <c r="E304" s="12"/>
-      <c r="F304" s="13"/>
+      <c r="D304" s="11"/>
+      <c r="E304" s="11"/>
+      <c r="F304" s="11"/>
     </row>
     <row r="305" spans="1:6" ht="13.5" customHeight="1">
       <c r="A305" s="7">
-        <v>46229</v>
+        <v>46231</v>
       </c>
       <c r="B305" s="8" t="s">
         <v>52</v>
@@ -14646,13 +14518,13 @@
       <c r="C305" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="D305" s="11"/>
-      <c r="E305" s="11"/>
-      <c r="F305" s="14"/>
+      <c r="D305" s="12"/>
+      <c r="E305" s="12"/>
+      <c r="F305" s="12"/>
     </row>
     <row r="306" spans="1:6" ht="13.5" customHeight="1">
       <c r="A306" s="9">
-        <v>46231</v>
+        <v>46233</v>
       </c>
       <c r="B306" s="10" t="s">
         <v>52</v>
@@ -14660,13 +14532,13 @@
       <c r="C306" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="D306" s="12"/>
-      <c r="E306" s="12"/>
-      <c r="F306" s="13"/>
+      <c r="D306" s="11"/>
+      <c r="E306" s="11"/>
+      <c r="F306" s="11"/>
     </row>
     <row r="307" spans="1:6" ht="13.5" customHeight="1">
       <c r="A307" s="7">
-        <v>46231</v>
+        <v>46233</v>
       </c>
       <c r="B307" s="8" t="s">
         <v>52</v>
@@ -14674,429 +14546,439 @@
       <c r="C307" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="D307" s="11"/>
-      <c r="E307" s="11"/>
-      <c r="F307" s="14"/>
+      <c r="D307" s="12"/>
+      <c r="E307" s="12"/>
+      <c r="F307" s="12"/>
     </row>
     <row r="308" spans="1:6" ht="13.5" customHeight="1">
       <c r="A308" s="9">
-        <v>46233</v>
+        <v>46210</v>
       </c>
       <c r="B308" s="10" t="s">
         <v>52</v>
       </c>
       <c r="C308" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="D308" s="12"/>
-      <c r="E308" s="12"/>
-      <c r="F308" s="13"/>
+        <v>66</v>
+      </c>
+      <c r="D308" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="E308" s="11"/>
+      <c r="F308" s="11"/>
     </row>
     <row r="309" spans="1:6" ht="13.5" customHeight="1">
       <c r="A309" s="7">
-        <v>46233</v>
+        <v>46217</v>
       </c>
       <c r="B309" s="8" t="s">
         <v>52</v>
       </c>
       <c r="C309" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="D309" s="11"/>
-      <c r="E309" s="11"/>
-      <c r="F309" s="14"/>
+        <v>66</v>
+      </c>
+      <c r="D309" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="E309" s="12"/>
+      <c r="F309" s="12"/>
     </row>
     <row r="310" spans="1:6" ht="13.5" customHeight="1">
-      <c r="A310" s="23" t="s">
-        <v>183</v>
-      </c>
-      <c r="B310" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C310" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="D310" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="E310" s="4"/>
+      <c r="A310" s="9">
+        <v>46224</v>
+      </c>
+      <c r="B310" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="C310" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="D310" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="E310" s="11"/>
+      <c r="F310" s="11"/>
     </row>
     <row r="311" spans="1:6" ht="13.5" customHeight="1">
-      <c r="A311" s="23" t="s">
-        <v>184</v>
-      </c>
-      <c r="B311" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C311" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="D311" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="E311" s="4"/>
+      <c r="A311" s="7">
+        <v>46231</v>
+      </c>
+      <c r="B311" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C311" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="D311" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="E311" s="12"/>
+      <c r="F311" s="12"/>
     </row>
     <row r="312" spans="1:6" ht="13.5" customHeight="1">
-      <c r="A312" s="23" t="s">
-        <v>185</v>
-      </c>
-      <c r="B312" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C312" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="D312" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="E312" s="4"/>
+      <c r="A312" s="9">
+        <v>46238</v>
+      </c>
+      <c r="B312" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="C312" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="D312" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="E312" s="11"/>
+      <c r="F312" s="11"/>
     </row>
     <row r="313" spans="1:6" ht="13.5" customHeight="1">
-      <c r="A313" s="23" t="s">
-        <v>186</v>
-      </c>
-      <c r="B313" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C313" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="D313" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="E313" s="4"/>
+      <c r="A313" s="7">
+        <v>46245</v>
+      </c>
+      <c r="B313" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C313" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="D313" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="E313" s="12"/>
+      <c r="F313" s="12"/>
     </row>
     <row r="314" spans="1:6" ht="13.5" customHeight="1">
-      <c r="A314" s="23" t="s">
-        <v>187</v>
-      </c>
-      <c r="B314" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C314" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="D314" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="E314" s="4"/>
+      <c r="A314" s="9">
+        <v>46252</v>
+      </c>
+      <c r="B314" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="C314" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="D314" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="E314" s="11"/>
+      <c r="F314" s="11"/>
     </row>
     <row r="315" spans="1:6" ht="13.5" customHeight="1">
-      <c r="A315" s="23" t="s">
-        <v>188</v>
-      </c>
-      <c r="B315" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C315" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="D315" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="E315" s="4"/>
+      <c r="A315" s="7">
+        <v>46259</v>
+      </c>
+      <c r="B315" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C315" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="D315" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="E315" s="12"/>
+      <c r="F315" s="12"/>
     </row>
     <row r="316" spans="1:6" ht="13.5" customHeight="1">
-      <c r="A316" s="23" t="s">
-        <v>189</v>
-      </c>
-      <c r="B316" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C316" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="D316" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="E316" s="4"/>
+      <c r="A316" s="9">
+        <v>46266</v>
+      </c>
+      <c r="B316" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="C316" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="D316" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="E316" s="11"/>
+      <c r="F316" s="11"/>
     </row>
     <row r="317" spans="1:6" ht="13.5" customHeight="1">
-      <c r="A317" s="23" t="s">
-        <v>190</v>
-      </c>
-      <c r="B317" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C317" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="D317" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="E317" s="4"/>
+      <c r="A317" s="7">
+        <v>46273</v>
+      </c>
+      <c r="B317" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C317" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="D317" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="E317" s="12"/>
+      <c r="F317" s="12"/>
     </row>
     <row r="318" spans="1:6" ht="13.5" customHeight="1">
-      <c r="A318" s="23" t="s">
-        <v>191</v>
-      </c>
-      <c r="B318" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C318" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="D318" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="E318" s="4"/>
+      <c r="A318" s="9">
+        <v>46280</v>
+      </c>
+      <c r="B318" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="C318" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="D318" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="E318" s="11"/>
+      <c r="F318" s="11"/>
     </row>
     <row r="319" spans="1:6" ht="13.5" customHeight="1">
-      <c r="A319" s="23" t="s">
-        <v>192</v>
-      </c>
-      <c r="B319" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C319" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="D319" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="E319" s="4"/>
+      <c r="A319" s="7">
+        <v>46287</v>
+      </c>
+      <c r="B319" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C319" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="D319" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="E319" s="12"/>
+      <c r="F319" s="12"/>
     </row>
     <row r="320" spans="1:6" ht="13.5" customHeight="1">
-      <c r="A320" s="23" t="s">
-        <v>193</v>
-      </c>
-      <c r="B320" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C320" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="D320" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="E320" s="4"/>
-    </row>
-    <row r="321" spans="1:5" ht="13.5" customHeight="1">
-      <c r="A321" s="23" t="s">
-        <v>194</v>
-      </c>
-      <c r="B321" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C321" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="D321" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="E321" s="4"/>
-    </row>
-    <row r="322" spans="1:5" ht="13.5" customHeight="1">
-      <c r="A322" s="23" t="s">
-        <v>195</v>
-      </c>
-      <c r="B322" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C322" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="D322" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="E322" s="4"/>
-    </row>
-    <row r="323" spans="1:5" ht="13.5" customHeight="1">
-      <c r="A323" s="23" t="s">
-        <v>196</v>
-      </c>
-      <c r="B323" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C323" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="D323" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="E323" s="4"/>
-    </row>
-    <row r="324" spans="1:5" ht="13.5" customHeight="1">
-      <c r="A324" s="23" t="s">
-        <v>197</v>
-      </c>
-      <c r="B324" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C324" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="D324" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="E324" s="4"/>
-    </row>
-    <row r="325" spans="1:5" ht="13.5" customHeight="1">
-      <c r="A325" s="23" t="s">
-        <v>198</v>
-      </c>
-      <c r="B325" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C325" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="D325" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="E325" s="4"/>
-    </row>
-    <row r="326" spans="1:5" ht="13.5" customHeight="1">
-      <c r="A326" s="23" t="s">
-        <v>199</v>
-      </c>
-      <c r="B326" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C326" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="D326" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="E326" s="4"/>
-    </row>
-    <row r="327" spans="1:5" ht="13.5" customHeight="1">
-      <c r="A327" s="23" t="s">
-        <v>200</v>
-      </c>
-      <c r="B327" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C327" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="D327" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="E327" s="4"/>
-    </row>
-    <row r="328" spans="1:5" ht="13.5" customHeight="1">
-      <c r="A328" s="23" t="s">
-        <v>201</v>
-      </c>
-      <c r="B328" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C328" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="D328" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="E328" s="4"/>
-    </row>
-    <row r="329" spans="1:5" ht="13.5" customHeight="1">
-      <c r="A329" s="23" t="s">
-        <v>202</v>
-      </c>
-      <c r="B329" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C329" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="D329" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="E329" s="4"/>
-    </row>
-    <row r="330" spans="1:5" ht="13.5" customHeight="1">
-      <c r="A330" s="23" t="s">
-        <v>203</v>
-      </c>
-      <c r="B330" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C330" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="D330" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="E330" s="4"/>
-    </row>
-    <row r="331" spans="1:5" ht="13.5" customHeight="1">
-      <c r="A331" s="23" t="s">
-        <v>204</v>
-      </c>
-      <c r="B331" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C331" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="D331" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="E331" s="4"/>
-    </row>
-    <row r="332" spans="1:5" ht="13.5" customHeight="1">
-      <c r="A332" s="23" t="s">
-        <v>205</v>
-      </c>
-      <c r="B332" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C332" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="D332" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="E332" s="4"/>
-    </row>
-    <row r="333" spans="1:5" ht="13.5" customHeight="1">
-      <c r="A333" s="23" t="s">
-        <v>206</v>
-      </c>
-      <c r="B333" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C333" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="D333" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="E333" s="4"/>
-    </row>
-    <row r="334" spans="1:5" ht="13.5" customHeight="1">
-      <c r="A334" s="23" t="s">
-        <v>207</v>
-      </c>
-      <c r="B334" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C334" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="D334" s="4" t="s">
-        <v>161</v>
-      </c>
+      <c r="A320" s="9">
+        <v>46294</v>
+      </c>
+      <c r="B320" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="C320" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="D320" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="E320" s="11"/>
+      <c r="F320" s="11"/>
+    </row>
+    <row r="321" spans="1:6" ht="13.5" customHeight="1">
+      <c r="A321" s="7">
+        <v>46301</v>
+      </c>
+      <c r="B321" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C321" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="D321" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="E321" s="12"/>
+      <c r="F321" s="12"/>
+    </row>
+    <row r="322" spans="1:6" ht="13.5" customHeight="1">
+      <c r="A322" s="9">
+        <v>46308</v>
+      </c>
+      <c r="B322" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="C322" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="D322" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="E322" s="11"/>
+      <c r="F322" s="11"/>
+    </row>
+    <row r="323" spans="1:6" ht="13.5" customHeight="1">
+      <c r="A323" s="7">
+        <v>46315</v>
+      </c>
+      <c r="B323" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C323" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="D323" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="E323" s="12"/>
+      <c r="F323" s="12"/>
+    </row>
+    <row r="324" spans="1:6" ht="13.5" customHeight="1">
+      <c r="A324" s="9">
+        <v>46322</v>
+      </c>
+      <c r="B324" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="C324" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="D324" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="E324" s="11"/>
+      <c r="F324" s="11"/>
+    </row>
+    <row r="325" spans="1:6" ht="13.5" customHeight="1">
+      <c r="A325" s="7">
+        <v>46329</v>
+      </c>
+      <c r="B325" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C325" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="D325" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="E325" s="12"/>
+      <c r="F325" s="12"/>
+    </row>
+    <row r="326" spans="1:6" ht="13.5" customHeight="1">
+      <c r="A326" s="9">
+        <v>46336</v>
+      </c>
+      <c r="B326" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="C326" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="D326" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="E326" s="11"/>
+      <c r="F326" s="11"/>
+    </row>
+    <row r="327" spans="1:6" ht="13.5" customHeight="1">
+      <c r="A327" s="7">
+        <v>46343</v>
+      </c>
+      <c r="B327" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C327" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="D327" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="E327" s="12"/>
+      <c r="F327" s="12"/>
+    </row>
+    <row r="328" spans="1:6" ht="13.5" customHeight="1">
+      <c r="A328" s="9">
+        <v>46350</v>
+      </c>
+      <c r="B328" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="C328" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="D328" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="E328" s="11"/>
+      <c r="F328" s="11"/>
+    </row>
+    <row r="329" spans="1:6" ht="13.5" customHeight="1">
+      <c r="A329" s="7">
+        <v>46357</v>
+      </c>
+      <c r="B329" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C329" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="D329" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="E329" s="12"/>
+      <c r="F329" s="12"/>
+    </row>
+    <row r="330" spans="1:6" ht="13.5" customHeight="1">
+      <c r="A330" s="9">
+        <v>46364</v>
+      </c>
+      <c r="B330" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="C330" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="D330" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="E330" s="11"/>
+      <c r="F330" s="11"/>
+    </row>
+    <row r="331" spans="1:6" ht="13.5" customHeight="1">
+      <c r="A331" s="7">
+        <v>46371</v>
+      </c>
+      <c r="B331" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C331" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="D331" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="E331" s="12"/>
+      <c r="F331" s="12"/>
+    </row>
+    <row r="332" spans="1:6" ht="13.5" customHeight="1">
+      <c r="A332" s="9">
+        <v>46378</v>
+      </c>
+      <c r="B332" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="C332" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="D332" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="E332" s="11"/>
+      <c r="F332" s="11"/>
+    </row>
+    <row r="333" spans="1:6" ht="13.5" customHeight="1">
+      <c r="A333" s="7">
+        <v>46385</v>
+      </c>
+      <c r="B333" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C333" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="D333" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="E333" s="12"/>
+      <c r="F333" s="12"/>
+    </row>
+    <row r="334" spans="1:6" ht="13.5" customHeight="1">
+      <c r="B334" s="4"/>
+      <c r="C334" s="4"/>
+      <c r="D334" s="4"/>
       <c r="E334" s="4"/>
     </row>
-    <row r="335" spans="1:5" ht="13.5" customHeight="1">
-      <c r="A335" s="23" t="s">
-        <v>208</v>
-      </c>
-      <c r="B335" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C335" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="D335" s="4" t="s">
-        <v>165</v>
-      </c>
+    <row r="335" spans="1:6" ht="13.5" customHeight="1">
+      <c r="B335" s="4"/>
+      <c r="C335" s="4"/>
+      <c r="D335" s="4"/>
       <c r="E335" s="4"/>
     </row>
-    <row r="336" spans="1:5" ht="13.5" customHeight="1">
+    <row r="336" spans="1:6" ht="13.5" customHeight="1">
       <c r="B336" s="4"/>
       <c r="C336" s="4"/>
       <c r="D336" s="4"/>
@@ -15426,188 +15308,48 @@
       <c r="D390" s="4"/>
       <c r="E390" s="4"/>
     </row>
-    <row r="391" spans="2:5" ht="13.5" customHeight="1">
-      <c r="B391" s="4"/>
-      <c r="C391" s="4"/>
-      <c r="D391" s="4"/>
-      <c r="E391" s="4"/>
-    </row>
-    <row r="392" spans="2:5" ht="13.5" customHeight="1">
-      <c r="B392" s="4"/>
-      <c r="C392" s="4"/>
-      <c r="D392" s="4"/>
-      <c r="E392" s="4"/>
-    </row>
-    <row r="393" spans="2:5" ht="13.5" customHeight="1">
-      <c r="B393" s="4"/>
-      <c r="C393" s="4"/>
-      <c r="D393" s="4"/>
-      <c r="E393" s="4"/>
-    </row>
-    <row r="394" spans="2:5" ht="13.5" customHeight="1">
-      <c r="B394" s="4"/>
-      <c r="C394" s="4"/>
-      <c r="D394" s="4"/>
-      <c r="E394" s="4"/>
-    </row>
-    <row r="395" spans="2:5" ht="13.5" customHeight="1">
-      <c r="B395" s="4"/>
-      <c r="C395" s="4"/>
-      <c r="D395" s="4"/>
-      <c r="E395" s="4"/>
-    </row>
-    <row r="396" spans="2:5" ht="13.5" customHeight="1">
-      <c r="B396" s="4"/>
-      <c r="C396" s="4"/>
-      <c r="D396" s="4"/>
-      <c r="E396" s="4"/>
-    </row>
-    <row r="397" spans="2:5" ht="13.5" customHeight="1">
-      <c r="B397" s="4"/>
-      <c r="C397" s="4"/>
-      <c r="D397" s="4"/>
-      <c r="E397" s="4"/>
-    </row>
-    <row r="398" spans="2:5" ht="13.5" customHeight="1">
-      <c r="B398" s="4"/>
-      <c r="C398" s="4"/>
-      <c r="D398" s="4"/>
-      <c r="E398" s="4"/>
-    </row>
-    <row r="399" spans="2:5" ht="13.5" customHeight="1">
-      <c r="B399" s="4"/>
-      <c r="C399" s="4"/>
-      <c r="D399" s="4"/>
-      <c r="E399" s="4"/>
-    </row>
-    <row r="400" spans="2:5" ht="13.5" customHeight="1">
-      <c r="B400" s="4"/>
-      <c r="C400" s="4"/>
-      <c r="D400" s="4"/>
-      <c r="E400" s="4"/>
-    </row>
-    <row r="401" spans="2:5" ht="13.5" customHeight="1">
-      <c r="B401" s="4"/>
-      <c r="C401" s="4"/>
-      <c r="D401" s="4"/>
-      <c r="E401" s="4"/>
-    </row>
-    <row r="402" spans="2:5" ht="13.5" customHeight="1">
-      <c r="B402" s="4"/>
-      <c r="C402" s="4"/>
-      <c r="D402" s="4"/>
-      <c r="E402" s="4"/>
-    </row>
-    <row r="403" spans="2:5" ht="13.5" customHeight="1">
-      <c r="B403" s="4"/>
-      <c r="C403" s="4"/>
-      <c r="D403" s="4"/>
-      <c r="E403" s="4"/>
-    </row>
-    <row r="404" spans="2:5" ht="13.5" customHeight="1">
-      <c r="B404" s="4"/>
-      <c r="C404" s="4"/>
-      <c r="D404" s="4"/>
-      <c r="E404" s="4"/>
-    </row>
-    <row r="405" spans="2:5" ht="13.5" customHeight="1">
-      <c r="B405" s="4"/>
-      <c r="C405" s="4"/>
-      <c r="D405" s="4"/>
-      <c r="E405" s="4"/>
-    </row>
-    <row r="406" spans="2:5" ht="13.5" customHeight="1">
-      <c r="B406" s="4"/>
-      <c r="C406" s="4"/>
-      <c r="D406" s="4"/>
-      <c r="E406" s="4"/>
-    </row>
-    <row r="407" spans="2:5" ht="13.5" customHeight="1">
-      <c r="B407" s="4"/>
-      <c r="C407" s="4"/>
-      <c r="D407" s="4"/>
-      <c r="E407" s="4"/>
-    </row>
-    <row r="408" spans="2:5" ht="13.5" customHeight="1">
-      <c r="B408" s="4"/>
-      <c r="C408" s="4"/>
-      <c r="D408" s="4"/>
-      <c r="E408" s="4"/>
-    </row>
-    <row r="409" spans="2:5" ht="13.5" customHeight="1">
-      <c r="B409" s="4"/>
-      <c r="C409" s="4"/>
-      <c r="D409" s="4"/>
-      <c r="E409" s="4"/>
-    </row>
-    <row r="410" spans="2:5" ht="13.5" customHeight="1">
-      <c r="B410" s="4"/>
-      <c r="C410" s="4"/>
-      <c r="D410" s="4"/>
-      <c r="E410" s="4"/>
-    </row>
-    <row r="411" spans="2:5" ht="13.5" customHeight="1">
-      <c r="B411" s="4"/>
-      <c r="C411" s="4"/>
-      <c r="D411" s="4"/>
-      <c r="E411" s="4"/>
-    </row>
-    <row r="412" spans="2:5" ht="13.5" customHeight="1">
-      <c r="B412" s="4"/>
-      <c r="C412" s="4"/>
-      <c r="D412" s="4"/>
-      <c r="E412" s="4"/>
-    </row>
-    <row r="413" spans="2:5" ht="13.5" customHeight="1">
-      <c r="B413" s="4"/>
-      <c r="C413" s="4"/>
-      <c r="D413" s="4"/>
-      <c r="E413" s="4"/>
-    </row>
-    <row r="414" spans="2:5" ht="13.5" customHeight="1">
-      <c r="B414" s="4"/>
-      <c r="C414" s="4"/>
-      <c r="D414" s="4"/>
-      <c r="E414" s="4"/>
-    </row>
-    <row r="415" spans="2:5" ht="13.5" customHeight="1">
-      <c r="B415" s="4"/>
-      <c r="C415" s="4"/>
-      <c r="D415" s="4"/>
-      <c r="E415" s="4"/>
-    </row>
-    <row r="416" spans="2:5" ht="13.5" customHeight="1">
-      <c r="B416" s="4"/>
-      <c r="C416" s="4"/>
-      <c r="D416" s="4"/>
-      <c r="E416" s="4"/>
-    </row>
-    <row r="417" spans="2:5" ht="13.5" customHeight="1">
-      <c r="B417" s="4"/>
-      <c r="C417" s="4"/>
-      <c r="D417" s="4"/>
-      <c r="E417" s="4"/>
-    </row>
-    <row r="418" spans="2:5" ht="13.5" customHeight="1">
-      <c r="B418" s="4"/>
-      <c r="C418" s="4"/>
-      <c r="D418" s="4"/>
-      <c r="E418" s="4"/>
-    </row>
-    <row r="419" spans="2:5" ht="13.5" customHeight="1"/>
-    <row r="420" spans="2:5" ht="13.5" customHeight="1"/>
-    <row r="421" spans="2:5" ht="13.5" customHeight="1"/>
-    <row r="422" spans="2:5" ht="13.5" customHeight="1"/>
-    <row r="423" spans="2:5" ht="13.5" customHeight="1"/>
-    <row r="424" spans="2:5" ht="13.5" customHeight="1"/>
-    <row r="425" spans="2:5" ht="13.5" customHeight="1"/>
-    <row r="426" spans="2:5" ht="13.5" customHeight="1"/>
-    <row r="427" spans="2:5" ht="13.5" customHeight="1"/>
-    <row r="428" spans="2:5" ht="13.5" customHeight="1"/>
-    <row r="429" spans="2:5" ht="13.5" customHeight="1"/>
-    <row r="430" spans="2:5" ht="13.5" customHeight="1"/>
-    <row r="431" spans="2:5" ht="13.5" customHeight="1"/>
-    <row r="432" spans="2:5" ht="13.5" customHeight="1"/>
+    <row r="391" spans="2:5" ht="13.5" customHeight="1"/>
+    <row r="392" spans="2:5" ht="13.5" customHeight="1"/>
+    <row r="393" spans="2:5" ht="13.5" customHeight="1"/>
+    <row r="394" spans="2:5" ht="13.5" customHeight="1"/>
+    <row r="395" spans="2:5" ht="13.5" customHeight="1"/>
+    <row r="396" spans="2:5" ht="13.5" customHeight="1"/>
+    <row r="397" spans="2:5" ht="13.5" customHeight="1"/>
+    <row r="398" spans="2:5" ht="13.5" customHeight="1"/>
+    <row r="399" spans="2:5" ht="13.5" customHeight="1"/>
+    <row r="400" spans="2:5" ht="13.5" customHeight="1"/>
+    <row r="401" ht="13.5" customHeight="1"/>
+    <row r="402" ht="13.5" customHeight="1"/>
+    <row r="403" ht="13.5" customHeight="1"/>
+    <row r="404" ht="13.5" customHeight="1"/>
+    <row r="405" ht="13.5" customHeight="1"/>
+    <row r="406" ht="13.5" customHeight="1"/>
+    <row r="407" ht="13.5" customHeight="1"/>
+    <row r="408" ht="13.5" customHeight="1"/>
+    <row r="409" ht="13.5" customHeight="1"/>
+    <row r="410" ht="13.5" customHeight="1"/>
+    <row r="411" ht="13.5" customHeight="1"/>
+    <row r="412" ht="13.5" customHeight="1"/>
+    <row r="413" ht="13.5" customHeight="1"/>
+    <row r="414" ht="13.5" customHeight="1"/>
+    <row r="415" ht="13.5" customHeight="1"/>
+    <row r="416" ht="13.5" customHeight="1"/>
+    <row r="417" ht="13.5" customHeight="1"/>
+    <row r="418" ht="13.5" customHeight="1"/>
+    <row r="419" ht="13.5" customHeight="1"/>
+    <row r="420" ht="13.5" customHeight="1"/>
+    <row r="421" ht="13.5" customHeight="1"/>
+    <row r="422" ht="13.5" customHeight="1"/>
+    <row r="423" ht="13.5" customHeight="1"/>
+    <row r="424" ht="13.5" customHeight="1"/>
+    <row r="425" ht="13.5" customHeight="1"/>
+    <row r="426" ht="13.5" customHeight="1"/>
+    <row r="427" ht="13.5" customHeight="1"/>
+    <row r="428" ht="13.5" customHeight="1"/>
+    <row r="429" ht="13.5" customHeight="1"/>
+    <row r="430" ht="13.5" customHeight="1"/>
+    <row r="431" ht="13.5" customHeight="1"/>
+    <row r="432" ht="13.5" customHeight="1"/>
     <row r="433" ht="13.5" customHeight="1"/>
     <row r="434" ht="13.5" customHeight="1"/>
     <row r="435" ht="13.5" customHeight="1"/>
@@ -16006,38 +15748,10 @@
     <row r="828" ht="13.5" customHeight="1"/>
     <row r="829" ht="13.5" customHeight="1"/>
     <row r="830" ht="13.5" customHeight="1"/>
-    <row r="831" ht="13.5" customHeight="1"/>
-    <row r="832" ht="13.5" customHeight="1"/>
-    <row r="833" ht="13.5" customHeight="1"/>
-    <row r="834" ht="13.5" customHeight="1"/>
-    <row r="835" ht="13.5" customHeight="1"/>
-    <row r="836" ht="13.5" customHeight="1"/>
-    <row r="837" ht="13.5" customHeight="1"/>
-    <row r="838" ht="13.5" customHeight="1"/>
-    <row r="839" ht="13.5" customHeight="1"/>
-    <row r="840" ht="13.5" customHeight="1"/>
-    <row r="841" ht="13.5" customHeight="1"/>
-    <row r="842" ht="13.5" customHeight="1"/>
-    <row r="843" ht="13.5" customHeight="1"/>
-    <row r="844" ht="13.5" customHeight="1"/>
-    <row r="845" ht="13.5" customHeight="1"/>
-    <row r="846" ht="13.5" customHeight="1"/>
-    <row r="847" ht="13.5" customHeight="1"/>
-    <row r="848" ht="13.5" customHeight="1"/>
-    <row r="849" ht="13.5" customHeight="1"/>
-    <row r="850" ht="13.5" customHeight="1"/>
-    <row r="851" ht="13.5" customHeight="1"/>
-    <row r="852" ht="13.5" customHeight="1"/>
-    <row r="853" ht="13.5" customHeight="1"/>
-    <row r="854" ht="13.5" customHeight="1"/>
-    <row r="855" ht="13.5" customHeight="1"/>
-    <row r="856" ht="13.5" customHeight="1"/>
-    <row r="857" ht="13.5" customHeight="1"/>
-    <row r="858" ht="13.5" customHeight="1"/>
   </sheetData>
-  <autoFilter ref="A1:F309" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
+  <autoFilter ref="A1:F333" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="B2:B418" xr:uid="{00000000-0002-0000-0400-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="B2:B390" xr:uid="{00000000-0002-0000-0400-000001000000}">
       <formula1>"Servicio,Actividad"</formula1>
     </dataValidation>
   </dataValidations>
@@ -16050,19 +15764,19 @@
           <x14:formula1>
             <xm:f>'Lista Servidores'!$A$2:$A$500</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D418</xm:sqref>
+          <xm:sqref>D2:D390</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0400-000002000000}">
           <x14:formula1>
             <xm:f>Servicios!$A$2:$A$200</xm:f>
           </x14:formula1>
-          <xm:sqref>C2:C418</xm:sqref>
+          <xm:sqref>C2:C390</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0400-000003000000}">
           <x14:formula1>
             <xm:f>Estados!$A$2:$A$100</xm:f>
           </x14:formula1>
-          <xm:sqref>E2:E418</xm:sqref>
+          <xm:sqref>E2:E390</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -16084,16 +15798,16 @@
   <sheetData>
     <row r="1" spans="1:26" ht="13.5" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
@@ -16120,13 +15834,13 @@
     </row>
     <row r="2" spans="1:26" ht="13.5" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="B2" s="17">
+        <v>125</v>
+      </c>
+      <c r="B2" s="15">
         <v>5</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>5</v>
@@ -16134,13 +15848,13 @@
     </row>
     <row r="3" spans="1:26" ht="13.5" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B3" s="18">
+        <v>127</v>
+      </c>
+      <c r="B3" s="16">
         <v>46173</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>5</v>
@@ -16148,13 +15862,13 @@
     </row>
     <row r="4" spans="1:26" ht="13.5" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="B4" s="17">
+        <v>129</v>
+      </c>
+      <c r="B4" s="15">
         <v>5</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>5</v>
@@ -16162,13 +15876,13 @@
     </row>
     <row r="5" spans="1:26" ht="13.5" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="B5" s="19" t="s">
-        <v>129</v>
+        <v>131</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>132</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>22</v>
@@ -16176,14 +15890,14 @@
     </row>
     <row r="6" spans="1:26" ht="13.5" customHeight="1">
       <c r="A6" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="B6" s="20">
+        <v>134</v>
+      </c>
+      <c r="B6" s="18">
         <f ca="1">TODAY()-WEEKDAY(TODAY(),1)+1</f>
         <v>46208</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>22</v>
@@ -16191,14 +15905,14 @@
     </row>
     <row r="7" spans="1:26" ht="13.5" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="B7" s="21" t="e">
+        <v>136</v>
+      </c>
+      <c r="B7" s="19" t="e">
         <f ca="1">MOD(B3-1+INT((B6-B2)/7),B1)+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>22</v>
@@ -16206,14 +15920,14 @@
     </row>
     <row r="8" spans="1:26" ht="13.5" customHeight="1">
       <c r="A8" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="B8" s="20">
+        <v>138</v>
+      </c>
+      <c r="B8" s="18">
         <f t="shared" ref="B8:B9" si="0">B2</f>
         <v>5</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>22</v>
@@ -16221,14 +15935,14 @@
     </row>
     <row r="9" spans="1:26" ht="13.5" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="B9" s="21">
+        <v>140</v>
+      </c>
+      <c r="B9" s="19">
         <f t="shared" si="0"/>
         <v>46173</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>22</v>
@@ -17247,7 +16961,7 @@
   <sheetData>
     <row r="1" spans="1:26" ht="13.5" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>2</v>
@@ -17257,7 +16971,7 @@
       </c>
       <c r="D1" s="2"/>
       <c r="E1" s="1" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F1" s="1"/>
       <c r="G1" s="2"/>
@@ -17289,10 +17003,10 @@
         <v>5</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="3" spans="1:26" ht="13.5" customHeight="1">
@@ -17303,10 +17017,10 @@
         <v>5</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="4" spans="1:26" ht="13.5" customHeight="1">
@@ -17317,10 +17031,10 @@
         <v>5</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="13.5" customHeight="1">
@@ -17331,10 +17045,10 @@
         <v>5</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="6" spans="1:26" ht="13.5" customHeight="1">
@@ -17345,10 +17059,10 @@
         <v>5</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="7" spans="1:26" ht="13.5" customHeight="1">
@@ -17369,7 +17083,7 @@
     </row>
     <row r="9" spans="1:26" ht="13.5" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>5</v>
@@ -17393,7 +17107,7 @@
     </row>
     <row r="12" spans="1:26" ht="13.5" customHeight="1">
       <c r="A12" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>5</v>
@@ -17401,7 +17115,7 @@
     </row>
     <row r="13" spans="1:26" ht="13.5" customHeight="1">
       <c r="A13" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>5</v>
@@ -17521,7 +17235,7 @@
     </row>
     <row r="28" spans="1:2" ht="13.5" customHeight="1">
       <c r="A28" s="4" t="s">
-        <v>107</v>
+        <v>154</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>5</v>
@@ -17545,7 +17259,7 @@
     </row>
     <row r="31" spans="1:2" ht="13.5" customHeight="1">
       <c r="A31" s="4" t="s">
-        <v>106</v>
+        <v>155</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>5</v>
@@ -17625,7 +17339,7 @@
     </row>
     <row r="41" spans="1:2" ht="13.5" customHeight="1">
       <c r="A41" s="4" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>5</v>
@@ -17676,7 +17390,7 @@
         <v>26</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
     </row>
     <row r="48" spans="1:2" ht="13.5" customHeight="1">
@@ -17713,7 +17427,7 @@
     </row>
     <row r="52" spans="1:2" ht="13.5" customHeight="1">
       <c r="A52" s="4" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="B52" s="4" t="s">
         <v>5</v>
@@ -17729,18 +17443,18 @@
     </row>
     <row r="54" spans="1:2" ht="13.5" customHeight="1">
       <c r="A54" s="4" t="s">
-        <v>104</v>
+        <v>159</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
     </row>
     <row r="55" spans="1:2" ht="13.5" customHeight="1">
       <c r="A55" s="4" t="s">
-        <v>105</v>
+        <v>160</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
     </row>
     <row r="56" spans="1:2" ht="13.5" customHeight="1">
@@ -19590,284 +19304,1262 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D9F9C71-360F-40CE-8BFB-A6B0FC41681D}">
-  <dimension ref="A1:D24"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <dimension ref="A1:D1000"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.59765625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="8.796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.3984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.8984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.69921875" customWidth="1"/>
+    <col min="2" max="2" width="7.3984375" customWidth="1"/>
+    <col min="3" max="3" width="6.5" customWidth="1"/>
+    <col min="4" max="4" width="5.8984375" customWidth="1"/>
+    <col min="5" max="26" width="10.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="22" t="s">
+    <row r="1" spans="1:4" ht="13.5" customHeight="1">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22" t="s">
+      <c r="B1" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="22" t="s">
+      <c r="C1" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="22" t="s">
+      <c r="D1" s="20" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
-      <c r="A2" t="s">
-        <v>155</v>
-      </c>
-      <c r="B2" t="s">
-        <v>156</v>
-      </c>
-      <c r="C2" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" t="s">
+    <row r="2" spans="1:4" ht="13.5" customHeight="1">
+      <c r="A2" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" s="21" t="s">
+        <v>120</v>
+      </c>
+      <c r="C2" s="21" t="s">
         <v>157</v>
       </c>
-      <c r="B3" t="s">
-        <v>156</v>
-      </c>
-      <c r="C3" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" t="s">
-        <v>158</v>
-      </c>
-      <c r="B4" t="s">
-        <v>156</v>
-      </c>
-      <c r="C4" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" t="s">
-        <v>159</v>
-      </c>
-      <c r="B5" t="s">
-        <v>156</v>
-      </c>
-      <c r="C5" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" t="s">
-        <v>169</v>
-      </c>
-      <c r="B6" t="s">
+    </row>
+    <row r="3" spans="1:4" ht="13.5" customHeight="1">
+      <c r="A3" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>120</v>
+      </c>
+      <c r="C3" s="21" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="13.5" customHeight="1">
+      <c r="A4" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>120</v>
+      </c>
+      <c r="C4" s="21" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="13.5" customHeight="1">
+      <c r="A5" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="21" t="s">
+        <v>120</v>
+      </c>
+      <c r="C5" s="21" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="13.5" customHeight="1">
+      <c r="A6" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" s="21" t="s">
+        <v>115</v>
+      </c>
+      <c r="C6" s="21" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="13.5" customHeight="1">
+      <c r="A7" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="C6" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" t="s">
-        <v>171</v>
-      </c>
-      <c r="B7" t="s">
-        <v>161</v>
-      </c>
-      <c r="C7" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" t="s">
-        <v>172</v>
-      </c>
-      <c r="B8" t="s">
-        <v>161</v>
-      </c>
-      <c r="C8" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" t="s">
+      <c r="B7" s="21" t="s">
+        <v>115</v>
+      </c>
+      <c r="C7" s="21" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="13.5" customHeight="1">
+      <c r="A8" s="21" t="s">
+        <v>162</v>
+      </c>
+      <c r="B8" s="21" t="s">
+        <v>115</v>
+      </c>
+      <c r="C8" s="21" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="13.5" customHeight="1">
+      <c r="A9" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="21" t="s">
+        <v>116</v>
+      </c>
+      <c r="C9" s="21" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="13.5" customHeight="1">
+      <c r="A10" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="21" t="s">
+        <v>116</v>
+      </c>
+      <c r="C10" s="21" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="13.5" customHeight="1">
+      <c r="A11" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="B11" s="21" t="s">
+        <v>116</v>
+      </c>
+      <c r="C11" s="21" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="13.5" customHeight="1">
+      <c r="A12" s="21" t="s">
+        <v>163</v>
+      </c>
+      <c r="B12" s="21" t="s">
+        <v>116</v>
+      </c>
+      <c r="C12" s="21" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="13.5" customHeight="1">
+      <c r="A13" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13" s="21" t="s">
+        <v>117</v>
+      </c>
+      <c r="C13" s="21" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="13.5" customHeight="1">
+      <c r="A14" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" s="21" t="s">
+        <v>117</v>
+      </c>
+      <c r="C14" s="21" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="13.5" customHeight="1">
+      <c r="A15" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" s="21" t="s">
+        <v>117</v>
+      </c>
+      <c r="C15" s="21" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="13.5" customHeight="1">
+      <c r="A16" s="21" t="s">
         <v>164</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B16" s="21" t="s">
+        <v>117</v>
+      </c>
+      <c r="C16" s="21" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="13.5" customHeight="1">
+      <c r="A17" s="21" t="s">
         <v>165</v>
       </c>
-      <c r="C9" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" t="s">
-        <v>166</v>
-      </c>
-      <c r="B10" t="s">
-        <v>165</v>
-      </c>
-      <c r="C10" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" t="s">
-        <v>167</v>
-      </c>
-      <c r="B11" t="s">
-        <v>165</v>
-      </c>
-      <c r="C11" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" t="s">
-        <v>168</v>
-      </c>
-      <c r="B12" t="s">
-        <v>165</v>
-      </c>
-      <c r="C12" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" t="s">
-        <v>160</v>
-      </c>
-      <c r="B13" t="s">
-        <v>170</v>
-      </c>
-      <c r="C13" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" t="s">
-        <v>162</v>
-      </c>
-      <c r="B14" t="s">
-        <v>170</v>
-      </c>
-      <c r="C14" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" t="s">
-        <v>79</v>
-      </c>
-      <c r="B15" t="s">
-        <v>170</v>
-      </c>
-      <c r="C15" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" t="s">
-        <v>163</v>
-      </c>
-      <c r="B16" t="s">
-        <v>170</v>
-      </c>
-      <c r="C16" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" t="s">
-        <v>173</v>
-      </c>
-      <c r="B17" t="s">
-        <v>174</v>
-      </c>
-      <c r="C17" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" t="s">
-        <v>175</v>
-      </c>
-      <c r="B18" t="s">
-        <v>174</v>
-      </c>
-      <c r="C18" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" t="s">
-        <v>176</v>
-      </c>
-      <c r="B19" t="s">
-        <v>174</v>
-      </c>
-      <c r="C19" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" t="s">
-        <v>177</v>
-      </c>
-      <c r="B20" t="s">
-        <v>174</v>
-      </c>
-      <c r="C20" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" t="s">
-        <v>178</v>
-      </c>
-      <c r="B21" t="s">
-        <v>179</v>
-      </c>
-      <c r="C21" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" t="s">
-        <v>180</v>
-      </c>
-      <c r="B22" t="s">
-        <v>179</v>
-      </c>
-      <c r="C22" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" t="s">
-        <v>181</v>
-      </c>
-      <c r="B23" t="s">
-        <v>179</v>
-      </c>
-      <c r="C23" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" t="s">
-        <v>182</v>
-      </c>
-      <c r="B24" t="s">
-        <v>179</v>
-      </c>
-      <c r="C24" t="s">
-        <v>152</v>
-      </c>
-    </row>
+      <c r="B17" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="C17" s="21" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="13.5" customHeight="1">
+      <c r="A18" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="B18" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="C18" s="21" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="13.5" customHeight="1">
+      <c r="A19" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="B19" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="C19" s="21" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="13.5" customHeight="1">
+      <c r="A20" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="C20" s="21" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="13.5" customHeight="1">
+      <c r="A21" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="C21" s="21" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="13.5" customHeight="1">
+      <c r="A22" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="B22" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="C22" s="21" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="13.5" customHeight="1">
+      <c r="A23" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="B23" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="C23" s="21" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="13.5" customHeight="1">
+      <c r="A24" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="C24" s="21" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="13.5" customHeight="1"/>
+    <row r="26" spans="1:3" ht="13.5" customHeight="1"/>
+    <row r="27" spans="1:3" ht="13.5" customHeight="1"/>
+    <row r="28" spans="1:3" ht="13.5" customHeight="1"/>
+    <row r="29" spans="1:3" ht="13.5" customHeight="1"/>
+    <row r="30" spans="1:3" ht="13.5" customHeight="1"/>
+    <row r="31" spans="1:3" ht="13.5" customHeight="1"/>
+    <row r="32" spans="1:3" ht="13.5" customHeight="1"/>
+    <row r="33" ht="13.5" customHeight="1"/>
+    <row r="34" ht="13.5" customHeight="1"/>
+    <row r="35" ht="13.5" customHeight="1"/>
+    <row r="36" ht="13.5" customHeight="1"/>
+    <row r="37" ht="13.5" customHeight="1"/>
+    <row r="38" ht="13.5" customHeight="1"/>
+    <row r="39" ht="13.5" customHeight="1"/>
+    <row r="40" ht="13.5" customHeight="1"/>
+    <row r="41" ht="13.5" customHeight="1"/>
+    <row r="42" ht="13.5" customHeight="1"/>
+    <row r="43" ht="13.5" customHeight="1"/>
+    <row r="44" ht="13.5" customHeight="1"/>
+    <row r="45" ht="13.5" customHeight="1"/>
+    <row r="46" ht="13.5" customHeight="1"/>
+    <row r="47" ht="13.5" customHeight="1"/>
+    <row r="48" ht="13.5" customHeight="1"/>
+    <row r="49" ht="13.5" customHeight="1"/>
+    <row r="50" ht="13.5" customHeight="1"/>
+    <row r="51" ht="13.5" customHeight="1"/>
+    <row r="52" ht="13.5" customHeight="1"/>
+    <row r="53" ht="13.5" customHeight="1"/>
+    <row r="54" ht="13.5" customHeight="1"/>
+    <row r="55" ht="13.5" customHeight="1"/>
+    <row r="56" ht="13.5" customHeight="1"/>
+    <row r="57" ht="13.5" customHeight="1"/>
+    <row r="58" ht="13.5" customHeight="1"/>
+    <row r="59" ht="13.5" customHeight="1"/>
+    <row r="60" ht="13.5" customHeight="1"/>
+    <row r="61" ht="13.5" customHeight="1"/>
+    <row r="62" ht="13.5" customHeight="1"/>
+    <row r="63" ht="13.5" customHeight="1"/>
+    <row r="64" ht="13.5" customHeight="1"/>
+    <row r="65" ht="13.5" customHeight="1"/>
+    <row r="66" ht="13.5" customHeight="1"/>
+    <row r="67" ht="13.5" customHeight="1"/>
+    <row r="68" ht="13.5" customHeight="1"/>
+    <row r="69" ht="13.5" customHeight="1"/>
+    <row r="70" ht="13.5" customHeight="1"/>
+    <row r="71" ht="13.5" customHeight="1"/>
+    <row r="72" ht="13.5" customHeight="1"/>
+    <row r="73" ht="13.5" customHeight="1"/>
+    <row r="74" ht="13.5" customHeight="1"/>
+    <row r="75" ht="13.5" customHeight="1"/>
+    <row r="76" ht="13.5" customHeight="1"/>
+    <row r="77" ht="13.5" customHeight="1"/>
+    <row r="78" ht="13.5" customHeight="1"/>
+    <row r="79" ht="13.5" customHeight="1"/>
+    <row r="80" ht="13.5" customHeight="1"/>
+    <row r="81" ht="13.5" customHeight="1"/>
+    <row r="82" ht="13.5" customHeight="1"/>
+    <row r="83" ht="13.5" customHeight="1"/>
+    <row r="84" ht="13.5" customHeight="1"/>
+    <row r="85" ht="13.5" customHeight="1"/>
+    <row r="86" ht="13.5" customHeight="1"/>
+    <row r="87" ht="13.5" customHeight="1"/>
+    <row r="88" ht="13.5" customHeight="1"/>
+    <row r="89" ht="13.5" customHeight="1"/>
+    <row r="90" ht="13.5" customHeight="1"/>
+    <row r="91" ht="13.5" customHeight="1"/>
+    <row r="92" ht="13.5" customHeight="1"/>
+    <row r="93" ht="13.5" customHeight="1"/>
+    <row r="94" ht="13.5" customHeight="1"/>
+    <row r="95" ht="13.5" customHeight="1"/>
+    <row r="96" ht="13.5" customHeight="1"/>
+    <row r="97" ht="13.5" customHeight="1"/>
+    <row r="98" ht="13.5" customHeight="1"/>
+    <row r="99" ht="13.5" customHeight="1"/>
+    <row r="100" ht="13.5" customHeight="1"/>
+    <row r="101" ht="13.5" customHeight="1"/>
+    <row r="102" ht="13.5" customHeight="1"/>
+    <row r="103" ht="13.5" customHeight="1"/>
+    <row r="104" ht="13.5" customHeight="1"/>
+    <row r="105" ht="13.5" customHeight="1"/>
+    <row r="106" ht="13.5" customHeight="1"/>
+    <row r="107" ht="13.5" customHeight="1"/>
+    <row r="108" ht="13.5" customHeight="1"/>
+    <row r="109" ht="13.5" customHeight="1"/>
+    <row r="110" ht="13.5" customHeight="1"/>
+    <row r="111" ht="13.5" customHeight="1"/>
+    <row r="112" ht="13.5" customHeight="1"/>
+    <row r="113" ht="13.5" customHeight="1"/>
+    <row r="114" ht="13.5" customHeight="1"/>
+    <row r="115" ht="13.5" customHeight="1"/>
+    <row r="116" ht="13.5" customHeight="1"/>
+    <row r="117" ht="13.5" customHeight="1"/>
+    <row r="118" ht="13.5" customHeight="1"/>
+    <row r="119" ht="13.5" customHeight="1"/>
+    <row r="120" ht="13.5" customHeight="1"/>
+    <row r="121" ht="13.5" customHeight="1"/>
+    <row r="122" ht="13.5" customHeight="1"/>
+    <row r="123" ht="13.5" customHeight="1"/>
+    <row r="124" ht="13.5" customHeight="1"/>
+    <row r="125" ht="13.5" customHeight="1"/>
+    <row r="126" ht="13.5" customHeight="1"/>
+    <row r="127" ht="13.5" customHeight="1"/>
+    <row r="128" ht="13.5" customHeight="1"/>
+    <row r="129" ht="13.5" customHeight="1"/>
+    <row r="130" ht="13.5" customHeight="1"/>
+    <row r="131" ht="13.5" customHeight="1"/>
+    <row r="132" ht="13.5" customHeight="1"/>
+    <row r="133" ht="13.5" customHeight="1"/>
+    <row r="134" ht="13.5" customHeight="1"/>
+    <row r="135" ht="13.5" customHeight="1"/>
+    <row r="136" ht="13.5" customHeight="1"/>
+    <row r="137" ht="13.5" customHeight="1"/>
+    <row r="138" ht="13.5" customHeight="1"/>
+    <row r="139" ht="13.5" customHeight="1"/>
+    <row r="140" ht="13.5" customHeight="1"/>
+    <row r="141" ht="13.5" customHeight="1"/>
+    <row r="142" ht="13.5" customHeight="1"/>
+    <row r="143" ht="13.5" customHeight="1"/>
+    <row r="144" ht="13.5" customHeight="1"/>
+    <row r="145" ht="13.5" customHeight="1"/>
+    <row r="146" ht="13.5" customHeight="1"/>
+    <row r="147" ht="13.5" customHeight="1"/>
+    <row r="148" ht="13.5" customHeight="1"/>
+    <row r="149" ht="13.5" customHeight="1"/>
+    <row r="150" ht="13.5" customHeight="1"/>
+    <row r="151" ht="13.5" customHeight="1"/>
+    <row r="152" ht="13.5" customHeight="1"/>
+    <row r="153" ht="13.5" customHeight="1"/>
+    <row r="154" ht="13.5" customHeight="1"/>
+    <row r="155" ht="13.5" customHeight="1"/>
+    <row r="156" ht="13.5" customHeight="1"/>
+    <row r="157" ht="13.5" customHeight="1"/>
+    <row r="158" ht="13.5" customHeight="1"/>
+    <row r="159" ht="13.5" customHeight="1"/>
+    <row r="160" ht="13.5" customHeight="1"/>
+    <row r="161" ht="13.5" customHeight="1"/>
+    <row r="162" ht="13.5" customHeight="1"/>
+    <row r="163" ht="13.5" customHeight="1"/>
+    <row r="164" ht="13.5" customHeight="1"/>
+    <row r="165" ht="13.5" customHeight="1"/>
+    <row r="166" ht="13.5" customHeight="1"/>
+    <row r="167" ht="13.5" customHeight="1"/>
+    <row r="168" ht="13.5" customHeight="1"/>
+    <row r="169" ht="13.5" customHeight="1"/>
+    <row r="170" ht="13.5" customHeight="1"/>
+    <row r="171" ht="13.5" customHeight="1"/>
+    <row r="172" ht="13.5" customHeight="1"/>
+    <row r="173" ht="13.5" customHeight="1"/>
+    <row r="174" ht="13.5" customHeight="1"/>
+    <row r="175" ht="13.5" customHeight="1"/>
+    <row r="176" ht="13.5" customHeight="1"/>
+    <row r="177" ht="13.5" customHeight="1"/>
+    <row r="178" ht="13.5" customHeight="1"/>
+    <row r="179" ht="13.5" customHeight="1"/>
+    <row r="180" ht="13.5" customHeight="1"/>
+    <row r="181" ht="13.5" customHeight="1"/>
+    <row r="182" ht="13.5" customHeight="1"/>
+    <row r="183" ht="13.5" customHeight="1"/>
+    <row r="184" ht="13.5" customHeight="1"/>
+    <row r="185" ht="13.5" customHeight="1"/>
+    <row r="186" ht="13.5" customHeight="1"/>
+    <row r="187" ht="13.5" customHeight="1"/>
+    <row r="188" ht="13.5" customHeight="1"/>
+    <row r="189" ht="13.5" customHeight="1"/>
+    <row r="190" ht="13.5" customHeight="1"/>
+    <row r="191" ht="13.5" customHeight="1"/>
+    <row r="192" ht="13.5" customHeight="1"/>
+    <row r="193" ht="13.5" customHeight="1"/>
+    <row r="194" ht="13.5" customHeight="1"/>
+    <row r="195" ht="13.5" customHeight="1"/>
+    <row r="196" ht="13.5" customHeight="1"/>
+    <row r="197" ht="13.5" customHeight="1"/>
+    <row r="198" ht="13.5" customHeight="1"/>
+    <row r="199" ht="13.5" customHeight="1"/>
+    <row r="200" ht="13.5" customHeight="1"/>
+    <row r="201" ht="13.5" customHeight="1"/>
+    <row r="202" ht="13.5" customHeight="1"/>
+    <row r="203" ht="13.5" customHeight="1"/>
+    <row r="204" ht="13.5" customHeight="1"/>
+    <row r="205" ht="13.5" customHeight="1"/>
+    <row r="206" ht="13.5" customHeight="1"/>
+    <row r="207" ht="13.5" customHeight="1"/>
+    <row r="208" ht="13.5" customHeight="1"/>
+    <row r="209" ht="13.5" customHeight="1"/>
+    <row r="210" ht="13.5" customHeight="1"/>
+    <row r="211" ht="13.5" customHeight="1"/>
+    <row r="212" ht="13.5" customHeight="1"/>
+    <row r="213" ht="13.5" customHeight="1"/>
+    <row r="214" ht="13.5" customHeight="1"/>
+    <row r="215" ht="13.5" customHeight="1"/>
+    <row r="216" ht="13.5" customHeight="1"/>
+    <row r="217" ht="13.5" customHeight="1"/>
+    <row r="218" ht="13.5" customHeight="1"/>
+    <row r="219" ht="13.5" customHeight="1"/>
+    <row r="220" ht="13.5" customHeight="1"/>
+    <row r="221" ht="13.5" customHeight="1"/>
+    <row r="222" ht="13.5" customHeight="1"/>
+    <row r="223" ht="13.5" customHeight="1"/>
+    <row r="224" ht="13.5" customHeight="1"/>
+    <row r="225" ht="13.5" customHeight="1"/>
+    <row r="226" ht="13.5" customHeight="1"/>
+    <row r="227" ht="13.5" customHeight="1"/>
+    <row r="228" ht="13.5" customHeight="1"/>
+    <row r="229" ht="13.5" customHeight="1"/>
+    <row r="230" ht="13.5" customHeight="1"/>
+    <row r="231" ht="13.5" customHeight="1"/>
+    <row r="232" ht="13.5" customHeight="1"/>
+    <row r="233" ht="13.5" customHeight="1"/>
+    <row r="234" ht="13.5" customHeight="1"/>
+    <row r="235" ht="13.5" customHeight="1"/>
+    <row r="236" ht="13.5" customHeight="1"/>
+    <row r="237" ht="13.5" customHeight="1"/>
+    <row r="238" ht="13.5" customHeight="1"/>
+    <row r="239" ht="13.5" customHeight="1"/>
+    <row r="240" ht="13.5" customHeight="1"/>
+    <row r="241" ht="13.5" customHeight="1"/>
+    <row r="242" ht="13.5" customHeight="1"/>
+    <row r="243" ht="13.5" customHeight="1"/>
+    <row r="244" ht="13.5" customHeight="1"/>
+    <row r="245" ht="13.5" customHeight="1"/>
+    <row r="246" ht="13.5" customHeight="1"/>
+    <row r="247" ht="13.5" customHeight="1"/>
+    <row r="248" ht="13.5" customHeight="1"/>
+    <row r="249" ht="13.5" customHeight="1"/>
+    <row r="250" ht="13.5" customHeight="1"/>
+    <row r="251" ht="13.5" customHeight="1"/>
+    <row r="252" ht="13.5" customHeight="1"/>
+    <row r="253" ht="13.5" customHeight="1"/>
+    <row r="254" ht="13.5" customHeight="1"/>
+    <row r="255" ht="13.5" customHeight="1"/>
+    <row r="256" ht="13.5" customHeight="1"/>
+    <row r="257" ht="13.5" customHeight="1"/>
+    <row r="258" ht="13.5" customHeight="1"/>
+    <row r="259" ht="13.5" customHeight="1"/>
+    <row r="260" ht="13.5" customHeight="1"/>
+    <row r="261" ht="13.5" customHeight="1"/>
+    <row r="262" ht="13.5" customHeight="1"/>
+    <row r="263" ht="13.5" customHeight="1"/>
+    <row r="264" ht="13.5" customHeight="1"/>
+    <row r="265" ht="13.5" customHeight="1"/>
+    <row r="266" ht="13.5" customHeight="1"/>
+    <row r="267" ht="13.5" customHeight="1"/>
+    <row r="268" ht="13.5" customHeight="1"/>
+    <row r="269" ht="13.5" customHeight="1"/>
+    <row r="270" ht="13.5" customHeight="1"/>
+    <row r="271" ht="13.5" customHeight="1"/>
+    <row r="272" ht="13.5" customHeight="1"/>
+    <row r="273" ht="13.5" customHeight="1"/>
+    <row r="274" ht="13.5" customHeight="1"/>
+    <row r="275" ht="13.5" customHeight="1"/>
+    <row r="276" ht="13.5" customHeight="1"/>
+    <row r="277" ht="13.5" customHeight="1"/>
+    <row r="278" ht="13.5" customHeight="1"/>
+    <row r="279" ht="13.5" customHeight="1"/>
+    <row r="280" ht="13.5" customHeight="1"/>
+    <row r="281" ht="13.5" customHeight="1"/>
+    <row r="282" ht="13.5" customHeight="1"/>
+    <row r="283" ht="13.5" customHeight="1"/>
+    <row r="284" ht="13.5" customHeight="1"/>
+    <row r="285" ht="13.5" customHeight="1"/>
+    <row r="286" ht="13.5" customHeight="1"/>
+    <row r="287" ht="13.5" customHeight="1"/>
+    <row r="288" ht="13.5" customHeight="1"/>
+    <row r="289" ht="13.5" customHeight="1"/>
+    <row r="290" ht="13.5" customHeight="1"/>
+    <row r="291" ht="13.5" customHeight="1"/>
+    <row r="292" ht="13.5" customHeight="1"/>
+    <row r="293" ht="13.5" customHeight="1"/>
+    <row r="294" ht="13.5" customHeight="1"/>
+    <row r="295" ht="13.5" customHeight="1"/>
+    <row r="296" ht="13.5" customHeight="1"/>
+    <row r="297" ht="13.5" customHeight="1"/>
+    <row r="298" ht="13.5" customHeight="1"/>
+    <row r="299" ht="13.5" customHeight="1"/>
+    <row r="300" ht="13.5" customHeight="1"/>
+    <row r="301" ht="13.5" customHeight="1"/>
+    <row r="302" ht="13.5" customHeight="1"/>
+    <row r="303" ht="13.5" customHeight="1"/>
+    <row r="304" ht="13.5" customHeight="1"/>
+    <row r="305" ht="13.5" customHeight="1"/>
+    <row r="306" ht="13.5" customHeight="1"/>
+    <row r="307" ht="13.5" customHeight="1"/>
+    <row r="308" ht="13.5" customHeight="1"/>
+    <row r="309" ht="13.5" customHeight="1"/>
+    <row r="310" ht="13.5" customHeight="1"/>
+    <row r="311" ht="13.5" customHeight="1"/>
+    <row r="312" ht="13.5" customHeight="1"/>
+    <row r="313" ht="13.5" customHeight="1"/>
+    <row r="314" ht="13.5" customHeight="1"/>
+    <row r="315" ht="13.5" customHeight="1"/>
+    <row r="316" ht="13.5" customHeight="1"/>
+    <row r="317" ht="13.5" customHeight="1"/>
+    <row r="318" ht="13.5" customHeight="1"/>
+    <row r="319" ht="13.5" customHeight="1"/>
+    <row r="320" ht="13.5" customHeight="1"/>
+    <row r="321" ht="13.5" customHeight="1"/>
+    <row r="322" ht="13.5" customHeight="1"/>
+    <row r="323" ht="13.5" customHeight="1"/>
+    <row r="324" ht="13.5" customHeight="1"/>
+    <row r="325" ht="13.5" customHeight="1"/>
+    <row r="326" ht="13.5" customHeight="1"/>
+    <row r="327" ht="13.5" customHeight="1"/>
+    <row r="328" ht="13.5" customHeight="1"/>
+    <row r="329" ht="13.5" customHeight="1"/>
+    <row r="330" ht="13.5" customHeight="1"/>
+    <row r="331" ht="13.5" customHeight="1"/>
+    <row r="332" ht="13.5" customHeight="1"/>
+    <row r="333" ht="13.5" customHeight="1"/>
+    <row r="334" ht="13.5" customHeight="1"/>
+    <row r="335" ht="13.5" customHeight="1"/>
+    <row r="336" ht="13.5" customHeight="1"/>
+    <row r="337" ht="13.5" customHeight="1"/>
+    <row r="338" ht="13.5" customHeight="1"/>
+    <row r="339" ht="13.5" customHeight="1"/>
+    <row r="340" ht="13.5" customHeight="1"/>
+    <row r="341" ht="13.5" customHeight="1"/>
+    <row r="342" ht="13.5" customHeight="1"/>
+    <row r="343" ht="13.5" customHeight="1"/>
+    <row r="344" ht="13.5" customHeight="1"/>
+    <row r="345" ht="13.5" customHeight="1"/>
+    <row r="346" ht="13.5" customHeight="1"/>
+    <row r="347" ht="13.5" customHeight="1"/>
+    <row r="348" ht="13.5" customHeight="1"/>
+    <row r="349" ht="13.5" customHeight="1"/>
+    <row r="350" ht="13.5" customHeight="1"/>
+    <row r="351" ht="13.5" customHeight="1"/>
+    <row r="352" ht="13.5" customHeight="1"/>
+    <row r="353" ht="13.5" customHeight="1"/>
+    <row r="354" ht="13.5" customHeight="1"/>
+    <row r="355" ht="13.5" customHeight="1"/>
+    <row r="356" ht="13.5" customHeight="1"/>
+    <row r="357" ht="13.5" customHeight="1"/>
+    <row r="358" ht="13.5" customHeight="1"/>
+    <row r="359" ht="13.5" customHeight="1"/>
+    <row r="360" ht="13.5" customHeight="1"/>
+    <row r="361" ht="13.5" customHeight="1"/>
+    <row r="362" ht="13.5" customHeight="1"/>
+    <row r="363" ht="13.5" customHeight="1"/>
+    <row r="364" ht="13.5" customHeight="1"/>
+    <row r="365" ht="13.5" customHeight="1"/>
+    <row r="366" ht="13.5" customHeight="1"/>
+    <row r="367" ht="13.5" customHeight="1"/>
+    <row r="368" ht="13.5" customHeight="1"/>
+    <row r="369" ht="13.5" customHeight="1"/>
+    <row r="370" ht="13.5" customHeight="1"/>
+    <row r="371" ht="13.5" customHeight="1"/>
+    <row r="372" ht="13.5" customHeight="1"/>
+    <row r="373" ht="13.5" customHeight="1"/>
+    <row r="374" ht="13.5" customHeight="1"/>
+    <row r="375" ht="13.5" customHeight="1"/>
+    <row r="376" ht="13.5" customHeight="1"/>
+    <row r="377" ht="13.5" customHeight="1"/>
+    <row r="378" ht="13.5" customHeight="1"/>
+    <row r="379" ht="13.5" customHeight="1"/>
+    <row r="380" ht="13.5" customHeight="1"/>
+    <row r="381" ht="13.5" customHeight="1"/>
+    <row r="382" ht="13.5" customHeight="1"/>
+    <row r="383" ht="13.5" customHeight="1"/>
+    <row r="384" ht="13.5" customHeight="1"/>
+    <row r="385" ht="13.5" customHeight="1"/>
+    <row r="386" ht="13.5" customHeight="1"/>
+    <row r="387" ht="13.5" customHeight="1"/>
+    <row r="388" ht="13.5" customHeight="1"/>
+    <row r="389" ht="13.5" customHeight="1"/>
+    <row r="390" ht="13.5" customHeight="1"/>
+    <row r="391" ht="13.5" customHeight="1"/>
+    <row r="392" ht="13.5" customHeight="1"/>
+    <row r="393" ht="13.5" customHeight="1"/>
+    <row r="394" ht="13.5" customHeight="1"/>
+    <row r="395" ht="13.5" customHeight="1"/>
+    <row r="396" ht="13.5" customHeight="1"/>
+    <row r="397" ht="13.5" customHeight="1"/>
+    <row r="398" ht="13.5" customHeight="1"/>
+    <row r="399" ht="13.5" customHeight="1"/>
+    <row r="400" ht="13.5" customHeight="1"/>
+    <row r="401" ht="13.5" customHeight="1"/>
+    <row r="402" ht="13.5" customHeight="1"/>
+    <row r="403" ht="13.5" customHeight="1"/>
+    <row r="404" ht="13.5" customHeight="1"/>
+    <row r="405" ht="13.5" customHeight="1"/>
+    <row r="406" ht="13.5" customHeight="1"/>
+    <row r="407" ht="13.5" customHeight="1"/>
+    <row r="408" ht="13.5" customHeight="1"/>
+    <row r="409" ht="13.5" customHeight="1"/>
+    <row r="410" ht="13.5" customHeight="1"/>
+    <row r="411" ht="13.5" customHeight="1"/>
+    <row r="412" ht="13.5" customHeight="1"/>
+    <row r="413" ht="13.5" customHeight="1"/>
+    <row r="414" ht="13.5" customHeight="1"/>
+    <row r="415" ht="13.5" customHeight="1"/>
+    <row r="416" ht="13.5" customHeight="1"/>
+    <row r="417" ht="13.5" customHeight="1"/>
+    <row r="418" ht="13.5" customHeight="1"/>
+    <row r="419" ht="13.5" customHeight="1"/>
+    <row r="420" ht="13.5" customHeight="1"/>
+    <row r="421" ht="13.5" customHeight="1"/>
+    <row r="422" ht="13.5" customHeight="1"/>
+    <row r="423" ht="13.5" customHeight="1"/>
+    <row r="424" ht="13.5" customHeight="1"/>
+    <row r="425" ht="13.5" customHeight="1"/>
+    <row r="426" ht="13.5" customHeight="1"/>
+    <row r="427" ht="13.5" customHeight="1"/>
+    <row r="428" ht="13.5" customHeight="1"/>
+    <row r="429" ht="13.5" customHeight="1"/>
+    <row r="430" ht="13.5" customHeight="1"/>
+    <row r="431" ht="13.5" customHeight="1"/>
+    <row r="432" ht="13.5" customHeight="1"/>
+    <row r="433" ht="13.5" customHeight="1"/>
+    <row r="434" ht="13.5" customHeight="1"/>
+    <row r="435" ht="13.5" customHeight="1"/>
+    <row r="436" ht="13.5" customHeight="1"/>
+    <row r="437" ht="13.5" customHeight="1"/>
+    <row r="438" ht="13.5" customHeight="1"/>
+    <row r="439" ht="13.5" customHeight="1"/>
+    <row r="440" ht="13.5" customHeight="1"/>
+    <row r="441" ht="13.5" customHeight="1"/>
+    <row r="442" ht="13.5" customHeight="1"/>
+    <row r="443" ht="13.5" customHeight="1"/>
+    <row r="444" ht="13.5" customHeight="1"/>
+    <row r="445" ht="13.5" customHeight="1"/>
+    <row r="446" ht="13.5" customHeight="1"/>
+    <row r="447" ht="13.5" customHeight="1"/>
+    <row r="448" ht="13.5" customHeight="1"/>
+    <row r="449" ht="13.5" customHeight="1"/>
+    <row r="450" ht="13.5" customHeight="1"/>
+    <row r="451" ht="13.5" customHeight="1"/>
+    <row r="452" ht="13.5" customHeight="1"/>
+    <row r="453" ht="13.5" customHeight="1"/>
+    <row r="454" ht="13.5" customHeight="1"/>
+    <row r="455" ht="13.5" customHeight="1"/>
+    <row r="456" ht="13.5" customHeight="1"/>
+    <row r="457" ht="13.5" customHeight="1"/>
+    <row r="458" ht="13.5" customHeight="1"/>
+    <row r="459" ht="13.5" customHeight="1"/>
+    <row r="460" ht="13.5" customHeight="1"/>
+    <row r="461" ht="13.5" customHeight="1"/>
+    <row r="462" ht="13.5" customHeight="1"/>
+    <row r="463" ht="13.5" customHeight="1"/>
+    <row r="464" ht="13.5" customHeight="1"/>
+    <row r="465" ht="13.5" customHeight="1"/>
+    <row r="466" ht="13.5" customHeight="1"/>
+    <row r="467" ht="13.5" customHeight="1"/>
+    <row r="468" ht="13.5" customHeight="1"/>
+    <row r="469" ht="13.5" customHeight="1"/>
+    <row r="470" ht="13.5" customHeight="1"/>
+    <row r="471" ht="13.5" customHeight="1"/>
+    <row r="472" ht="13.5" customHeight="1"/>
+    <row r="473" ht="13.5" customHeight="1"/>
+    <row r="474" ht="13.5" customHeight="1"/>
+    <row r="475" ht="13.5" customHeight="1"/>
+    <row r="476" ht="13.5" customHeight="1"/>
+    <row r="477" ht="13.5" customHeight="1"/>
+    <row r="478" ht="13.5" customHeight="1"/>
+    <row r="479" ht="13.5" customHeight="1"/>
+    <row r="480" ht="13.5" customHeight="1"/>
+    <row r="481" ht="13.5" customHeight="1"/>
+    <row r="482" ht="13.5" customHeight="1"/>
+    <row r="483" ht="13.5" customHeight="1"/>
+    <row r="484" ht="13.5" customHeight="1"/>
+    <row r="485" ht="13.5" customHeight="1"/>
+    <row r="486" ht="13.5" customHeight="1"/>
+    <row r="487" ht="13.5" customHeight="1"/>
+    <row r="488" ht="13.5" customHeight="1"/>
+    <row r="489" ht="13.5" customHeight="1"/>
+    <row r="490" ht="13.5" customHeight="1"/>
+    <row r="491" ht="13.5" customHeight="1"/>
+    <row r="492" ht="13.5" customHeight="1"/>
+    <row r="493" ht="13.5" customHeight="1"/>
+    <row r="494" ht="13.5" customHeight="1"/>
+    <row r="495" ht="13.5" customHeight="1"/>
+    <row r="496" ht="13.5" customHeight="1"/>
+    <row r="497" ht="13.5" customHeight="1"/>
+    <row r="498" ht="13.5" customHeight="1"/>
+    <row r="499" ht="13.5" customHeight="1"/>
+    <row r="500" ht="13.5" customHeight="1"/>
+    <row r="501" ht="13.5" customHeight="1"/>
+    <row r="502" ht="13.5" customHeight="1"/>
+    <row r="503" ht="13.5" customHeight="1"/>
+    <row r="504" ht="13.5" customHeight="1"/>
+    <row r="505" ht="13.5" customHeight="1"/>
+    <row r="506" ht="13.5" customHeight="1"/>
+    <row r="507" ht="13.5" customHeight="1"/>
+    <row r="508" ht="13.5" customHeight="1"/>
+    <row r="509" ht="13.5" customHeight="1"/>
+    <row r="510" ht="13.5" customHeight="1"/>
+    <row r="511" ht="13.5" customHeight="1"/>
+    <row r="512" ht="13.5" customHeight="1"/>
+    <row r="513" ht="13.5" customHeight="1"/>
+    <row r="514" ht="13.5" customHeight="1"/>
+    <row r="515" ht="13.5" customHeight="1"/>
+    <row r="516" ht="13.5" customHeight="1"/>
+    <row r="517" ht="13.5" customHeight="1"/>
+    <row r="518" ht="13.5" customHeight="1"/>
+    <row r="519" ht="13.5" customHeight="1"/>
+    <row r="520" ht="13.5" customHeight="1"/>
+    <row r="521" ht="13.5" customHeight="1"/>
+    <row r="522" ht="13.5" customHeight="1"/>
+    <row r="523" ht="13.5" customHeight="1"/>
+    <row r="524" ht="13.5" customHeight="1"/>
+    <row r="525" ht="13.5" customHeight="1"/>
+    <row r="526" ht="13.5" customHeight="1"/>
+    <row r="527" ht="13.5" customHeight="1"/>
+    <row r="528" ht="13.5" customHeight="1"/>
+    <row r="529" ht="13.5" customHeight="1"/>
+    <row r="530" ht="13.5" customHeight="1"/>
+    <row r="531" ht="13.5" customHeight="1"/>
+    <row r="532" ht="13.5" customHeight="1"/>
+    <row r="533" ht="13.5" customHeight="1"/>
+    <row r="534" ht="13.5" customHeight="1"/>
+    <row r="535" ht="13.5" customHeight="1"/>
+    <row r="536" ht="13.5" customHeight="1"/>
+    <row r="537" ht="13.5" customHeight="1"/>
+    <row r="538" ht="13.5" customHeight="1"/>
+    <row r="539" ht="13.5" customHeight="1"/>
+    <row r="540" ht="13.5" customHeight="1"/>
+    <row r="541" ht="13.5" customHeight="1"/>
+    <row r="542" ht="13.5" customHeight="1"/>
+    <row r="543" ht="13.5" customHeight="1"/>
+    <row r="544" ht="13.5" customHeight="1"/>
+    <row r="545" ht="13.5" customHeight="1"/>
+    <row r="546" ht="13.5" customHeight="1"/>
+    <row r="547" ht="13.5" customHeight="1"/>
+    <row r="548" ht="13.5" customHeight="1"/>
+    <row r="549" ht="13.5" customHeight="1"/>
+    <row r="550" ht="13.5" customHeight="1"/>
+    <row r="551" ht="13.5" customHeight="1"/>
+    <row r="552" ht="13.5" customHeight="1"/>
+    <row r="553" ht="13.5" customHeight="1"/>
+    <row r="554" ht="13.5" customHeight="1"/>
+    <row r="555" ht="13.5" customHeight="1"/>
+    <row r="556" ht="13.5" customHeight="1"/>
+    <row r="557" ht="13.5" customHeight="1"/>
+    <row r="558" ht="13.5" customHeight="1"/>
+    <row r="559" ht="13.5" customHeight="1"/>
+    <row r="560" ht="13.5" customHeight="1"/>
+    <row r="561" ht="13.5" customHeight="1"/>
+    <row r="562" ht="13.5" customHeight="1"/>
+    <row r="563" ht="13.5" customHeight="1"/>
+    <row r="564" ht="13.5" customHeight="1"/>
+    <row r="565" ht="13.5" customHeight="1"/>
+    <row r="566" ht="13.5" customHeight="1"/>
+    <row r="567" ht="13.5" customHeight="1"/>
+    <row r="568" ht="13.5" customHeight="1"/>
+    <row r="569" ht="13.5" customHeight="1"/>
+    <row r="570" ht="13.5" customHeight="1"/>
+    <row r="571" ht="13.5" customHeight="1"/>
+    <row r="572" ht="13.5" customHeight="1"/>
+    <row r="573" ht="13.5" customHeight="1"/>
+    <row r="574" ht="13.5" customHeight="1"/>
+    <row r="575" ht="13.5" customHeight="1"/>
+    <row r="576" ht="13.5" customHeight="1"/>
+    <row r="577" ht="13.5" customHeight="1"/>
+    <row r="578" ht="13.5" customHeight="1"/>
+    <row r="579" ht="13.5" customHeight="1"/>
+    <row r="580" ht="13.5" customHeight="1"/>
+    <row r="581" ht="13.5" customHeight="1"/>
+    <row r="582" ht="13.5" customHeight="1"/>
+    <row r="583" ht="13.5" customHeight="1"/>
+    <row r="584" ht="13.5" customHeight="1"/>
+    <row r="585" ht="13.5" customHeight="1"/>
+    <row r="586" ht="13.5" customHeight="1"/>
+    <row r="587" ht="13.5" customHeight="1"/>
+    <row r="588" ht="13.5" customHeight="1"/>
+    <row r="589" ht="13.5" customHeight="1"/>
+    <row r="590" ht="13.5" customHeight="1"/>
+    <row r="591" ht="13.5" customHeight="1"/>
+    <row r="592" ht="13.5" customHeight="1"/>
+    <row r="593" ht="13.5" customHeight="1"/>
+    <row r="594" ht="13.5" customHeight="1"/>
+    <row r="595" ht="13.5" customHeight="1"/>
+    <row r="596" ht="13.5" customHeight="1"/>
+    <row r="597" ht="13.5" customHeight="1"/>
+    <row r="598" ht="13.5" customHeight="1"/>
+    <row r="599" ht="13.5" customHeight="1"/>
+    <row r="600" ht="13.5" customHeight="1"/>
+    <row r="601" ht="13.5" customHeight="1"/>
+    <row r="602" ht="13.5" customHeight="1"/>
+    <row r="603" ht="13.5" customHeight="1"/>
+    <row r="604" ht="13.5" customHeight="1"/>
+    <row r="605" ht="13.5" customHeight="1"/>
+    <row r="606" ht="13.5" customHeight="1"/>
+    <row r="607" ht="13.5" customHeight="1"/>
+    <row r="608" ht="13.5" customHeight="1"/>
+    <row r="609" ht="13.5" customHeight="1"/>
+    <row r="610" ht="13.5" customHeight="1"/>
+    <row r="611" ht="13.5" customHeight="1"/>
+    <row r="612" ht="13.5" customHeight="1"/>
+    <row r="613" ht="13.5" customHeight="1"/>
+    <row r="614" ht="13.5" customHeight="1"/>
+    <row r="615" ht="13.5" customHeight="1"/>
+    <row r="616" ht="13.5" customHeight="1"/>
+    <row r="617" ht="13.5" customHeight="1"/>
+    <row r="618" ht="13.5" customHeight="1"/>
+    <row r="619" ht="13.5" customHeight="1"/>
+    <row r="620" ht="13.5" customHeight="1"/>
+    <row r="621" ht="13.5" customHeight="1"/>
+    <row r="622" ht="13.5" customHeight="1"/>
+    <row r="623" ht="13.5" customHeight="1"/>
+    <row r="624" ht="13.5" customHeight="1"/>
+    <row r="625" ht="13.5" customHeight="1"/>
+    <row r="626" ht="13.5" customHeight="1"/>
+    <row r="627" ht="13.5" customHeight="1"/>
+    <row r="628" ht="13.5" customHeight="1"/>
+    <row r="629" ht="13.5" customHeight="1"/>
+    <row r="630" ht="13.5" customHeight="1"/>
+    <row r="631" ht="13.5" customHeight="1"/>
+    <row r="632" ht="13.5" customHeight="1"/>
+    <row r="633" ht="13.5" customHeight="1"/>
+    <row r="634" ht="13.5" customHeight="1"/>
+    <row r="635" ht="13.5" customHeight="1"/>
+    <row r="636" ht="13.5" customHeight="1"/>
+    <row r="637" ht="13.5" customHeight="1"/>
+    <row r="638" ht="13.5" customHeight="1"/>
+    <row r="639" ht="13.5" customHeight="1"/>
+    <row r="640" ht="13.5" customHeight="1"/>
+    <row r="641" ht="13.5" customHeight="1"/>
+    <row r="642" ht="13.5" customHeight="1"/>
+    <row r="643" ht="13.5" customHeight="1"/>
+    <row r="644" ht="13.5" customHeight="1"/>
+    <row r="645" ht="13.5" customHeight="1"/>
+    <row r="646" ht="13.5" customHeight="1"/>
+    <row r="647" ht="13.5" customHeight="1"/>
+    <row r="648" ht="13.5" customHeight="1"/>
+    <row r="649" ht="13.5" customHeight="1"/>
+    <row r="650" ht="13.5" customHeight="1"/>
+    <row r="651" ht="13.5" customHeight="1"/>
+    <row r="652" ht="13.5" customHeight="1"/>
+    <row r="653" ht="13.5" customHeight="1"/>
+    <row r="654" ht="13.5" customHeight="1"/>
+    <row r="655" ht="13.5" customHeight="1"/>
+    <row r="656" ht="13.5" customHeight="1"/>
+    <row r="657" ht="13.5" customHeight="1"/>
+    <row r="658" ht="13.5" customHeight="1"/>
+    <row r="659" ht="13.5" customHeight="1"/>
+    <row r="660" ht="13.5" customHeight="1"/>
+    <row r="661" ht="13.5" customHeight="1"/>
+    <row r="662" ht="13.5" customHeight="1"/>
+    <row r="663" ht="13.5" customHeight="1"/>
+    <row r="664" ht="13.5" customHeight="1"/>
+    <row r="665" ht="13.5" customHeight="1"/>
+    <row r="666" ht="13.5" customHeight="1"/>
+    <row r="667" ht="13.5" customHeight="1"/>
+    <row r="668" ht="13.5" customHeight="1"/>
+    <row r="669" ht="13.5" customHeight="1"/>
+    <row r="670" ht="13.5" customHeight="1"/>
+    <row r="671" ht="13.5" customHeight="1"/>
+    <row r="672" ht="13.5" customHeight="1"/>
+    <row r="673" ht="13.5" customHeight="1"/>
+    <row r="674" ht="13.5" customHeight="1"/>
+    <row r="675" ht="13.5" customHeight="1"/>
+    <row r="676" ht="13.5" customHeight="1"/>
+    <row r="677" ht="13.5" customHeight="1"/>
+    <row r="678" ht="13.5" customHeight="1"/>
+    <row r="679" ht="13.5" customHeight="1"/>
+    <row r="680" ht="13.5" customHeight="1"/>
+    <row r="681" ht="13.5" customHeight="1"/>
+    <row r="682" ht="13.5" customHeight="1"/>
+    <row r="683" ht="13.5" customHeight="1"/>
+    <row r="684" ht="13.5" customHeight="1"/>
+    <row r="685" ht="13.5" customHeight="1"/>
+    <row r="686" ht="13.5" customHeight="1"/>
+    <row r="687" ht="13.5" customHeight="1"/>
+    <row r="688" ht="13.5" customHeight="1"/>
+    <row r="689" ht="13.5" customHeight="1"/>
+    <row r="690" ht="13.5" customHeight="1"/>
+    <row r="691" ht="13.5" customHeight="1"/>
+    <row r="692" ht="13.5" customHeight="1"/>
+    <row r="693" ht="13.5" customHeight="1"/>
+    <row r="694" ht="13.5" customHeight="1"/>
+    <row r="695" ht="13.5" customHeight="1"/>
+    <row r="696" ht="13.5" customHeight="1"/>
+    <row r="697" ht="13.5" customHeight="1"/>
+    <row r="698" ht="13.5" customHeight="1"/>
+    <row r="699" ht="13.5" customHeight="1"/>
+    <row r="700" ht="13.5" customHeight="1"/>
+    <row r="701" ht="13.5" customHeight="1"/>
+    <row r="702" ht="13.5" customHeight="1"/>
+    <row r="703" ht="13.5" customHeight="1"/>
+    <row r="704" ht="13.5" customHeight="1"/>
+    <row r="705" ht="13.5" customHeight="1"/>
+    <row r="706" ht="13.5" customHeight="1"/>
+    <row r="707" ht="13.5" customHeight="1"/>
+    <row r="708" ht="13.5" customHeight="1"/>
+    <row r="709" ht="13.5" customHeight="1"/>
+    <row r="710" ht="13.5" customHeight="1"/>
+    <row r="711" ht="13.5" customHeight="1"/>
+    <row r="712" ht="13.5" customHeight="1"/>
+    <row r="713" ht="13.5" customHeight="1"/>
+    <row r="714" ht="13.5" customHeight="1"/>
+    <row r="715" ht="13.5" customHeight="1"/>
+    <row r="716" ht="13.5" customHeight="1"/>
+    <row r="717" ht="13.5" customHeight="1"/>
+    <row r="718" ht="13.5" customHeight="1"/>
+    <row r="719" ht="13.5" customHeight="1"/>
+    <row r="720" ht="13.5" customHeight="1"/>
+    <row r="721" ht="13.5" customHeight="1"/>
+    <row r="722" ht="13.5" customHeight="1"/>
+    <row r="723" ht="13.5" customHeight="1"/>
+    <row r="724" ht="13.5" customHeight="1"/>
+    <row r="725" ht="13.5" customHeight="1"/>
+    <row r="726" ht="13.5" customHeight="1"/>
+    <row r="727" ht="13.5" customHeight="1"/>
+    <row r="728" ht="13.5" customHeight="1"/>
+    <row r="729" ht="13.5" customHeight="1"/>
+    <row r="730" ht="13.5" customHeight="1"/>
+    <row r="731" ht="13.5" customHeight="1"/>
+    <row r="732" ht="13.5" customHeight="1"/>
+    <row r="733" ht="13.5" customHeight="1"/>
+    <row r="734" ht="13.5" customHeight="1"/>
+    <row r="735" ht="13.5" customHeight="1"/>
+    <row r="736" ht="13.5" customHeight="1"/>
+    <row r="737" ht="13.5" customHeight="1"/>
+    <row r="738" ht="13.5" customHeight="1"/>
+    <row r="739" ht="13.5" customHeight="1"/>
+    <row r="740" ht="13.5" customHeight="1"/>
+    <row r="741" ht="13.5" customHeight="1"/>
+    <row r="742" ht="13.5" customHeight="1"/>
+    <row r="743" ht="13.5" customHeight="1"/>
+    <row r="744" ht="13.5" customHeight="1"/>
+    <row r="745" ht="13.5" customHeight="1"/>
+    <row r="746" ht="13.5" customHeight="1"/>
+    <row r="747" ht="13.5" customHeight="1"/>
+    <row r="748" ht="13.5" customHeight="1"/>
+    <row r="749" ht="13.5" customHeight="1"/>
+    <row r="750" ht="13.5" customHeight="1"/>
+    <row r="751" ht="13.5" customHeight="1"/>
+    <row r="752" ht="13.5" customHeight="1"/>
+    <row r="753" ht="13.5" customHeight="1"/>
+    <row r="754" ht="13.5" customHeight="1"/>
+    <row r="755" ht="13.5" customHeight="1"/>
+    <row r="756" ht="13.5" customHeight="1"/>
+    <row r="757" ht="13.5" customHeight="1"/>
+    <row r="758" ht="13.5" customHeight="1"/>
+    <row r="759" ht="13.5" customHeight="1"/>
+    <row r="760" ht="13.5" customHeight="1"/>
+    <row r="761" ht="13.5" customHeight="1"/>
+    <row r="762" ht="13.5" customHeight="1"/>
+    <row r="763" ht="13.5" customHeight="1"/>
+    <row r="764" ht="13.5" customHeight="1"/>
+    <row r="765" ht="13.5" customHeight="1"/>
+    <row r="766" ht="13.5" customHeight="1"/>
+    <row r="767" ht="13.5" customHeight="1"/>
+    <row r="768" ht="13.5" customHeight="1"/>
+    <row r="769" ht="13.5" customHeight="1"/>
+    <row r="770" ht="13.5" customHeight="1"/>
+    <row r="771" ht="13.5" customHeight="1"/>
+    <row r="772" ht="13.5" customHeight="1"/>
+    <row r="773" ht="13.5" customHeight="1"/>
+    <row r="774" ht="13.5" customHeight="1"/>
+    <row r="775" ht="13.5" customHeight="1"/>
+    <row r="776" ht="13.5" customHeight="1"/>
+    <row r="777" ht="13.5" customHeight="1"/>
+    <row r="778" ht="13.5" customHeight="1"/>
+    <row r="779" ht="13.5" customHeight="1"/>
+    <row r="780" ht="13.5" customHeight="1"/>
+    <row r="781" ht="13.5" customHeight="1"/>
+    <row r="782" ht="13.5" customHeight="1"/>
+    <row r="783" ht="13.5" customHeight="1"/>
+    <row r="784" ht="13.5" customHeight="1"/>
+    <row r="785" ht="13.5" customHeight="1"/>
+    <row r="786" ht="13.5" customHeight="1"/>
+    <row r="787" ht="13.5" customHeight="1"/>
+    <row r="788" ht="13.5" customHeight="1"/>
+    <row r="789" ht="13.5" customHeight="1"/>
+    <row r="790" ht="13.5" customHeight="1"/>
+    <row r="791" ht="13.5" customHeight="1"/>
+    <row r="792" ht="13.5" customHeight="1"/>
+    <row r="793" ht="13.5" customHeight="1"/>
+    <row r="794" ht="13.5" customHeight="1"/>
+    <row r="795" ht="13.5" customHeight="1"/>
+    <row r="796" ht="13.5" customHeight="1"/>
+    <row r="797" ht="13.5" customHeight="1"/>
+    <row r="798" ht="13.5" customHeight="1"/>
+    <row r="799" ht="13.5" customHeight="1"/>
+    <row r="800" ht="13.5" customHeight="1"/>
+    <row r="801" ht="13.5" customHeight="1"/>
+    <row r="802" ht="13.5" customHeight="1"/>
+    <row r="803" ht="13.5" customHeight="1"/>
+    <row r="804" ht="13.5" customHeight="1"/>
+    <row r="805" ht="13.5" customHeight="1"/>
+    <row r="806" ht="13.5" customHeight="1"/>
+    <row r="807" ht="13.5" customHeight="1"/>
+    <row r="808" ht="13.5" customHeight="1"/>
+    <row r="809" ht="13.5" customHeight="1"/>
+    <row r="810" ht="13.5" customHeight="1"/>
+    <row r="811" ht="13.5" customHeight="1"/>
+    <row r="812" ht="13.5" customHeight="1"/>
+    <row r="813" ht="13.5" customHeight="1"/>
+    <row r="814" ht="13.5" customHeight="1"/>
+    <row r="815" ht="13.5" customHeight="1"/>
+    <row r="816" ht="13.5" customHeight="1"/>
+    <row r="817" ht="13.5" customHeight="1"/>
+    <row r="818" ht="13.5" customHeight="1"/>
+    <row r="819" ht="13.5" customHeight="1"/>
+    <row r="820" ht="13.5" customHeight="1"/>
+    <row r="821" ht="13.5" customHeight="1"/>
+    <row r="822" ht="13.5" customHeight="1"/>
+    <row r="823" ht="13.5" customHeight="1"/>
+    <row r="824" ht="13.5" customHeight="1"/>
+    <row r="825" ht="13.5" customHeight="1"/>
+    <row r="826" ht="13.5" customHeight="1"/>
+    <row r="827" ht="13.5" customHeight="1"/>
+    <row r="828" ht="13.5" customHeight="1"/>
+    <row r="829" ht="13.5" customHeight="1"/>
+    <row r="830" ht="13.5" customHeight="1"/>
+    <row r="831" ht="13.5" customHeight="1"/>
+    <row r="832" ht="13.5" customHeight="1"/>
+    <row r="833" ht="13.5" customHeight="1"/>
+    <row r="834" ht="13.5" customHeight="1"/>
+    <row r="835" ht="13.5" customHeight="1"/>
+    <row r="836" ht="13.5" customHeight="1"/>
+    <row r="837" ht="13.5" customHeight="1"/>
+    <row r="838" ht="13.5" customHeight="1"/>
+    <row r="839" ht="13.5" customHeight="1"/>
+    <row r="840" ht="13.5" customHeight="1"/>
+    <row r="841" ht="13.5" customHeight="1"/>
+    <row r="842" ht="13.5" customHeight="1"/>
+    <row r="843" ht="13.5" customHeight="1"/>
+    <row r="844" ht="13.5" customHeight="1"/>
+    <row r="845" ht="13.5" customHeight="1"/>
+    <row r="846" ht="13.5" customHeight="1"/>
+    <row r="847" ht="13.5" customHeight="1"/>
+    <row r="848" ht="13.5" customHeight="1"/>
+    <row r="849" ht="13.5" customHeight="1"/>
+    <row r="850" ht="13.5" customHeight="1"/>
+    <row r="851" ht="13.5" customHeight="1"/>
+    <row r="852" ht="13.5" customHeight="1"/>
+    <row r="853" ht="13.5" customHeight="1"/>
+    <row r="854" ht="13.5" customHeight="1"/>
+    <row r="855" ht="13.5" customHeight="1"/>
+    <row r="856" ht="13.5" customHeight="1"/>
+    <row r="857" ht="13.5" customHeight="1"/>
+    <row r="858" ht="13.5" customHeight="1"/>
+    <row r="859" ht="13.5" customHeight="1"/>
+    <row r="860" ht="13.5" customHeight="1"/>
+    <row r="861" ht="13.5" customHeight="1"/>
+    <row r="862" ht="13.5" customHeight="1"/>
+    <row r="863" ht="13.5" customHeight="1"/>
+    <row r="864" ht="13.5" customHeight="1"/>
+    <row r="865" ht="13.5" customHeight="1"/>
+    <row r="866" ht="13.5" customHeight="1"/>
+    <row r="867" ht="13.5" customHeight="1"/>
+    <row r="868" ht="13.5" customHeight="1"/>
+    <row r="869" ht="13.5" customHeight="1"/>
+    <row r="870" ht="13.5" customHeight="1"/>
+    <row r="871" ht="13.5" customHeight="1"/>
+    <row r="872" ht="13.5" customHeight="1"/>
+    <row r="873" ht="13.5" customHeight="1"/>
+    <row r="874" ht="13.5" customHeight="1"/>
+    <row r="875" ht="13.5" customHeight="1"/>
+    <row r="876" ht="13.5" customHeight="1"/>
+    <row r="877" ht="13.5" customHeight="1"/>
+    <row r="878" ht="13.5" customHeight="1"/>
+    <row r="879" ht="13.5" customHeight="1"/>
+    <row r="880" ht="13.5" customHeight="1"/>
+    <row r="881" ht="13.5" customHeight="1"/>
+    <row r="882" ht="13.5" customHeight="1"/>
+    <row r="883" ht="13.5" customHeight="1"/>
+    <row r="884" ht="13.5" customHeight="1"/>
+    <row r="885" ht="13.5" customHeight="1"/>
+    <row r="886" ht="13.5" customHeight="1"/>
+    <row r="887" ht="13.5" customHeight="1"/>
+    <row r="888" ht="13.5" customHeight="1"/>
+    <row r="889" ht="13.5" customHeight="1"/>
+    <row r="890" ht="13.5" customHeight="1"/>
+    <row r="891" ht="13.5" customHeight="1"/>
+    <row r="892" ht="13.5" customHeight="1"/>
+    <row r="893" ht="13.5" customHeight="1"/>
+    <row r="894" ht="13.5" customHeight="1"/>
+    <row r="895" ht="13.5" customHeight="1"/>
+    <row r="896" ht="13.5" customHeight="1"/>
+    <row r="897" ht="13.5" customHeight="1"/>
+    <row r="898" ht="13.5" customHeight="1"/>
+    <row r="899" ht="13.5" customHeight="1"/>
+    <row r="900" ht="13.5" customHeight="1"/>
+    <row r="901" ht="13.5" customHeight="1"/>
+    <row r="902" ht="13.5" customHeight="1"/>
+    <row r="903" ht="13.5" customHeight="1"/>
+    <row r="904" ht="13.5" customHeight="1"/>
+    <row r="905" ht="13.5" customHeight="1"/>
+    <row r="906" ht="13.5" customHeight="1"/>
+    <row r="907" ht="13.5" customHeight="1"/>
+    <row r="908" ht="13.5" customHeight="1"/>
+    <row r="909" ht="13.5" customHeight="1"/>
+    <row r="910" ht="13.5" customHeight="1"/>
+    <row r="911" ht="13.5" customHeight="1"/>
+    <row r="912" ht="13.5" customHeight="1"/>
+    <row r="913" ht="13.5" customHeight="1"/>
+    <row r="914" ht="13.5" customHeight="1"/>
+    <row r="915" ht="13.5" customHeight="1"/>
+    <row r="916" ht="13.5" customHeight="1"/>
+    <row r="917" ht="13.5" customHeight="1"/>
+    <row r="918" ht="13.5" customHeight="1"/>
+    <row r="919" ht="13.5" customHeight="1"/>
+    <row r="920" ht="13.5" customHeight="1"/>
+    <row r="921" ht="13.5" customHeight="1"/>
+    <row r="922" ht="13.5" customHeight="1"/>
+    <row r="923" ht="13.5" customHeight="1"/>
+    <row r="924" ht="13.5" customHeight="1"/>
+    <row r="925" ht="13.5" customHeight="1"/>
+    <row r="926" ht="13.5" customHeight="1"/>
+    <row r="927" ht="13.5" customHeight="1"/>
+    <row r="928" ht="13.5" customHeight="1"/>
+    <row r="929" ht="13.5" customHeight="1"/>
+    <row r="930" ht="13.5" customHeight="1"/>
+    <row r="931" ht="13.5" customHeight="1"/>
+    <row r="932" ht="13.5" customHeight="1"/>
+    <row r="933" ht="13.5" customHeight="1"/>
+    <row r="934" ht="13.5" customHeight="1"/>
+    <row r="935" ht="13.5" customHeight="1"/>
+    <row r="936" ht="13.5" customHeight="1"/>
+    <row r="937" ht="13.5" customHeight="1"/>
+    <row r="938" ht="13.5" customHeight="1"/>
+    <row r="939" ht="13.5" customHeight="1"/>
+    <row r="940" ht="13.5" customHeight="1"/>
+    <row r="941" ht="13.5" customHeight="1"/>
+    <row r="942" ht="13.5" customHeight="1"/>
+    <row r="943" ht="13.5" customHeight="1"/>
+    <row r="944" ht="13.5" customHeight="1"/>
+    <row r="945" ht="13.5" customHeight="1"/>
+    <row r="946" ht="13.5" customHeight="1"/>
+    <row r="947" ht="13.5" customHeight="1"/>
+    <row r="948" ht="13.5" customHeight="1"/>
+    <row r="949" ht="13.5" customHeight="1"/>
+    <row r="950" ht="13.5" customHeight="1"/>
+    <row r="951" ht="13.5" customHeight="1"/>
+    <row r="952" ht="13.5" customHeight="1"/>
+    <row r="953" ht="13.5" customHeight="1"/>
+    <row r="954" ht="13.5" customHeight="1"/>
+    <row r="955" ht="13.5" customHeight="1"/>
+    <row r="956" ht="13.5" customHeight="1"/>
+    <row r="957" ht="13.5" customHeight="1"/>
+    <row r="958" ht="13.5" customHeight="1"/>
+    <row r="959" ht="13.5" customHeight="1"/>
+    <row r="960" ht="13.5" customHeight="1"/>
+    <row r="961" ht="13.5" customHeight="1"/>
+    <row r="962" ht="13.5" customHeight="1"/>
+    <row r="963" ht="13.5" customHeight="1"/>
+    <row r="964" ht="13.5" customHeight="1"/>
+    <row r="965" ht="13.5" customHeight="1"/>
+    <row r="966" ht="13.5" customHeight="1"/>
+    <row r="967" ht="13.5" customHeight="1"/>
+    <row r="968" ht="13.5" customHeight="1"/>
+    <row r="969" ht="13.5" customHeight="1"/>
+    <row r="970" ht="13.5" customHeight="1"/>
+    <row r="971" ht="13.5" customHeight="1"/>
+    <row r="972" ht="13.5" customHeight="1"/>
+    <row r="973" ht="13.5" customHeight="1"/>
+    <row r="974" ht="13.5" customHeight="1"/>
+    <row r="975" ht="13.5" customHeight="1"/>
+    <row r="976" ht="13.5" customHeight="1"/>
+    <row r="977" ht="13.5" customHeight="1"/>
+    <row r="978" ht="13.5" customHeight="1"/>
+    <row r="979" ht="13.5" customHeight="1"/>
+    <row r="980" ht="13.5" customHeight="1"/>
+    <row r="981" ht="13.5" customHeight="1"/>
+    <row r="982" ht="13.5" customHeight="1"/>
+    <row r="983" ht="13.5" customHeight="1"/>
+    <row r="984" ht="13.5" customHeight="1"/>
+    <row r="985" ht="13.5" customHeight="1"/>
+    <row r="986" ht="13.5" customHeight="1"/>
+    <row r="987" ht="13.5" customHeight="1"/>
+    <row r="988" ht="13.5" customHeight="1"/>
+    <row r="989" ht="13.5" customHeight="1"/>
+    <row r="990" ht="13.5" customHeight="1"/>
+    <row r="991" ht="13.5" customHeight="1"/>
+    <row r="992" ht="13.5" customHeight="1"/>
+    <row r="993" ht="13.5" customHeight="1"/>
+    <row r="994" ht="13.5" customHeight="1"/>
+    <row r="995" ht="13.5" customHeight="1"/>
+    <row r="996" ht="13.5" customHeight="1"/>
+    <row r="997" ht="13.5" customHeight="1"/>
+    <row r="998" ht="13.5" customHeight="1"/>
+    <row r="999" ht="13.5" customHeight="1"/>
+    <row r="1000" ht="13.5" customHeight="1"/>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup orientation="landscape"/>
 </worksheet>
 </file>